--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18A5B0B5-FE8B-4060-9268-AE9895F60F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{203938AA-C9D6-4019-89EA-E7D2CE6B2A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8465,7 +8465,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE96781D-FF40-441B-82B2-DDD08DD456A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{811CF0A0-40D7-4938-A553-0772589F71F8}">
   <dimension ref="B9:D1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20657,7 +20657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39994794-2E14-4EDD-A8E5-05C289883757}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D6ECB70-EAC4-40C2-B31C-BE3002D47205}">
   <dimension ref="B9:H1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{203938AA-C9D6-4019-89EA-E7D2CE6B2A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52F587FF-CA44-4AC6-B8BA-1CD63B09155D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8465,7 +8465,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{811CF0A0-40D7-4938-A553-0772589F71F8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{930E3F8C-43F6-408F-85A3-54A628E6A6DE}">
   <dimension ref="B9:D1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20657,7 +20657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D6ECB70-EAC4-40C2-B31C-BE3002D47205}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D87EE4CD-2117-435A-BBA1-E13663B369AB}">
   <dimension ref="B9:H1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52F587FF-CA44-4AC6-B8BA-1CD63B09155D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C2D6A8B-A5B7-49E3-A4D4-8D52EA0F14F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8465,7 +8465,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{930E3F8C-43F6-408F-85A3-54A628E6A6DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84929580-C975-4756-BFD0-BFE76589A487}">
   <dimension ref="B9:D1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20657,7 +20657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D87EE4CD-2117-435A-BBA1-E13663B369AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CA0090C-C442-427F-AEB3-89A752407D9A}">
   <dimension ref="B9:H1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C2D6A8B-A5B7-49E3-A4D4-8D52EA0F14F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFCD3FC7-B573-4DB1-8D9E-8DB096865B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8465,7 +8465,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84929580-C975-4756-BFD0-BFE76589A487}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B354EC7B-C474-4D19-8851-2C1628FA2EA5}">
   <dimension ref="B9:D1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20657,7 +20657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CA0090C-C442-427F-AEB3-89A752407D9A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{947A2A52-81AD-43F0-8033-E31053556CD3}">
   <dimension ref="B9:H1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFCD3FC7-B573-4DB1-8D9E-8DB096865B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{404D212B-F7D4-4961-AA46-B37E7084EE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8465,7 +8465,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B354EC7B-C474-4D19-8851-2C1628FA2EA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBFC2BF2-FE72-42A7-9DC1-5135D47C259B}">
   <dimension ref="B9:D1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20657,7 +20657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{947A2A52-81AD-43F0-8033-E31053556CD3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7017DECA-2082-4307-AE55-22DF3A8EED61}">
   <dimension ref="B9:H1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{404D212B-F7D4-4961-AA46-B37E7084EE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE495724-AC9A-4D43-A2EB-7EA68D5B0459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8465,7 +8465,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBFC2BF2-FE72-42A7-9DC1-5135D47C259B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5748BDAD-89B7-4FBD-B1C8-9E30977DBA0D}">
   <dimension ref="B9:D1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20657,7 +20657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7017DECA-2082-4307-AE55-22DF3A8EED61}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{977D989B-FCC9-478A-98EF-178EAF52D7BA}">
   <dimension ref="B9:H1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE495724-AC9A-4D43-A2EB-7EA68D5B0459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8EE7BD8-FA47-40D1-AA49-B69E6978A866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8465,7 +8465,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5748BDAD-89B7-4FBD-B1C8-9E30977DBA0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E5EF1A-9B5C-4872-8BE6-5B72170025CB}">
   <dimension ref="B9:D1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20657,7 +20657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{977D989B-FCC9-478A-98EF-178EAF52D7BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F46C9979-19BF-44EE-93B4-7F6D8FF305D3}">
   <dimension ref="B9:H1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8EE7BD8-FA47-40D1-AA49-B69E6978A866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{599233D9-AF68-4836-B27B-FF2AB355E1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8465,7 +8465,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E5EF1A-9B5C-4872-8BE6-5B72170025CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52DE684E-139E-4C55-B5E8-1B2A36794B87}">
   <dimension ref="B9:D1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20657,7 +20657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F46C9979-19BF-44EE-93B4-7F6D8FF305D3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54503564-3A7D-450D-9A9B-5B5E477882AB}">
   <dimension ref="B9:H1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{599233D9-AF68-4836-B27B-FF2AB355E1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1210BA40-CDFD-4C8F-9385-5E7A9BAED2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1241,13 +1241,13 @@
     <t>g64</t>
   </si>
   <si>
-    <t>f97p50</t>
-  </si>
-  <si>
     <t>f96p10</t>
   </si>
   <si>
     <t>f96p90</t>
+  </si>
+  <si>
+    <t>f96p50</t>
   </si>
   <si>
     <t>grid_node</t>
@@ -8465,7 +8465,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52DE684E-139E-4C55-B5E8-1B2A36794B87}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F10BE571-86D0-4FFB-B701-5D44FDB5B5EE}">
   <dimension ref="B9:D1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20657,7 +20657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54503564-3A7D-450D-9A9B-5B5E477882AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B4227E2-00F8-4928-B080-24E622175B97}">
   <dimension ref="B9:H1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -43248,7 +43248,7 @@
         <v>337</v>
       </c>
       <c r="U12" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" spans="2:24">
@@ -43291,7 +43291,7 @@
         <v>343</v>
       </c>
       <c r="U13" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="14" spans="2:24">
@@ -43334,7 +43334,7 @@
         <v>349</v>
       </c>
       <c r="U14" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="15" spans="2:24">
@@ -44151,11 +44151,11 @@
       </c>
       <c r="C36" t="str">
         <f t="shared" si="5"/>
-        <v>e 1.5 deg no OS.f97p50</v>
+        <v>e 1.5 deg no OS.f96p50</v>
       </c>
       <c r="H36" t="str">
         <f t="shared" si="2"/>
-        <v>e 1.5 deg no OS.f97p50</v>
+        <v>e 1.5 deg no OS.f96p50</v>
       </c>
       <c r="I36" t="str">
         <f t="shared" si="3"/>
@@ -44163,7 +44163,7 @@
       </c>
       <c r="J36" t="str">
         <f t="shared" si="4"/>
-        <v>f97p50</v>
+        <v>f96p50</v>
       </c>
       <c r="N36">
         <v>5</v>
@@ -44188,11 +44188,11 @@
       </c>
       <c r="C37" t="str">
         <f t="shared" si="5"/>
-        <v>d 1.5 deg OS.f97p50</v>
+        <v>d 1.5 deg OS.f96p50</v>
       </c>
       <c r="H37" t="str">
         <f t="shared" si="2"/>
-        <v>d 1.5 deg OS.f97p50</v>
+        <v>d 1.5 deg OS.f96p50</v>
       </c>
       <c r="I37" t="str">
         <f t="shared" si="3"/>
@@ -44200,7 +44200,7 @@
       </c>
       <c r="J37" t="str">
         <f t="shared" si="4"/>
-        <v>f97p50</v>
+        <v>f96p50</v>
       </c>
       <c r="N37">
         <v>5</v>
@@ -44225,11 +44225,11 @@
       </c>
       <c r="C38" t="str">
         <f t="shared" si="5"/>
-        <v>c 2 deg (67%).f97p50</v>
+        <v>c 2 deg (67%).f96p50</v>
       </c>
       <c r="H38" t="str">
         <f t="shared" si="2"/>
-        <v>c 2 deg (67%).f97p50</v>
+        <v>c 2 deg (67%).f96p50</v>
       </c>
       <c r="I38" t="str">
         <f t="shared" si="3"/>
@@ -44237,7 +44237,7 @@
       </c>
       <c r="J38" t="str">
         <f t="shared" si="4"/>
-        <v>f97p50</v>
+        <v>f96p50</v>
       </c>
       <c r="N38">
         <v>5</v>
@@ -44262,11 +44262,11 @@
       </c>
       <c r="C39" t="str">
         <f t="shared" si="5"/>
-        <v>b 2 deg (50%).f97p50</v>
+        <v>b 2 deg (50%).f96p50</v>
       </c>
       <c r="H39" t="str">
         <f t="shared" si="2"/>
-        <v>b 2 deg (50%).f97p50</v>
+        <v>b 2 deg (50%).f96p50</v>
       </c>
       <c r="I39" t="str">
         <f t="shared" si="3"/>
@@ -44274,7 +44274,7 @@
       </c>
       <c r="J39" t="str">
         <f t="shared" si="4"/>
-        <v>f97p50</v>
+        <v>f96p50</v>
       </c>
       <c r="N39">
         <v>5</v>
@@ -44299,11 +44299,11 @@
       </c>
       <c r="C40" t="str">
         <f t="shared" si="5"/>
-        <v>a 3 deg.f97p50</v>
+        <v>a 3 deg.f96p50</v>
       </c>
       <c r="H40" t="str">
         <f t="shared" si="2"/>
-        <v>a 3 deg.f97p50</v>
+        <v>a 3 deg.f96p50</v>
       </c>
       <c r="I40" t="str">
         <f t="shared" si="3"/>
@@ -44311,7 +44311,7 @@
       </c>
       <c r="J40" t="str">
         <f t="shared" si="4"/>
-        <v>f97p50</v>
+        <v>f96p50</v>
       </c>
       <c r="N40">
         <v>5</v>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1210BA40-CDFD-4C8F-9385-5E7A9BAED2EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{637937DE-252C-49C4-A4CF-8AE3ABFF36C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="12682" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap_OLD" sheetId="70" r:id="rId1"/>
@@ -8465,7 +8465,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F10BE571-86D0-4FFB-B701-5D44FDB5B5EE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0509CF8E-53F2-4C0B-9059-B4326F3E6AAD}">
   <dimension ref="B9:D1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -20657,7 +20657,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B4227E2-00F8-4928-B080-24E622175B97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7CD61AC-9DD2-453E-9229-E7CF0D9DC363}">
   <dimension ref="B9:H1116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C2779D2-3A95-44A2-B517-8CD1EA13045C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2D95EA3-3B8B-4F3F-95E2-662C74A67532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8891,7 +8891,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C1FF46B-2796-47BF-B66F-B1045190FA08}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61AB5D57-7AD9-425C-9AA1-FD46D9C6E852}">
   <dimension ref="B9:D298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12085,7 +12085,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A71B8A6-7CFB-4AEA-81F7-C63D0F7F3BED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0883FD8E-757D-4FAA-A07B-951893F66083}">
   <dimension ref="B9:H298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2D95EA3-3B8B-4F3F-95E2-662C74A67532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74BA20FC-5413-47FB-AA60-189D02ABFCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8891,7 +8891,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61AB5D57-7AD9-425C-9AA1-FD46D9C6E852}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DB8703E-96EB-46F4-A765-E9919C0F8F56}">
   <dimension ref="B9:D298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12085,7 +12085,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0883FD8E-757D-4FAA-A07B-951893F66083}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D439DC9C-53BB-4AD0-B66F-8E82670D1693}">
   <dimension ref="B9:H298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{74BA20FC-5413-47FB-AA60-189D02ABFCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{34DC773A-AEAB-4721-8DBA-0693691F6C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8891,7 +8891,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DB8703E-96EB-46F4-A765-E9919C0F8F56}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EC46BFE-99A6-43F1-AE99-E27934AFC484}">
   <dimension ref="B9:D298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12085,7 +12085,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D439DC9C-53BB-4AD0-B66F-8E82670D1693}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ABBA048-A8B6-4396-B3A8-A7CF91D711E3}">
   <dimension ref="B9:H298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AC33804-0D58-4679-8984-A8B21FE0E74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{64DF6711-24B1-4A2A-A508-DFBE767D68FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8891,7 +8891,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8220F6F9-C22B-458D-A490-3CA95DBFEE5E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39179948-8D39-4D3F-9A9A-F666D700FBF0}">
   <dimension ref="B9:D298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12085,7 +12085,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E37C466-FEE5-47BD-A79F-F2CEBA3186BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{689A0A43-949E-47D9-8BC6-5C3E7DF09684}">
   <dimension ref="B9:H298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64DF6711-24B1-4A2A-A508-DFBE767D68FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{09868DF0-E8C5-4B60-AE77-65F0DC4A3AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8891,7 +8891,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39179948-8D39-4D3F-9A9A-F666D700FBF0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF52B901-8A73-4297-9939-7C24A33E88DC}">
   <dimension ref="B9:D298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12085,7 +12085,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{689A0A43-949E-47D9-8BC6-5C3E7DF09684}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68DEF76B-EE4C-4B44-ABA5-02D0D3E0F8AA}">
   <dimension ref="B9:H298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09868DF0-E8C5-4B60-AE77-65F0DC4A3AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFF35090-E665-44C9-9C7C-A58F7CE71979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8891,7 +8891,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF52B901-8A73-4297-9939-7C24A33E88DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BF1B6A-07C3-4AE8-91E2-1570C4BEE289}">
   <dimension ref="B9:D298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12085,7 +12085,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68DEF76B-EE4C-4B44-ABA5-02D0D3E0F8AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118B2726-F61C-4181-9ABD-719AEC63149E}">
   <dimension ref="B9:H298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFF35090-E665-44C9-9C7C-A58F7CE71979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBED1195-F36F-4BCC-B1C2-D7C66758D91A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8891,7 +8891,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BF1B6A-07C3-4AE8-91E2-1570C4BEE289}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE11C847-FD89-4245-A8F8-178664313562}">
   <dimension ref="B9:D298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12085,7 +12085,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118B2726-F61C-4181-9ABD-719AEC63149E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B53FD76B-FB09-4255-9052-55474412E4EA}">
   <dimension ref="B9:H298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{38352A79-3268-41B7-8633-79A392964542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AEBD19E-40D1-4F38-AF1C-E80959B29F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2852" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2852" uniqueCount="745">
   <si>
     <t>Unit</t>
   </si>
@@ -2298,6 +2298,9 @@
   </si>
   <si>
     <t>Hokkaidō</t>
+  </si>
+  <si>
+    <t>Yamagata</t>
   </si>
   <si>
     <t>Akita</t>
@@ -8906,24 +8909,24 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2186A339-34DA-49E4-BAB6-D7223F8F388F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BA644FC-647E-460B-886F-4CF924F99980}">
   <dimension ref="B9:D298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:4">
       <c r="B9" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="10" spans="2:4">
       <c r="B10" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C10" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D10" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="11" spans="2:4">
@@ -10933,10 +10936,10 @@
         <v>587</v>
       </c>
       <c r="C193">
-        <v>41.3361912214217</v>
+        <v>27.229708944713892</v>
       </c>
       <c r="D193">
-        <v>140.82133755355883</v>
+        <v>128.34501674818958</v>
       </c>
     </row>
     <row r="194" spans="2:4">
@@ -10944,10 +10947,10 @@
         <v>588</v>
       </c>
       <c r="C194">
-        <v>40.045024127788608</v>
+        <v>24.81653263538637</v>
       </c>
       <c r="D194">
-        <v>140.08826559663316</v>
+        <v>124.47994184709124</v>
       </c>
     </row>
     <row r="195" spans="2:4">
@@ -10955,10 +10958,10 @@
         <v>589</v>
       </c>
       <c r="C195">
-        <v>42.76546822805534</v>
+        <v>25.790796362754623</v>
       </c>
       <c r="D195">
-        <v>142.3661927191954</v>
+        <v>138.21329309141947</v>
       </c>
     </row>
     <row r="196" spans="2:4">
@@ -10966,10 +10969,10 @@
         <v>590</v>
       </c>
       <c r="C196">
-        <v>42.492460260496109</v>
+        <v>33.659849545344365</v>
       </c>
       <c r="D196">
-        <v>140.46889911272919</v>
+        <v>129.68428282334222</v>
       </c>
     </row>
     <row r="197" spans="2:4">
@@ -10977,10 +10980,10 @@
         <v>591</v>
       </c>
       <c r="C197">
-        <v>44.41957532562013</v>
+        <v>30.737058363239601</v>
       </c>
       <c r="D197">
-        <v>141.45572674705218</v>
+        <v>130.61472030713247</v>
       </c>
     </row>
     <row r="198" spans="2:4">
@@ -10988,10 +10991,10 @@
         <v>592</v>
       </c>
       <c r="C198">
-        <v>44.390376612512185</v>
+        <v>32.431931356412775</v>
       </c>
       <c r="D198">
-        <v>142.60916164431279</v>
+        <v>130.39458183486042</v>
       </c>
     </row>
     <row r="199" spans="2:4">
@@ -10999,10 +11002,10 @@
         <v>593</v>
       </c>
       <c r="C199">
-        <v>43.969915143757859</v>
+        <v>31.546446690591694</v>
       </c>
       <c r="D199">
-        <v>144.34572196185522</v>
+        <v>131.40418241459082</v>
       </c>
     </row>
     <row r="200" spans="2:4">
@@ -11010,10 +11013,10 @@
         <v>594</v>
       </c>
       <c r="C200">
-        <v>43.147679382638273</v>
+        <v>33.276315860814783</v>
       </c>
       <c r="D200">
-        <v>145.02240376824813</v>
+        <v>132.4954976807833</v>
       </c>
     </row>
     <row r="201" spans="2:4">
@@ -11021,10 +11024,10 @@
         <v>595</v>
       </c>
       <c r="C201">
-        <v>42.877883273520922</v>
+        <v>33.8846796362755</v>
       </c>
       <c r="D201">
-        <v>143.64084508019593</v>
+        <v>135.62287055132165</v>
       </c>
     </row>
     <row r="202" spans="2:4">
@@ -11032,10 +11035,10 @@
         <v>596</v>
       </c>
       <c r="C202">
-        <v>33.659849545344365</v>
+        <v>35.233660181862305</v>
       </c>
       <c r="D202">
-        <v>129.68428282334222</v>
+        <v>137.47317236567724</v>
       </c>
     </row>
     <row r="203" spans="2:4">
@@ -11043,10 +11046,10 @@
         <v>597</v>
       </c>
       <c r="C203">
-        <v>30.737058363239601</v>
+        <v>35.183697939433166</v>
       </c>
       <c r="D203">
-        <v>130.61472030713247</v>
+        <v>135.11575079479454</v>
       </c>
     </row>
     <row r="204" spans="2:4">
@@ -11054,10 +11057,10 @@
         <v>598</v>
       </c>
       <c r="C204">
-        <v>32.431931356412775</v>
+        <v>34.424271854510224</v>
       </c>
       <c r="D204">
-        <v>130.39458183486042</v>
+        <v>133.6245445918176</v>
       </c>
     </row>
     <row r="205" spans="2:4">
@@ -11065,10 +11068,10 @@
         <v>599</v>
       </c>
       <c r="C205">
-        <v>35.233660181862305</v>
+        <v>34.887767734275947</v>
       </c>
       <c r="D205">
-        <v>137.47317236567724</v>
+        <v>132.33028219449398</v>
       </c>
     </row>
     <row r="206" spans="2:4">
@@ -11076,10 +11079,10 @@
         <v>600</v>
       </c>
       <c r="C206">
-        <v>34.484226545425187</v>
+        <v>43.969915143757859</v>
       </c>
       <c r="D206">
-        <v>135.60916461195606</v>
+        <v>144.34572196185522</v>
       </c>
     </row>
     <row r="207" spans="2:4">
@@ -11087,10 +11090,10 @@
         <v>601</v>
       </c>
       <c r="C207">
-        <v>31.546446690591694</v>
+        <v>43.147679382638273</v>
       </c>
       <c r="D207">
-        <v>131.40418241459082</v>
+        <v>145.02240376824813</v>
       </c>
     </row>
     <row r="208" spans="2:4">
@@ -11098,10 +11101,10 @@
         <v>602</v>
       </c>
       <c r="C208">
-        <v>33.276315860814783</v>
+        <v>42.877883273520922</v>
       </c>
       <c r="D208">
-        <v>132.4954976807833</v>
+        <v>143.64084508019593</v>
       </c>
     </row>
     <row r="209" spans="2:4">
@@ -11109,10 +11112,10 @@
         <v>603</v>
       </c>
       <c r="C209">
-        <v>35.49060885721218</v>
+        <v>44.41957532562013</v>
       </c>
       <c r="D209">
-        <v>133.84305642513195</v>
+        <v>141.45572674705218</v>
       </c>
     </row>
     <row r="210" spans="2:4">
@@ -11120,10 +11123,10 @@
         <v>604</v>
       </c>
       <c r="C210">
-        <v>34.334339818137771</v>
+        <v>44.390376612512185</v>
       </c>
       <c r="D210">
-        <v>131.79891346832002</v>
+        <v>142.60916164431279</v>
       </c>
     </row>
     <row r="211" spans="2:4">
@@ -11131,10 +11134,10 @@
         <v>605</v>
       </c>
       <c r="C211">
-        <v>34.424271854510224</v>
+        <v>42.76546822805534</v>
       </c>
       <c r="D211">
-        <v>133.6245445918176</v>
+        <v>142.3661927191954</v>
       </c>
     </row>
     <row r="212" spans="2:4">
@@ -11142,10 +11145,10 @@
         <v>606</v>
       </c>
       <c r="C212">
-        <v>28.263927362997119</v>
+        <v>42.492460260496109</v>
       </c>
       <c r="D212">
-        <v>129.33184438251254</v>
+        <v>140.46889911272919</v>
       </c>
     </row>
     <row r="213" spans="2:4">
@@ -11153,10 +11156,10 @@
         <v>607</v>
       </c>
       <c r="C213">
-        <v>26.853629519883636</v>
+        <v>34.896415045465609</v>
       </c>
       <c r="D213">
-        <v>127.98617033570848</v>
+        <v>139.44682763432323</v>
       </c>
     </row>
     <row r="214" spans="2:4">
@@ -11164,10 +11167,10 @@
         <v>608</v>
       </c>
       <c r="C214">
-        <v>24.81653263538637</v>
+        <v>37.931621273035937</v>
       </c>
       <c r="D214">
-        <v>124.47994184709124</v>
+        <v>141.09154035819489</v>
       </c>
     </row>
     <row r="215" spans="2:4">
@@ -11175,10 +11178,10 @@
         <v>609</v>
       </c>
       <c r="C215">
-        <v>25.790796362754623</v>
+        <v>36.357810636517982</v>
       </c>
       <c r="D215">
-        <v>138.21329309141947</v>
+        <v>140.55700872293659</v>
       </c>
     </row>
     <row r="216" spans="2:4">
@@ -11186,10 +11189,10 @@
         <v>610</v>
       </c>
       <c r="C216">
-        <v>34.896415045465609</v>
+        <v>36.492708691076665</v>
       </c>
       <c r="D216">
-        <v>139.44682763432323</v>
+        <v>139.29880348917476</v>
       </c>
     </row>
     <row r="217" spans="2:4">
@@ -11197,10 +11200,10 @@
         <v>611</v>
       </c>
       <c r="C217">
-        <v>36.357810636517982</v>
+        <v>36.651819216966402</v>
       </c>
       <c r="D217">
-        <v>140.55700872293659</v>
+        <v>137.30237527512134</v>
       </c>
     </row>
     <row r="218" spans="2:4">
@@ -11208,10 +11211,10 @@
         <v>612</v>
       </c>
       <c r="C218">
-        <v>36.492708691076665</v>
+        <v>37.831696788177652</v>
       </c>
       <c r="D218">
-        <v>139.29880348917476</v>
+        <v>138.0488218190323</v>
       </c>
     </row>
     <row r="219" spans="2:4">
@@ -11219,10 +11222,10 @@
         <v>613</v>
       </c>
       <c r="C219">
-        <v>39.834029734760925</v>
+        <v>38.066519327594612</v>
       </c>
       <c r="D219">
-        <v>141.47741526648781</v>
+        <v>139.79221730633628</v>
       </c>
     </row>
     <row r="220" spans="2:4">
@@ -11230,10 +11233,10 @@
         <v>614</v>
       </c>
       <c r="C220">
-        <v>38.156451363967072</v>
+        <v>39.376957571878961</v>
       </c>
       <c r="D220">
-        <v>140.92706908580772</v>
+        <v>141.38523905888621</v>
       </c>
     </row>
     <row r="221" spans="2:4">
@@ -11241,10 +11244,10 @@
         <v>615</v>
       </c>
       <c r="C221">
-        <v>38.060095610710867</v>
+        <v>39.955092091416148</v>
       </c>
       <c r="D221">
-        <v>139.23536456982546</v>
+        <v>139.94024145148472</v>
       </c>
     </row>
     <row r="222" spans="2:4">
@@ -11252,10 +11255,10 @@
         <v>616</v>
       </c>
       <c r="C222">
-        <v>37.63184781846109</v>
+        <v>40.449718291464649</v>
       </c>
       <c r="D222">
-        <v>136.89752291232216</v>
+        <v>141.07509323095616</v>
       </c>
     </row>
     <row r="223" spans="2:4">
@@ -11263,10 +11266,10 @@
         <v>617</v>
       </c>
       <c r="C223">
-        <v>36.651819216966402</v>
+        <v>41.3361912214217</v>
       </c>
       <c r="D223">
-        <v>137.30237527512134</v>
+        <v>140.82133755355883</v>
       </c>
     </row>
     <row r="224" spans="2:4">
@@ -11538,10 +11541,10 @@
         <v>642</v>
       </c>
       <c r="C248">
-        <v>42.806884297437385</v>
+        <v>42.668041855318521</v>
       </c>
       <c r="D248">
-        <v>141.06989940130185</v>
+        <v>141.20667024886589</v>
       </c>
     </row>
     <row r="249" spans="2:4">
@@ -11549,10 +11552,10 @@
         <v>643</v>
       </c>
       <c r="C249">
-        <v>41.817969987702703</v>
+        <v>42.153430758298363</v>
       </c>
       <c r="D249">
-        <v>140.68036217722695</v>
+        <v>140.65295029849574</v>
       </c>
     </row>
     <row r="250" spans="2:4">
@@ -11692,10 +11695,10 @@
         <v>656</v>
       </c>
       <c r="C262">
-        <v>31.550192137224879</v>
+        <v>33.380951449092692</v>
       </c>
       <c r="D262">
-        <v>131.70164591938115</v>
+        <v>133.88858020407105</v>
       </c>
     </row>
     <row r="263" spans="2:4">
@@ -11703,10 +11706,10 @@
         <v>657</v>
       </c>
       <c r="C263">
-        <v>33.006234630874133</v>
+        <v>31.550192137224879</v>
       </c>
       <c r="D263">
-        <v>134.62653033705877</v>
+        <v>131.70164591938115</v>
       </c>
     </row>
     <row r="264" spans="2:4">
@@ -11714,10 +11717,10 @@
         <v>658</v>
       </c>
       <c r="C264">
-        <v>33.380951449092692</v>
+        <v>33.006234630874133</v>
       </c>
       <c r="D264">
-        <v>133.88858020407105</v>
+        <v>134.62653033705877</v>
       </c>
     </row>
     <row r="265" spans="2:4">
@@ -11736,10 +11739,10 @@
         <v>660</v>
       </c>
       <c r="C266">
-        <v>31.935615150249681</v>
+        <v>32.060074664872275</v>
       </c>
       <c r="D266">
-        <v>129.11096992059461</v>
+        <v>129.14882070629113</v>
       </c>
     </row>
     <row r="267" spans="2:4">
@@ -11758,10 +11761,10 @@
         <v>662</v>
       </c>
       <c r="C268">
-        <v>33.409055210459087</v>
+        <v>33.477307202348889</v>
       </c>
       <c r="D268">
-        <v>128.79554670645661</v>
+        <v>128.707228206498</v>
       </c>
     </row>
     <row r="269" spans="2:4">
@@ -11769,10 +11772,10 @@
         <v>663</v>
       </c>
       <c r="C269">
-        <v>43.198532086418936</v>
+        <v>41.382257626347794</v>
       </c>
       <c r="D269">
-        <v>140.92789175632942</v>
+        <v>140.21980443639964</v>
       </c>
     </row>
     <row r="270" spans="2:4">
@@ -11780,10 +11783,10 @@
         <v>664</v>
       </c>
       <c r="C270">
-        <v>41.449853601398999</v>
+        <v>42.598985177269242</v>
       </c>
       <c r="D270">
-        <v>142.07930331134563</v>
+        <v>141.89612420032034</v>
       </c>
     </row>
     <row r="271" spans="2:4">
@@ -11791,10 +11794,10 @@
         <v>665</v>
       </c>
       <c r="C271">
-        <v>41.382257626347794</v>
+        <v>41.449853601398999</v>
       </c>
       <c r="D271">
-        <v>140.21980443639964</v>
+        <v>142.07930331134563</v>
       </c>
     </row>
     <row r="272" spans="2:4">
@@ -11802,10 +11805,10 @@
         <v>666</v>
       </c>
       <c r="C272">
-        <v>42.767607745467593</v>
+        <v>43.562542709831241</v>
       </c>
       <c r="D272">
-        <v>144.72231619899657</v>
+        <v>140.28115734393396</v>
       </c>
     </row>
     <row r="273" spans="2:4">
@@ -11813,10 +11816,10 @@
         <v>667</v>
       </c>
       <c r="C273">
-        <v>43.947965722856047</v>
+        <v>45.027150159325508</v>
       </c>
       <c r="D273">
-        <v>144.48680019910688</v>
+        <v>140.05909940118082</v>
       </c>
     </row>
     <row r="274" spans="2:4">
@@ -11824,10 +11827,10 @@
         <v>668</v>
       </c>
       <c r="C274">
-        <v>44.697399359293172</v>
+        <v>45.222002904799162</v>
       </c>
       <c r="D274">
-        <v>144.6438108657</v>
+        <v>141.73911353372725</v>
       </c>
     </row>
     <row r="275" spans="2:4">
@@ -11835,10 +11838,10 @@
         <v>669</v>
       </c>
       <c r="C275">
-        <v>44.62245599564946</v>
+        <v>42.767607745467593</v>
       </c>
       <c r="D275">
-        <v>140.22939558571642</v>
+        <v>144.72231619899657</v>
       </c>
     </row>
     <row r="276" spans="2:4">
@@ -11846,10 +11849,10 @@
         <v>670</v>
       </c>
       <c r="C276">
-        <v>45.521776359374002</v>
+        <v>43.947965722856047</v>
       </c>
       <c r="D276">
-        <v>141.89612420032034</v>
+        <v>144.48680019910688</v>
       </c>
     </row>
     <row r="277" spans="2:4">
@@ -11857,10 +11860,10 @@
         <v>671</v>
       </c>
       <c r="C277">
-        <v>44.959701132046163</v>
+        <v>44.697399359293172</v>
       </c>
       <c r="D277">
-        <v>143.19146219971361</v>
+        <v>144.6438108657</v>
       </c>
     </row>
     <row r="278" spans="2:4">
@@ -11868,10 +11871,10 @@
         <v>672</v>
       </c>
       <c r="C278">
-        <v>39.345561508501049</v>
+        <v>44.959701132046163</v>
       </c>
       <c r="D278">
-        <v>139.05607831929763</v>
+        <v>143.19146219971361</v>
       </c>
     </row>
     <row r="279" spans="2:4">
@@ -11879,10 +11882,10 @@
         <v>673</v>
       </c>
       <c r="C279">
-        <v>37.877553267715399</v>
+        <v>39.345561508501049</v>
       </c>
       <c r="D279">
-        <v>138.12786820208541</v>
+        <v>139.05607831929763</v>
       </c>
     </row>
     <row r="280" spans="2:4">
@@ -11890,10 +11893,10 @@
         <v>674</v>
       </c>
       <c r="C280">
-        <v>37.315478040387561</v>
+        <v>37.877553267715399</v>
       </c>
       <c r="D280">
-        <v>136.59701420280243</v>
+        <v>138.12786820208541</v>
       </c>
     </row>
     <row r="281" spans="2:4">
@@ -11901,10 +11904,10 @@
         <v>675</v>
       </c>
       <c r="C281">
-        <v>38.597009558695028</v>
+        <v>37.315478040387561</v>
       </c>
       <c r="D281">
-        <v>136.66766900276934</v>
+        <v>136.59701420280243</v>
       </c>
     </row>
     <row r="282" spans="2:4">
@@ -11912,10 +11915,10 @@
         <v>676</v>
       </c>
       <c r="C282">
-        <v>34.920172840852004</v>
+        <v>38.597009558695028</v>
       </c>
       <c r="D282">
-        <v>130.06597435970772</v>
+        <v>136.66766900276934</v>
       </c>
     </row>
     <row r="283" spans="2:4">
@@ -11923,10 +11926,10 @@
         <v>677</v>
       </c>
       <c r="C283">
-        <v>35.577368491266093</v>
+        <v>34.920172840852004</v>
       </c>
       <c r="D283">
-        <v>132.02256882032972</v>
+        <v>130.06597435970772</v>
       </c>
     </row>
     <row r="284" spans="2:4">
@@ -11934,10 +11937,10 @@
         <v>678</v>
       </c>
       <c r="C284">
-        <v>37.592768485869293</v>
+        <v>35.577368491266093</v>
       </c>
       <c r="D284">
-        <v>133.24483647103926</v>
+        <v>132.02256882032972</v>
       </c>
     </row>
     <row r="285" spans="2:4">
@@ -11945,10 +11948,10 @@
         <v>679</v>
       </c>
       <c r="C285">
-        <v>36.303742631197451</v>
+        <v>37.592768485869293</v>
       </c>
       <c r="D285">
-        <v>135.77270820318856</v>
+        <v>133.24483647103926</v>
       </c>
     </row>
     <row r="286" spans="2:4">
@@ -11956,10 +11959,10 @@
         <v>680</v>
       </c>
       <c r="C286">
-        <v>36.327408956558621</v>
+        <v>36.303742631197451</v>
       </c>
       <c r="D286">
-        <v>134.24805199337632</v>
+        <v>135.77270820318856</v>
       </c>
     </row>
     <row r="287" spans="2:4">
@@ -11967,10 +11970,10 @@
         <v>681</v>
       </c>
       <c r="C287">
-        <v>26.989353149764732</v>
+        <v>36.327408956558621</v>
       </c>
       <c r="D287">
-        <v>141.88490915270651</v>
+        <v>134.24805199337632</v>
       </c>
     </row>
     <row r="288" spans="2:4">
@@ -11978,10 +11981,10 @@
         <v>682</v>
       </c>
       <c r="C288">
-        <v>23.983053648171296</v>
+        <v>26.989353149764732</v>
       </c>
       <c r="D288">
-        <v>153.43640819491492</v>
+        <v>141.88490915270651</v>
       </c>
     </row>
     <row r="289" spans="2:4">
@@ -11989,10 +11992,10 @@
         <v>683</v>
       </c>
       <c r="C289">
-        <v>24.741052240453403</v>
+        <v>23.983053648171296</v>
       </c>
       <c r="D289">
-        <v>141.39144705769962</v>
+        <v>153.43640819491492</v>
       </c>
     </row>
     <row r="290" spans="2:4">
@@ -12000,10 +12003,10 @@
         <v>684</v>
       </c>
       <c r="C290">
-        <v>22.863899417758542</v>
+        <v>24.741052240453403</v>
       </c>
       <c r="D290">
-        <v>141.18957620065129</v>
+        <v>141.39144705769962</v>
       </c>
     </row>
     <row r="291" spans="2:4">
@@ -12011,10 +12014,10 @@
         <v>685</v>
       </c>
       <c r="C291">
-        <v>32.219329312615159</v>
+        <v>22.863899417758542</v>
       </c>
       <c r="D291">
-        <v>139.3839535348304</v>
+        <v>141.18957620065129</v>
       </c>
     </row>
     <row r="292" spans="2:4">
@@ -12022,10 +12025,10 @@
         <v>686</v>
       </c>
       <c r="C292">
-        <v>30.682990357919081</v>
+        <v>31.113914698870417</v>
       </c>
       <c r="D292">
-        <v>139.59984320139591</v>
+        <v>139.50171153477521</v>
       </c>
     </row>
     <row r="293" spans="2:4">
@@ -12033,10 +12036,10 @@
         <v>687</v>
       </c>
       <c r="C293">
-        <v>33.830611630954962</v>
+        <v>34.205328449173521</v>
       </c>
       <c r="D293">
-        <v>139.54096420142352</v>
+        <v>137.73534153560257</v>
       </c>
     </row>
     <row r="294" spans="2:4">
@@ -12044,10 +12047,10 @@
         <v>688</v>
       </c>
       <c r="C294">
-        <v>34.205328449173521</v>
+        <v>33.580800418809254</v>
       </c>
       <c r="D294">
-        <v>137.73534153560257</v>
+        <v>139.54096420142346</v>
       </c>
     </row>
     <row r="295" spans="2:4">
@@ -12100,7 +12103,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{871C57FC-F5E9-4CB8-95D0-821140FB08C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A5702C8-DD3E-4FC6-A484-440067E00DEC}">
   <dimension ref="B9:H298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -15789,7 +15792,7 @@
         <v>693</v>
       </c>
       <c r="H193" t="s">
-        <v>734</v>
+        <v>722</v>
       </c>
     </row>
     <row r="194" spans="2:8">
@@ -15809,7 +15812,7 @@
         <v>693</v>
       </c>
       <c r="H194" t="s">
-        <v>738</v>
+        <v>722</v>
       </c>
     </row>
     <row r="195" spans="2:8">
@@ -15829,7 +15832,7 @@
         <v>693</v>
       </c>
       <c r="H195" t="s">
-        <v>737</v>
+        <v>722</v>
       </c>
     </row>
     <row r="196" spans="2:8">
@@ -15889,7 +15892,7 @@
         <v>693</v>
       </c>
       <c r="H198" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
     </row>
     <row r="199" spans="2:8">
@@ -15909,7 +15912,7 @@
         <v>693</v>
       </c>
       <c r="H199" t="s">
-        <v>737</v>
+        <v>722</v>
       </c>
     </row>
     <row r="200" spans="2:8">
@@ -15929,7 +15932,7 @@
         <v>693</v>
       </c>
       <c r="H200" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
     </row>
     <row r="201" spans="2:8">
@@ -15949,7 +15952,7 @@
         <v>693</v>
       </c>
       <c r="H201" t="s">
-        <v>737</v>
+        <v>710</v>
       </c>
     </row>
     <row r="202" spans="2:8">
@@ -15969,7 +15972,7 @@
         <v>693</v>
       </c>
       <c r="H202" t="s">
-        <v>722</v>
+        <v>703</v>
       </c>
     </row>
     <row r="203" spans="2:8">
@@ -15989,7 +15992,7 @@
         <v>693</v>
       </c>
       <c r="H203" t="s">
-        <v>722</v>
+        <v>702</v>
       </c>
     </row>
     <row r="204" spans="2:8">
@@ -16009,7 +16012,7 @@
         <v>693</v>
       </c>
       <c r="H204" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
     </row>
     <row r="205" spans="2:8">
@@ -16029,7 +16032,7 @@
         <v>693</v>
       </c>
       <c r="H205" t="s">
-        <v>703</v>
+        <v>733</v>
       </c>
     </row>
     <row r="206" spans="2:8">
@@ -16049,7 +16052,7 @@
         <v>693</v>
       </c>
       <c r="H206" t="s">
-        <v>700</v>
+        <v>737</v>
       </c>
     </row>
     <row r="207" spans="2:8">
@@ -16069,7 +16072,7 @@
         <v>693</v>
       </c>
       <c r="H207" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
     </row>
     <row r="208" spans="2:8">
@@ -16089,7 +16092,7 @@
         <v>693</v>
       </c>
       <c r="H208" t="s">
-        <v>718</v>
+        <v>737</v>
       </c>
     </row>
     <row r="209" spans="2:8">
@@ -16109,7 +16112,7 @@
         <v>693</v>
       </c>
       <c r="H209" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
     </row>
     <row r="210" spans="2:8">
@@ -16129,7 +16132,7 @@
         <v>693</v>
       </c>
       <c r="H210" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
     </row>
     <row r="211" spans="2:8">
@@ -16149,7 +16152,7 @@
         <v>693</v>
       </c>
       <c r="H211" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
     </row>
     <row r="212" spans="2:8">
@@ -16169,7 +16172,7 @@
         <v>693</v>
       </c>
       <c r="H212" t="s">
-        <v>739</v>
+        <v>722</v>
       </c>
     </row>
     <row r="213" spans="2:8">
@@ -16229,7 +16232,7 @@
         <v>693</v>
       </c>
       <c r="H215" t="s">
-        <v>722</v>
+        <v>705</v>
       </c>
     </row>
     <row r="216" spans="2:8">
@@ -16249,7 +16252,7 @@
         <v>693</v>
       </c>
       <c r="H216" t="s">
-        <v>722</v>
+        <v>694</v>
       </c>
     </row>
     <row r="217" spans="2:8">
@@ -16269,7 +16272,7 @@
         <v>693</v>
       </c>
       <c r="H217" t="s">
-        <v>705</v>
+        <v>714</v>
       </c>
     </row>
     <row r="218" spans="2:8">
@@ -16289,7 +16292,7 @@
         <v>693</v>
       </c>
       <c r="H218" t="s">
-        <v>694</v>
+        <v>722</v>
       </c>
     </row>
     <row r="219" spans="2:8">
@@ -16309,7 +16312,7 @@
         <v>693</v>
       </c>
       <c r="H219" t="s">
-        <v>720</v>
+        <v>738</v>
       </c>
     </row>
     <row r="220" spans="2:8">
@@ -16329,7 +16332,7 @@
         <v>693</v>
       </c>
       <c r="H220" t="s">
-        <v>699</v>
+        <v>720</v>
       </c>
     </row>
     <row r="221" spans="2:8">
@@ -16349,7 +16352,7 @@
         <v>693</v>
       </c>
       <c r="H221" t="s">
-        <v>722</v>
+        <v>739</v>
       </c>
     </row>
     <row r="222" spans="2:8">
@@ -16369,7 +16372,7 @@
         <v>693</v>
       </c>
       <c r="H222" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
     </row>
     <row r="223" spans="2:8">
@@ -16389,7 +16392,7 @@
         <v>693</v>
       </c>
       <c r="H223" t="s">
-        <v>714</v>
+        <v>734</v>
       </c>
     </row>
     <row r="224" spans="2:8">
@@ -17089,7 +17092,7 @@
         <v>693</v>
       </c>
       <c r="H258" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="259" spans="2:8">
@@ -17309,7 +17312,7 @@
         <v>693</v>
       </c>
       <c r="H269" t="s">
-        <v>737</v>
+        <v>722</v>
       </c>
     </row>
     <row r="270" spans="2:8">
@@ -17329,7 +17332,7 @@
         <v>693</v>
       </c>
       <c r="H270" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
     </row>
     <row r="271" spans="2:8">
@@ -17409,7 +17412,7 @@
         <v>693</v>
       </c>
       <c r="H274" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
     </row>
     <row r="275" spans="2:8">

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AEBD19E-40D1-4F38-AF1C-E80959B29F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{575FE622-9F38-4F18-89B0-1A7C966E8126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8909,7 +8909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BA644FC-647E-460B-886F-4CF924F99980}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E94F2948-6B27-4080-A14D-E85369C74425}">
   <dimension ref="B9:D298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12103,7 +12103,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A5702C8-DD3E-4FC6-A484-440067E00DEC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17AC6F4C-6D18-44E7-B545-3049D697CEE0}">
   <dimension ref="B9:H298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{575FE622-9F38-4F18-89B0-1A7C966E8126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{76313C0E-F9D8-4317-ADD4-6594A28F591C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8909,7 +8909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E94F2948-6B27-4080-A14D-E85369C74425}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{834A047F-31D6-4640-B35B-9D3CCC058B1A}">
   <dimension ref="B9:D298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12103,7 +12103,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17AC6F4C-6D18-44E7-B545-3049D697CEE0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FCA273F-045D-4586-9162-B8579E0F3A2C}">
   <dimension ref="B9:H298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76313C0E-F9D8-4317-ADD4-6594A28F591C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F1CE32E-D496-41D0-8300-034F54DA2D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8909,7 +8909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{834A047F-31D6-4640-B35B-9D3CCC058B1A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{202E54F5-5230-4C50-9681-2FD5176E15AF}">
   <dimension ref="B9:D298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12103,7 +12103,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FCA273F-045D-4586-9162-B8579E0F3A2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B1F5C36-881B-4B16-9A79-6869C0DD73BD}">
   <dimension ref="B9:H298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F1CE32E-D496-41D0-8300-034F54DA2D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBCDC7A7-04DA-44E7-B58F-E6F05C1FBC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8909,7 +8909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{202E54F5-5230-4C50-9681-2FD5176E15AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADD675D2-AA14-4F01-8AED-06214EB50F5B}">
   <dimension ref="B9:D298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12103,7 +12103,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B1F5C36-881B-4B16-9A79-6869C0DD73BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68B3DEE2-3C1A-454B-AC30-828BFD0ED024}">
   <dimension ref="B9:H298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBCDC7A7-04DA-44E7-B58F-E6F05C1FBC1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{056D8C02-35B9-486E-825B-D7B2C4F41F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8909,7 +8909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADD675D2-AA14-4F01-8AED-06214EB50F5B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF7FAEB-6820-40D9-B101-BD8B7581CA30}">
   <dimension ref="B9:D298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12103,7 +12103,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68B3DEE2-3C1A-454B-AC30-828BFD0ED024}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC59C412-4B03-4803-82FA-7A6C3AEB9103}">
   <dimension ref="B9:H298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{056D8C02-35B9-486E-825B-D7B2C4F41F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAD94377-F589-4B1D-9E95-2CD2D3DFF1DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8909,7 +8909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF7FAEB-6820-40D9-B101-BD8B7581CA30}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54EC1EBE-18D8-4CA2-A9E7-76ADD807784B}">
   <dimension ref="B9:D298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12103,7 +12103,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC59C412-4B03-4803-82FA-7A6C3AEB9103}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6119B78-7FDE-457E-9D12-1655FE671368}">
   <dimension ref="B9:H298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAD94377-F589-4B1D-9E95-2CD2D3DFF1DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{19C99289-F6F0-4345-BEC6-388A707BF84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8909,7 +8909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54EC1EBE-18D8-4CA2-A9E7-76ADD807784B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73DBB423-E931-42EF-B99D-F0737BDA7A74}">
   <dimension ref="B9:D298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12103,7 +12103,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6119B78-7FDE-457E-9D12-1655FE671368}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C026A83-A83B-4778-AF65-3A2ACC48880E}">
   <dimension ref="B9:H298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19C99289-F6F0-4345-BEC6-388A707BF84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D686C4B-FB33-4B7E-AF70-B329DCA54AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8909,7 +8909,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73DBB423-E931-42EF-B99D-F0737BDA7A74}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7523F016-93E2-4941-ADD6-49FB5FE9DC04}">
   <dimension ref="B9:D298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12103,7 +12103,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C026A83-A83B-4778-AF65-3A2ACC48880E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18EEE888-5AE2-4DCF-9407-E3BE274C768A}">
   <dimension ref="B9:H298"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D6A1F21-2FC7-4C39-A7E5-27D5DC179B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22D32B30-8BDB-40EF-9BD8-F45697871E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10798,7 +10798,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{604C02AB-779F-451A-990C-8C76AC3EC9FA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E5A02D-0A6E-4D9D-B320-AC22F7810936}">
   <dimension ref="B9:H303"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -16651,7 +16651,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6969C5F9-5309-4EE3-9C42-60437FC30FDB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27AC32A0-BF99-4AEB-A504-24630F825705}">
   <dimension ref="B9:L303"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22D32B30-8BDB-40EF-9BD8-F45697871E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995AC6B2-EBE1-47EF-8AF4-4E76290D0E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenMap_OLD" sheetId="70" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4067" uniqueCount="1349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4067" uniqueCount="1350">
   <si>
     <t>Unit</t>
   </si>
@@ -4131,6 +4131,9 @@
   </si>
   <si>
     <t>JPN-elc_wof_044</t>
+  </si>
+  <si>
+    <t>e[_]*</t>
   </si>
 </sst>
 </file>
@@ -25535,10 +25538,10 @@
         <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>400</v>
+        <v>1349</v>
       </c>
       <c r="G21" t="s">
-        <v>400</v>
+        <v>1349</v>
       </c>
       <c r="K21" t="s">
         <v>8</v>
@@ -25558,10 +25561,10 @@
         <v>36</v>
       </c>
       <c r="F22" t="s">
-        <v>400</v>
+        <v>1349</v>
       </c>
       <c r="G22" t="s">
-        <v>400</v>
+        <v>1349</v>
       </c>
       <c r="K22" t="s">
         <v>8</v>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55EB2509-8C71-402F-9CCE-D13BD35DBFC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7E52288-0F52-44B9-86A5-1F123A09065A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4056" uniqueCount="1348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4056" uniqueCount="1347">
   <si>
     <t>Unit</t>
   </si>
@@ -2358,9 +2358,6 @@
   </si>
   <si>
     <t>Akita</t>
-  </si>
-  <si>
-    <t>Kōchi</t>
   </si>
   <si>
     <t>region_com</t>
@@ -10795,36 +10792,36 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28C5103C-0EDA-474C-A7BB-D919FA5D2AAD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C094C7AC-79A3-4491-BBED-E672EA6B5667}">
   <dimension ref="B9:H302"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:8">
       <c r="B9" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="F9" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="10" spans="2:8">
       <c r="B10" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C10" t="s">
         <v>1053</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>1054</v>
       </c>
-      <c r="D10" t="s">
-        <v>1055</v>
-      </c>
       <c r="F10" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G10" t="s">
         <v>1053</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>1054</v>
-      </c>
-      <c r="H10" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="11" spans="2:8">
@@ -10838,7 +10835,7 @@
         <v>138.80177043536111</v>
       </c>
       <c r="F11" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G11">
         <v>36.623159551188849</v>
@@ -10858,7 +10855,7 @@
         <v>133.95401090047395</v>
       </c>
       <c r="F12" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="G12">
         <v>34.16492140881175</v>
@@ -10878,7 +10875,7 @@
         <v>133.86250228190178</v>
       </c>
       <c r="F13" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G13">
         <v>34.302173069560816</v>
@@ -10898,7 +10895,7 @@
         <v>141.02183643624105</v>
       </c>
       <c r="F14" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="G14">
         <v>37.316218892491598</v>
@@ -10918,7 +10915,7 @@
         <v>140.72295560659705</v>
       </c>
       <c r="F15" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G15">
         <v>37.141850931652939</v>
@@ -10938,7 +10935,7 @@
         <v>139.91772358683002</v>
       </c>
       <c r="F16" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="G16">
         <v>36.65527049556583</v>
@@ -10958,7 +10955,7 @@
         <v>140.45810292549854</v>
       </c>
       <c r="F17" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="G17">
         <v>35.865258454640866</v>
@@ -10978,7 +10975,7 @@
         <v>140.84893075302352</v>
       </c>
       <c r="F18" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="G18">
         <v>38.604776865796879</v>
@@ -10998,7 +10995,7 @@
         <v>140.96068542100087</v>
       </c>
       <c r="F19" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="G19">
         <v>37.359425564472978</v>
@@ -11018,7 +11015,7 @@
         <v>135.58694108806569</v>
       </c>
       <c r="F20" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="G20">
         <v>34.402512992032868</v>
@@ -11038,7 +11035,7 @@
         <v>135.50211531023922</v>
       </c>
       <c r="F21" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G21">
         <v>34.213923715840174</v>
@@ -11058,7 +11055,7 @@
         <v>135.3461014713138</v>
       </c>
       <c r="F22" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="G22">
         <v>34.984222780255479</v>
@@ -11078,7 +11075,7 @@
         <v>137.70854060707654</v>
       </c>
       <c r="F23" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="G23">
         <v>35.07143216942076</v>
@@ -11098,7 +11095,7 @@
         <v>139.4364465197805</v>
       </c>
       <c r="F24" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="G24">
         <v>35.962037835496112</v>
@@ -11118,7 +11115,7 @@
         <v>139.90353088187334</v>
       </c>
       <c r="F25" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G25">
         <v>36.167130274968521</v>
@@ -11138,7 +11135,7 @@
         <v>139.37072375217352</v>
       </c>
       <c r="F26" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="G26">
         <v>35.928728165249211</v>
@@ -11158,7 +11155,7 @@
         <v>139.23954260184681</v>
       </c>
       <c r="F27" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="G27">
         <v>35.851788162102174</v>
@@ -11178,7 +11175,7 @@
         <v>137.72908932599771</v>
       </c>
       <c r="F28" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="G28">
         <v>35.162272886797354</v>
@@ -11198,7 +11195,7 @@
         <v>139.22338930422998</v>
       </c>
       <c r="F29" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="G29">
         <v>35.71470374426972</v>
@@ -11218,7 +11215,7 @@
         <v>139.22566862063019</v>
       </c>
       <c r="F30" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="G30">
         <v>35.400444620287395</v>
@@ -11238,7 +11235,7 @@
         <v>138.79989115700727</v>
       </c>
       <c r="F31" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="G31">
         <v>35.590726684810875</v>
@@ -11258,7 +11255,7 @@
         <v>138.96317390902462</v>
       </c>
       <c r="F32" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G32">
         <v>35.372238518852974</v>
@@ -11278,7 +11275,7 @@
         <v>140.16653208165212</v>
       </c>
       <c r="F33" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="G33">
         <v>35.499051212291768</v>
@@ -11298,7 +11295,7 @@
         <v>140.9495383195725</v>
       </c>
       <c r="F34" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="G34">
         <v>37.535340448744797</v>
@@ -11318,7 +11315,7 @@
         <v>135.71481347221845</v>
       </c>
       <c r="F35" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="G35">
         <v>34.734669337370775</v>
@@ -11338,7 +11335,7 @@
         <v>135.89763769563652</v>
       </c>
       <c r="F36" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="G36">
         <v>34.865486852490449</v>
@@ -11358,7 +11355,7 @@
         <v>136.93748324308584</v>
       </c>
       <c r="F37" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="G37">
         <v>35.527092198043391</v>
@@ -11378,7 +11375,7 @@
         <v>140.06957983959583</v>
       </c>
       <c r="F38" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="G38">
         <v>35.781310478950395</v>
@@ -11398,7 +11395,7 @@
         <v>140.15286635448939</v>
       </c>
       <c r="F39" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="G39">
         <v>36.52251279266028</v>
@@ -11418,7 +11415,7 @@
         <v>139.83246221583255</v>
       </c>
       <c r="F40" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="G40">
         <v>36.712761848859408</v>
@@ -11438,7 +11435,7 @@
         <v>135.61912454072566</v>
       </c>
       <c r="F41" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G41">
         <v>34.96965036789733</v>
@@ -11458,7 +11455,7 @@
         <v>135.90243240056623</v>
       </c>
       <c r="F42" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G42">
         <v>34.448778413299458</v>
@@ -11478,7 +11475,7 @@
         <v>137.26239319012302</v>
       </c>
       <c r="F43" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="G43">
         <v>35.105965944995894</v>
@@ -11498,7 +11495,7 @@
         <v>136.82594005142843</v>
       </c>
       <c r="F44" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="G44">
         <v>36.499195713422203</v>
@@ -11518,7 +11515,7 @@
         <v>136.7170002183575</v>
       </c>
       <c r="F45" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="G45">
         <v>36.500393255821443</v>
@@ -11538,7 +11535,7 @@
         <v>135.64795104006993</v>
       </c>
       <c r="F46" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="G46">
         <v>34.5973116203552</v>
@@ -11558,7 +11555,7 @@
         <v>138.83246934123443</v>
       </c>
       <c r="F47" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="G47">
         <v>36.547838660667693</v>
@@ -11578,7 +11575,7 @@
         <v>137.45239068692709</v>
       </c>
       <c r="F48" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="G48">
         <v>34.890777361936721</v>
@@ -11598,7 +11595,7 @@
         <v>136.96265986651665</v>
       </c>
       <c r="F49" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G49">
         <v>35.635668447344635</v>
@@ -11618,7 +11615,7 @@
         <v>136.51456115331234</v>
       </c>
       <c r="F50" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="G50">
         <v>35.193003060430279</v>
@@ -11638,7 +11635,7 @@
         <v>136.45106186446196</v>
       </c>
       <c r="F51" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G51">
         <v>35.203342007191587</v>
@@ -11658,7 +11655,7 @@
         <v>136.29336601111871</v>
       </c>
       <c r="F52" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G52">
         <v>35.095109605490656</v>
@@ -11678,7 +11675,7 @@
         <v>135.11013357438321</v>
       </c>
       <c r="F53" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="G53">
         <v>34.931631944821412</v>
@@ -11698,7 +11695,7 @@
         <v>137.29809780148221</v>
       </c>
       <c r="F54" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="G54">
         <v>35.210233689303443</v>
@@ -11718,7 +11715,7 @@
         <v>132.70939419496085</v>
       </c>
       <c r="F55" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="G55">
         <v>34.488899953033631</v>
@@ -11738,7 +11735,7 @@
         <v>133.39500139141035</v>
       </c>
       <c r="F56" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="G56">
         <v>33.944279016269924</v>
@@ -11758,7 +11755,7 @@
         <v>130.62404746626811</v>
       </c>
       <c r="F57" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G57">
         <v>33.491618269579163</v>
@@ -11778,7 +11775,7 @@
         <v>130.36472007060911</v>
       </c>
       <c r="F58" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G58">
         <v>33.470083483004061</v>
@@ -11798,7 +11795,7 @@
         <v>132.92821331235666</v>
       </c>
       <c r="F59" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G59">
         <v>33.79201549752927</v>
@@ -11818,7 +11815,7 @@
         <v>141.17616155822515</v>
       </c>
       <c r="F60" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="G60">
         <v>39.90505248701556</v>
@@ -11838,7 +11835,7 @@
         <v>129.92909232659014</v>
       </c>
       <c r="F61" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G61">
         <v>33.350251889794762</v>
@@ -11858,7 +11855,7 @@
         <v>129.83491441267549</v>
       </c>
       <c r="F62" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G62">
         <v>33.515582068392803</v>
@@ -11878,7 +11875,7 @@
         <v>130.80444891114544</v>
       </c>
       <c r="F63" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G63">
         <v>33.809905742139442</v>
@@ -11898,7 +11895,7 @@
         <v>136.72358330816681</v>
       </c>
       <c r="F64" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G64">
         <v>35.584257599900546</v>
@@ -11918,7 +11915,7 @@
         <v>132.25764638741936</v>
       </c>
       <c r="F65" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="G65">
         <v>34.412363937355089</v>
@@ -11938,7 +11935,7 @@
         <v>138.93642749968816</v>
       </c>
       <c r="F66" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="G66">
         <v>36.031277392158273</v>
@@ -11958,7 +11955,7 @@
         <v>131.01563614443441</v>
       </c>
       <c r="F67" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G67">
         <v>33.607991608822481</v>
@@ -11978,7 +11975,7 @@
         <v>131.0932403187953</v>
       </c>
       <c r="F68" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="G68">
         <v>34.163080826303833</v>
@@ -11998,7 +11995,7 @@
         <v>137.99699148650129</v>
       </c>
       <c r="F69" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="G69">
         <v>35.710010548181799</v>
@@ -12018,7 +12015,7 @@
         <v>137.98740065939847</v>
       </c>
       <c r="F70" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="G70">
         <v>36.063822401692441</v>
@@ -12038,7 +12035,7 @@
         <v>138.06316947909724</v>
       </c>
       <c r="F71" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="G71">
         <v>34.808204237724084</v>
@@ -12058,7 +12055,7 @@
         <v>139.98010146039354</v>
       </c>
       <c r="F72" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="G72">
         <v>35.463760116184766</v>
@@ -12078,7 +12075,7 @@
         <v>130.65571883093563</v>
       </c>
       <c r="F73" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="G73">
         <v>31.957566960028267</v>
@@ -12098,7 +12095,7 @@
         <v>130.79932246595934</v>
       </c>
       <c r="F74" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G74">
         <v>32.614196415120603</v>
@@ -12118,7 +12115,7 @@
         <v>131.72943865137833</v>
       </c>
       <c r="F75" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="G75">
         <v>33.13401562004119</v>
@@ -12138,7 +12135,7 @@
         <v>131.38565953692876</v>
       </c>
       <c r="F76" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G76">
         <v>32.250790927091856</v>
@@ -12158,7 +12155,7 @@
         <v>131.1942495227193</v>
       </c>
       <c r="F77" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G77">
         <v>31.921816379278063</v>
@@ -12178,7 +12175,7 @@
         <v>134.6016239057528</v>
       </c>
       <c r="F78" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="G78">
         <v>35.063269231517701</v>
@@ -12198,7 +12195,7 @@
         <v>134.02522903294857</v>
       </c>
       <c r="F79" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="G79">
         <v>34.887992263344749</v>
@@ -12218,7 +12215,7 @@
         <v>134.42591403567502</v>
       </c>
       <c r="F80" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="G80">
         <v>34.861843414722763</v>
@@ -12238,7 +12235,7 @@
         <v>133.38849243239446</v>
       </c>
       <c r="F81" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G81">
         <v>34.803558863629867</v>
@@ -12258,7 +12255,7 @@
         <v>133.40586917675526</v>
       </c>
       <c r="F82" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="G82">
         <v>35.295973542322862</v>
@@ -12278,7 +12275,7 @@
         <v>133.78319068983876</v>
       </c>
       <c r="F83" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G83">
         <v>34.457906539847727</v>
@@ -12298,7 +12295,7 @@
         <v>131.82627354738659</v>
       </c>
       <c r="F84" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G84">
         <v>34.200093958841528</v>
@@ -12318,7 +12315,7 @@
         <v>139.22353939760555</v>
       </c>
       <c r="F85" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G85">
         <v>36.57931508910017</v>
@@ -12338,7 +12335,7 @@
         <v>140.80525197784883</v>
       </c>
       <c r="F86" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="G86">
         <v>37.381807329228366</v>
@@ -12358,7 +12355,7 @@
         <v>135.33715318384688</v>
       </c>
       <c r="F87" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G87">
         <v>34.211616497136646</v>
@@ -12378,7 +12375,7 @@
         <v>134.40861283503324</v>
       </c>
       <c r="F88" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="G88">
         <v>34.000763351330342</v>
@@ -12398,7 +12395,7 @@
         <v>139.21300372758429</v>
       </c>
       <c r="F89" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G89">
         <v>36.219906325405837</v>
@@ -12418,7 +12415,7 @@
         <v>139.83661319523603</v>
       </c>
       <c r="F90" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G90">
         <v>35.343898881203259</v>
@@ -12438,7 +12435,7 @@
         <v>140.02788035567903</v>
       </c>
       <c r="F91" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="G91">
         <v>35.343352324848951</v>
@@ -12458,7 +12455,7 @@
         <v>136.41546992363067</v>
       </c>
       <c r="F92" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G92">
         <v>35.996020957962997</v>
@@ -12478,7 +12475,7 @@
         <v>137.88397061557541</v>
       </c>
       <c r="F93" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="G93">
         <v>36.137503274067335</v>
@@ -12498,7 +12495,7 @@
         <v>131.97979992173993</v>
       </c>
       <c r="F94" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="G94">
         <v>34.697486518391401</v>
@@ -12518,7 +12515,7 @@
         <v>133.11610242421423</v>
       </c>
       <c r="F95" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="G95">
         <v>35.470241157388045</v>
@@ -12538,7 +12535,7 @@
         <v>135.48469961836187</v>
       </c>
       <c r="F96" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G96">
         <v>34.990387052647066</v>
@@ -12558,7 +12555,7 @@
         <v>130.90270499954008</v>
       </c>
       <c r="F97" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="G97">
         <v>32.909226897681798</v>
@@ -12578,7 +12575,7 @@
         <v>135.64462162700926</v>
       </c>
       <c r="F98" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="G98">
         <v>35.136785367773712</v>
@@ -12598,7 +12595,7 @@
         <v>138.04906886461768</v>
       </c>
       <c r="F99" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="G99">
         <v>34.863332048008239</v>
@@ -12618,7 +12615,7 @@
         <v>139.30483820209852</v>
       </c>
       <c r="F100" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G100">
         <v>36.326085164714421</v>
@@ -12638,7 +12635,7 @@
         <v>140.64403184405094</v>
       </c>
       <c r="F101" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G101">
         <v>38.254801587089091</v>
@@ -12658,7 +12655,7 @@
         <v>141.17318529712139</v>
       </c>
       <c r="F102" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="G102">
         <v>40.78296544539743</v>
@@ -12678,7 +12675,7 @@
         <v>134.63656431903473</v>
       </c>
       <c r="F103" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="G103">
         <v>33.827824780612865</v>
@@ -12698,7 +12695,7 @@
         <v>140.75152492552408</v>
       </c>
       <c r="F104" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="G104">
         <v>38.352304032247361</v>
@@ -12718,7 +12715,7 @@
         <v>136.6608688257156</v>
       </c>
       <c r="F105" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G105">
         <v>35.735051436097457</v>
@@ -12738,7 +12735,7 @@
         <v>140.94904314929377</v>
       </c>
       <c r="F106" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G106">
         <v>37.85105814374495</v>
@@ -12758,7 +12755,7 @@
         <v>140.94113293098712</v>
       </c>
       <c r="F107" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G107">
         <v>37.844730745516557</v>
@@ -12778,7 +12775,7 @@
         <v>136.02064253754861</v>
       </c>
       <c r="F108" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="G108">
         <v>35.751901182366495</v>
@@ -12798,7 +12795,7 @@
         <v>137.05971491227285</v>
       </c>
       <c r="F109" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="G109">
         <v>36.070189422281686</v>
@@ -12818,7 +12815,7 @@
         <v>141.38653983141012</v>
       </c>
       <c r="F110" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="G110">
         <v>41.187613246344768</v>
@@ -12838,7 +12835,7 @@
         <v>139.90848727441983</v>
       </c>
       <c r="F111" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="G111">
         <v>37.344902507375927</v>
@@ -12858,7 +12855,7 @@
         <v>132.31197455192955</v>
       </c>
       <c r="F112" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="G112">
         <v>33.488989843085079</v>
@@ -12878,7 +12875,7 @@
         <v>135.15440900189861</v>
       </c>
       <c r="F113" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="G113">
         <v>33.860371739222863</v>
@@ -12898,7 +12895,7 @@
         <v>135.82246848008975</v>
       </c>
       <c r="F114" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="G114">
         <v>34.112988242957435</v>
@@ -12918,7 +12915,7 @@
         <v>139.79080912025844</v>
       </c>
       <c r="F115" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G115">
         <v>35.647882725800528</v>
@@ -12938,7 +12935,7 @@
         <v>135.9722405327953</v>
       </c>
       <c r="F116" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G116">
         <v>35.556434741181334</v>
@@ -12958,7 +12955,7 @@
         <v>135.26635354845138</v>
       </c>
       <c r="F117" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="G117">
         <v>35.351099606986459</v>
@@ -12978,7 +12975,7 @@
         <v>139.91058845823864</v>
       </c>
       <c r="F118" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="G118">
         <v>35.930809236247349</v>
@@ -12998,7 +12995,7 @@
         <v>139.83263097329305</v>
       </c>
       <c r="F119" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="G119">
         <v>36.106697327015418</v>
@@ -13018,7 +13015,7 @@
         <v>136.83804195925802</v>
       </c>
       <c r="F120" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="G120">
         <v>36.995998879309816</v>
@@ -13038,7 +13035,7 @@
         <v>138.59820514421614</v>
       </c>
       <c r="F121" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G121">
         <v>37.425338985543583</v>
@@ -13058,7 +13055,7 @@
         <v>138.74669119999999</v>
       </c>
       <c r="F122" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G122">
         <v>36.833393683160601</v>
@@ -13078,7 +13075,7 @@
         <v>138.74501577195321</v>
       </c>
       <c r="F123" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G123">
         <v>36.622841071131219</v>
@@ -13098,7 +13095,7 @@
         <v>139.38204658642061</v>
       </c>
       <c r="F124" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G124">
         <v>37.025403708186893</v>
@@ -13118,7 +13115,7 @@
         <v>141.00975359999998</v>
       </c>
       <c r="F125" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G125">
         <v>37.381484291677808</v>
@@ -13138,7 +13135,7 @@
         <v>138.9077149736554</v>
       </c>
       <c r="F126" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G126">
         <v>36.371120610978807</v>
@@ -13158,7 +13155,7 @@
         <v>135.91735309240229</v>
       </c>
       <c r="F127" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="G127">
         <v>37.237118883574631</v>
@@ -13178,7 +13175,7 @@
         <v>135.65658974924909</v>
       </c>
       <c r="F128" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="G128">
         <v>35.708267733884668</v>
@@ -13198,7 +13195,7 @@
         <v>136.29851369999997</v>
       </c>
       <c r="F129" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="G129">
         <v>34.838968568013591</v>
@@ -13218,7 +13215,7 @@
         <v>136.43987240000001</v>
       </c>
       <c r="F130" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="G130">
         <v>35.539462784211032</v>
@@ -13238,7 +13235,7 @@
         <v>136.1105518</v>
       </c>
       <c r="F131" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="G131">
         <v>35.10344718137253</v>
@@ -13258,7 +13255,7 @@
         <v>135.09373984404087</v>
       </c>
       <c r="F132" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="G132">
         <v>35.202859981475441</v>
@@ -13278,7 +13275,7 @@
         <v>132.99172771294303</v>
       </c>
       <c r="F133" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="G133">
         <v>35.515618181799375</v>
@@ -13298,7 +13295,7 @@
         <v>140.02967839999999</v>
       </c>
       <c r="F134" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="G134">
         <v>34.961593435279937</v>
@@ -13318,7 +13315,7 @@
         <v>129.68433039999996</v>
       </c>
       <c r="F135" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="G135">
         <v>35.53899968060265</v>
@@ -13338,7 +13335,7 @@
         <v>140.75025629999996</v>
       </c>
       <c r="F136" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="G136">
         <v>35.315672781592291</v>
@@ -13358,7 +13355,7 @@
         <v>129.9236435</v>
       </c>
       <c r="F137" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="G137">
         <v>33.348565879568348</v>
@@ -13378,7 +13375,7 @@
         <v>136.65407619999999</v>
       </c>
       <c r="F138" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="G138">
         <v>37.842662384191179</v>
@@ -13398,7 +13395,7 @@
         <v>136.6633563</v>
       </c>
       <c r="F139" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G139">
         <v>33.393767779614286</v>
@@ -13418,7 +13415,7 @@
         <v>136.65658429999999</v>
       </c>
       <c r="F140" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="G140">
         <v>35.675360981964779</v>
@@ -13438,7 +13435,7 @@
         <v>136.6639787</v>
       </c>
       <c r="F141" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="G141">
         <v>35.633574681921566</v>
@@ -13458,7 +13455,7 @@
         <v>140.91210482362231</v>
       </c>
       <c r="F142" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="G142">
         <v>35.650100581938673</v>
@@ -13478,7 +13475,7 @@
         <v>130.0443314</v>
       </c>
       <c r="F143" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G143">
         <v>35.706360981996944</v>
@@ -13498,7 +13495,7 @@
         <v>130.0722404</v>
       </c>
       <c r="F144" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="G144">
         <v>41.508651564773203</v>
@@ -13518,7 +13515,7 @@
         <v>139.82014500000002</v>
       </c>
       <c r="F145" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="G145">
         <v>32.484738478698453</v>
@@ -13538,7 +13535,7 @@
         <v>139.66736009999997</v>
       </c>
       <c r="F146" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="G146">
         <v>32.465651478679419</v>
@@ -13558,7 +13555,7 @@
         <v>139.67164638616484</v>
       </c>
       <c r="F147" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="G147">
         <v>36.716571783040472</v>
@@ -13578,7 +13575,7 @@
         <v>134.14717879997406</v>
       </c>
       <c r="F148" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="G148">
         <v>37.012263983344255</v>
@@ -13598,7 +13595,7 @@
         <v>134.18795782269976</v>
       </c>
       <c r="F149" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="G149">
         <v>36.831030068493966</v>
@@ -13618,7 +13615,7 @@
         <v>141.1459764</v>
       </c>
       <c r="F150" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="G150">
         <v>34.656600980925262</v>
@@ -13638,7 +13635,7 @@
         <v>136.85355660000005</v>
       </c>
       <c r="F151" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="G151">
         <v>35.208514496067693</v>
@@ -13658,7 +13655,7 @@
         <v>139.86426240000003</v>
       </c>
       <c r="F152" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="G152">
         <v>40.755782887038599</v>
@@ -13678,7 +13675,7 @@
         <v>138.76684369999998</v>
       </c>
       <c r="F153" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="G153">
         <v>36.459874082775926</v>
@@ -13698,7 +13695,7 @@
         <v>135.97127599999999</v>
       </c>
       <c r="F154" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="G154">
         <v>36.993515983324997</v>
@@ -13718,7 +13715,7 @@
         <v>135.98637149999996</v>
       </c>
       <c r="F155" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="G155">
         <v>36.845897183173513</v>
@@ -13738,7 +13735,7 @@
         <v>135.31301980000001</v>
       </c>
       <c r="F156" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="G156">
         <v>35.539115781823647</v>
@@ -13758,7 +13755,7 @@
         <v>135.36116000000004</v>
       </c>
       <c r="F157" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="G157">
         <v>35.533805881818225</v>
@@ -13778,7 +13775,7 @@
         <v>135.50414703991692</v>
       </c>
       <c r="F158" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="G158">
         <v>35.283431681558874</v>
@@ -13798,7 +13795,7 @@
         <v>135.46966040000004</v>
       </c>
       <c r="F159" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="G159">
         <v>35.08315948135143</v>
@@ -13818,7 +13815,7 @@
         <v>134.65037140000004</v>
       </c>
       <c r="F160" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="G160">
         <v>35.52070181861027</v>
@@ -13838,7 +13835,7 @@
         <v>138.70539420000003</v>
       </c>
       <c r="F161" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="G161">
         <v>35.48131578176384</v>
@@ -13858,7 +13855,7 @@
         <v>134.71815123527378</v>
       </c>
       <c r="F162" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="G162">
         <v>33.860734580091119</v>
@@ -13878,7 +13875,7 @@
         <v>138.14599129416126</v>
       </c>
       <c r="F163" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="G163">
         <v>36.033951482335901</v>
@@ -13898,7 +13895,7 @@
         <v>131.35489939999999</v>
       </c>
       <c r="F164" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="G164">
         <v>35.128425766214498</v>
@@ -13918,7 +13915,7 @@
         <v>137.04902529999998</v>
       </c>
       <c r="F165" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="G165">
         <v>34.624290259299336</v>
@@ -13938,7 +13935,7 @@
         <v>134.85631707609716</v>
       </c>
       <c r="F166" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="G166">
         <v>32.318128478532813</v>
@@ -13958,7 +13955,7 @@
         <v>138.96215179999999</v>
       </c>
       <c r="F167" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G167">
         <v>36.079947782383513</v>
@@ -13978,7 +13975,7 @@
         <v>138.94781469999998</v>
       </c>
       <c r="F168" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G168">
         <v>35.236783699163318</v>
@@ -13998,7 +13995,7 @@
         <v>135.1978422</v>
       </c>
       <c r="F169" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="G169">
         <v>36.527150382845349</v>
@@ -14018,7 +14015,7 @@
         <v>134.56571169999998</v>
       </c>
       <c r="F170" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="G170">
         <v>36.531049382849403</v>
@@ -14038,7 +14035,7 @@
         <v>130.18954854445479</v>
       </c>
       <c r="F171" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="G171">
         <v>33.860709380091059</v>
@@ -14058,7 +14055,7 @@
         <v>136.7293475498264</v>
       </c>
       <c r="F172" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="G172">
         <v>34.973205081237758</v>
@@ -14078,7 +14075,7 @@
         <v>139.9691358</v>
       </c>
       <c r="F173" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="G173">
         <v>31.831554494509291</v>
@@ -14098,7 +14095,7 @@
         <v>139.95336681437402</v>
       </c>
       <c r="F174" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="G174">
         <v>37.06119413998394</v>
@@ -14118,7 +14115,7 @@
         <v>139.92874660000001</v>
       </c>
       <c r="F175" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G175">
         <v>35.690483081980481</v>
@@ -14138,7 +14135,7 @@
         <v>139.88276669999999</v>
       </c>
       <c r="F176" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="G176">
         <v>35.691145203332042</v>
@@ -14158,7 +14155,7 @@
         <v>139.8673253</v>
       </c>
       <c r="F177" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="G177">
         <v>35.673833481963186</v>
@@ -14178,7 +14175,7 @@
         <v>139.85114659999999</v>
       </c>
       <c r="F178" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="G178">
         <v>35.637957981926078</v>
@@ -14198,7 +14195,7 @@
         <v>139.84061359999998</v>
       </c>
       <c r="F179" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="G179">
         <v>35.643357481931645</v>
@@ -14218,7 +14215,7 @@
         <v>139.80703298771471</v>
       </c>
       <c r="F180" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="G180">
         <v>35.647114881935543</v>
@@ -14238,7 +14235,7 @@
         <v>135.34489300000001</v>
       </c>
       <c r="F181" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="G181">
         <v>35.647820481936307</v>
@@ -14258,7 +14255,7 @@
         <v>138.62571410000004</v>
       </c>
       <c r="F182" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="G182">
         <v>35.642827600842622</v>
@@ -14278,7 +14275,7 @@
         <v>141.45121793661826</v>
       </c>
       <c r="F183" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="G183">
         <v>36.579104053018241</v>
@@ -14298,7 +14295,7 @@
         <v>140.58515938711835</v>
       </c>
       <c r="F184" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="G184">
         <v>35.590406542941842</v>
@@ -14318,7 +14315,7 @@
         <v>141.03539173232843</v>
       </c>
       <c r="F185" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="G185">
         <v>35.524235781808308</v>
@@ -14338,7 +14335,7 @@
         <v>141.05492399999997</v>
       </c>
       <c r="F186" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="G186">
         <v>36.081367082384993</v>
@@ -14358,7 +14355,7 @@
         <v>141.2221878926961</v>
       </c>
       <c r="F187" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="G187">
         <v>37.025086041614799</v>
@@ -14378,7 +14375,7 @@
         <v>140.60642612495218</v>
       </c>
       <c r="F188" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G188">
         <v>43.234266159817281</v>
@@ -14398,7 +14395,7 @@
         <v>141.80450293753924</v>
       </c>
       <c r="F189" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="G189">
         <v>41.916289110672011</v>
@@ -14418,7 +14415,7 @@
         <v>141.78185613570739</v>
       </c>
       <c r="F190" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="G190">
         <v>42.749349494630721</v>
@@ -14438,7 +14435,7 @@
         <v>140.5164523543362</v>
       </c>
       <c r="F191" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="G191">
         <v>43.103426189125337</v>
@@ -14458,7 +14455,7 @@
         <v>141.1341659</v>
       </c>
       <c r="F192" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="G192">
         <v>43.058029756113321</v>
@@ -14472,13 +14469,13 @@
         <v>606</v>
       </c>
       <c r="C193">
-        <v>28.403760866267952</v>
+        <v>28.263927362997119</v>
       </c>
       <c r="D193">
-        <v>129.62425485007154</v>
+        <v>129.33184438251254</v>
       </c>
       <c r="F193" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="G193">
         <v>41.888040971612753</v>
@@ -14492,13 +14489,13 @@
         <v>607</v>
       </c>
       <c r="C194">
-        <v>26.437121286940336</v>
+        <v>26.853629519883636</v>
       </c>
       <c r="D194">
-        <v>127.94749044991164</v>
+        <v>127.98617033570848</v>
       </c>
       <c r="F194" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="G194">
         <v>42.612540162775971</v>
@@ -14512,13 +14509,13 @@
         <v>608</v>
       </c>
       <c r="C195">
-        <v>33.435019454413229</v>
+        <v>33.659849545344365</v>
       </c>
       <c r="D195">
-        <v>129.82525819967407</v>
+        <v>129.68428282334222</v>
       </c>
       <c r="F195" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="G195">
         <v>42.714095832936565</v>
@@ -14532,13 +14529,13 @@
         <v>609</v>
       </c>
       <c r="C196">
-        <v>31.186718545101872</v>
+        <v>30.737058363239601</v>
       </c>
       <c r="D196">
-        <v>130.81208583399706</v>
+        <v>130.61472030713247</v>
       </c>
       <c r="F196" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="G196">
         <v>43.039701541285162</v>
@@ -14552,13 +14549,13 @@
         <v>610</v>
       </c>
       <c r="C197">
-        <v>32.535699090688681</v>
+        <v>32.431931356412775</v>
       </c>
       <c r="D197">
-        <v>130.81208583399706</v>
+        <v>130.39458183486042</v>
       </c>
       <c r="F197" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="G197">
         <v>43.054394789084093</v>
@@ -14572,19 +14569,19 @@
         <v>611</v>
       </c>
       <c r="C198">
-        <v>35.087966156787431</v>
+        <v>35.233660181862305</v>
       </c>
       <c r="D198">
-        <v>137.14688624260751</v>
+        <v>137.47317236567724</v>
       </c>
       <c r="F198" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="G198">
-        <v>28.403760866267952</v>
+        <v>28.263927362997119</v>
       </c>
       <c r="H198">
-        <v>129.62425485007154</v>
+        <v>129.33184438251254</v>
       </c>
     </row>
     <row r="199" spans="2:8">
@@ -14592,19 +14589,19 @@
         <v>612</v>
       </c>
       <c r="C199">
-        <v>34.707949188537874</v>
+        <v>34.334339818137757</v>
       </c>
       <c r="D199">
-        <v>135.24391188699428</v>
+        <v>135.14067068455017</v>
       </c>
       <c r="F199" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="G199">
-        <v>26.437121286940336</v>
+        <v>26.853629519883636</v>
       </c>
       <c r="H199">
-        <v>127.94749044991164</v>
+        <v>127.98617033570848</v>
       </c>
     </row>
     <row r="200" spans="2:8">
@@ -14612,19 +14609,19 @@
         <v>613</v>
       </c>
       <c r="C200">
-        <v>31.938760417794487</v>
+        <v>35.458490272793441</v>
       </c>
       <c r="D200">
-        <v>131.3068894775561</v>
+        <v>134.51268946270827</v>
       </c>
       <c r="F200" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="G200">
-        <v>33.435019454413229</v>
+        <v>33.659849545344365</v>
       </c>
       <c r="H200">
-        <v>129.82525819967407</v>
+        <v>129.68428282334222</v>
       </c>
     </row>
     <row r="201" spans="2:8">
@@ -14632,19 +14629,19 @@
         <v>614</v>
       </c>
       <c r="C201">
-        <v>33.214877451158252</v>
+        <v>34.933886727287465</v>
       </c>
       <c r="D201">
-        <v>131.85800087797219</v>
+        <v>132.6212698302559</v>
       </c>
       <c r="F201" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="G201">
-        <v>31.186718545101872</v>
+        <v>30.737058363239601</v>
       </c>
       <c r="H201">
-        <v>130.81208583399706</v>
+        <v>130.61472030713247</v>
       </c>
     </row>
     <row r="202" spans="2:8">
@@ -14652,19 +14649,19 @@
         <v>615</v>
       </c>
       <c r="C202">
-        <v>34.473438915726867</v>
+        <v>31.546446690591694</v>
       </c>
       <c r="D202">
-        <v>132.44984778916526</v>
+        <v>131.40418241459082</v>
       </c>
       <c r="F202" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="G202">
-        <v>32.535699090688681</v>
+        <v>32.431931356412775</v>
       </c>
       <c r="H202">
-        <v>130.81208583399706</v>
+        <v>130.39458183486042</v>
       </c>
     </row>
     <row r="203" spans="2:8">
@@ -14672,19 +14669,19 @@
         <v>616</v>
       </c>
       <c r="C203">
-        <v>35.308061608240791</v>
+        <v>33.340354152968537</v>
       </c>
       <c r="D203">
-        <v>133.79022259650586</v>
+        <v>132.3962038785682</v>
       </c>
       <c r="F203" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="G203">
-        <v>35.087966156787431</v>
+        <v>35.233660181862305</v>
       </c>
       <c r="H203">
-        <v>137.14688624260751</v>
+        <v>137.47317236567724</v>
       </c>
     </row>
     <row r="204" spans="2:8">
@@ -14692,19 +14689,19 @@
         <v>617</v>
       </c>
       <c r="C204">
-        <v>43.824758326357014</v>
+        <v>43.969915143757859</v>
       </c>
       <c r="D204">
-        <v>144.24247770518093</v>
+        <v>144.34572196185522</v>
       </c>
       <c r="F204" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="G204">
-        <v>34.707949188537874</v>
+        <v>34.334339818137757</v>
       </c>
       <c r="H204">
-        <v>135.24391188699428</v>
+        <v>135.14067068455017</v>
       </c>
     </row>
     <row r="205" spans="2:8">
@@ -14712,19 +14709,19 @@
         <v>618</v>
       </c>
       <c r="C205">
-        <v>43.29039933952194</v>
+        <v>43.147679382638273</v>
       </c>
       <c r="D205">
-        <v>144.83899676653832</v>
+        <v>145.02240376824813</v>
       </c>
       <c r="F205" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="G205">
-        <v>31.938760417794487</v>
+        <v>35.458490272793441</v>
       </c>
       <c r="H205">
-        <v>131.3068894775561</v>
+        <v>134.51268946270827</v>
       </c>
     </row>
     <row r="206" spans="2:8">
@@ -14732,19 +14729,19 @@
         <v>619</v>
       </c>
       <c r="C206">
-        <v>42.904367131388497</v>
+        <v>42.877883273520922</v>
       </c>
       <c r="D206">
-        <v>143.43877200055002</v>
+        <v>143.64084508019593</v>
       </c>
       <c r="F206" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="G206">
-        <v>33.214877451158252</v>
+        <v>34.933886727287465</v>
       </c>
       <c r="H206">
-        <v>131.85800087797219</v>
+        <v>132.6212698302559</v>
       </c>
     </row>
     <row r="207" spans="2:8">
@@ -14752,19 +14749,19 @@
         <v>620</v>
       </c>
       <c r="C207">
-        <v>44.02764494294621</v>
+        <v>44.09838948143279</v>
       </c>
       <c r="D207">
-        <v>141.98230705528843</v>
+        <v>141.66718981154995</v>
       </c>
       <c r="F207" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="G207">
-        <v>34.473438915726867</v>
+        <v>31.546446690591694</v>
       </c>
       <c r="H207">
-        <v>132.44984778916526</v>
+        <v>131.40418241459082</v>
       </c>
     </row>
     <row r="208" spans="2:8">
@@ -14772,19 +14769,19 @@
         <v>621</v>
       </c>
       <c r="C208">
-        <v>44.866389962657003</v>
+        <v>44.776448485828283</v>
       </c>
       <c r="D208">
-        <v>142.2268015903324</v>
+        <v>142.37989865856099</v>
       </c>
       <c r="F208" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="G208">
-        <v>35.308061608240791</v>
+        <v>33.340354152968537</v>
       </c>
       <c r="H208">
-        <v>133.79022259650586</v>
+        <v>132.3962038785682</v>
       </c>
     </row>
     <row r="209" spans="2:8">
@@ -14792,19 +14789,19 @@
         <v>622</v>
       </c>
       <c r="C209">
-        <v>42.952035290389645</v>
+        <v>43.05774734626582</v>
       </c>
       <c r="D209">
-        <v>140.85749327909829</v>
+        <v>140.77904494065928</v>
       </c>
       <c r="F209" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="G209">
-        <v>43.824758326357014</v>
+        <v>43.969915143757859</v>
       </c>
       <c r="H209">
-        <v>144.24247770518093</v>
+        <v>144.34572196185522</v>
       </c>
     </row>
     <row r="210" spans="2:8">
@@ -14812,19 +14809,19 @@
         <v>623</v>
       </c>
       <c r="C210">
-        <v>42.428223091658637</v>
+        <v>42.178411879512936</v>
       </c>
       <c r="D210">
-        <v>140.18694836006549</v>
+        <v>140.29659587499023</v>
       </c>
       <c r="F210" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="G210">
-        <v>43.29039933952194</v>
+        <v>43.147679382638273</v>
       </c>
       <c r="H210">
-        <v>144.83899676653832</v>
+        <v>145.02240376824813</v>
       </c>
     </row>
     <row r="211" spans="2:8">
@@ -14832,19 +14829,19 @@
         <v>624</v>
       </c>
       <c r="C211">
-        <v>42.439170214390096</v>
+        <v>42.353279728014932</v>
       </c>
       <c r="D211">
-        <v>142.27918947110257</v>
+        <v>142.48954617348576</v>
       </c>
       <c r="F211" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G211">
-        <v>42.904367131388497</v>
+        <v>42.877883273520922</v>
       </c>
       <c r="H211">
-        <v>143.43877200055002</v>
+        <v>143.64084508019593</v>
       </c>
     </row>
     <row r="212" spans="2:8">
@@ -14852,19 +14849,19 @@
         <v>625</v>
       </c>
       <c r="C212">
-        <v>43.158509213102896</v>
+        <v>43.327543455383179</v>
       </c>
       <c r="D212">
-        <v>142.00528620895545</v>
+        <v>142.4073105372922</v>
       </c>
       <c r="F212" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="G212">
-        <v>44.02764494294621</v>
+        <v>44.09838948143279</v>
       </c>
       <c r="H212">
-        <v>141.98230705528843</v>
+        <v>141.66718981154995</v>
       </c>
     </row>
     <row r="213" spans="2:8">
@@ -14872,19 +14869,19 @@
         <v>626</v>
       </c>
       <c r="C213">
-        <v>35.516357497927203</v>
+        <v>34.896415045465609</v>
       </c>
       <c r="D213">
-        <v>139.66018408801415</v>
+        <v>139.44682763432323</v>
       </c>
       <c r="F213" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="G213">
-        <v>44.866389962657003</v>
+        <v>44.776448485828283</v>
       </c>
       <c r="H213">
-        <v>142.2268015903324</v>
+        <v>142.37989865856099</v>
       </c>
     </row>
     <row r="214" spans="2:8">
@@ -14892,19 +14889,19 @@
         <v>627</v>
       </c>
       <c r="C214">
-        <v>36.19147631712201</v>
+        <v>36.357810636517982</v>
       </c>
       <c r="D214">
-        <v>140.30754342094826</v>
+        <v>140.55700872293659</v>
       </c>
       <c r="F214" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="G214">
-        <v>42.952035290389645</v>
+        <v>43.05774734626582</v>
       </c>
       <c r="H214">
-        <v>140.85749327909829</v>
+        <v>140.77904494065928</v>
       </c>
     </row>
     <row r="215" spans="2:8">
@@ -14912,19 +14909,19 @@
         <v>628</v>
       </c>
       <c r="C215">
-        <v>36.348454276526617</v>
+        <v>36.492708691076665</v>
       </c>
       <c r="D215">
-        <v>139.60657015788613</v>
+        <v>139.29880348917476</v>
       </c>
       <c r="F215" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="G215">
-        <v>42.428223091658637</v>
+        <v>42.178411879512936</v>
       </c>
       <c r="H215">
-        <v>140.18694836006549</v>
+        <v>140.29659587499023</v>
       </c>
     </row>
     <row r="216" spans="2:8">
@@ -14932,19 +14929,19 @@
         <v>629</v>
       </c>
       <c r="C216">
-        <v>37.989078017834409</v>
+        <v>38.060095610710867</v>
       </c>
       <c r="D216">
-        <v>139.39537508870831</v>
+        <v>139.23536456982546</v>
       </c>
       <c r="F216" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="G216">
-        <v>42.439170214390096</v>
+        <v>42.353279728014932</v>
       </c>
       <c r="H216">
-        <v>142.27918947110257</v>
+        <v>142.48954617348576</v>
       </c>
     </row>
     <row r="217" spans="2:8">
@@ -14952,19 +14949,19 @@
         <v>630</v>
       </c>
       <c r="C217">
-        <v>37.48200393492224</v>
+        <v>37.63184781846109</v>
       </c>
       <c r="D217">
-        <v>137.13221205726239</v>
+        <v>136.89752291232216</v>
       </c>
       <c r="F217" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="G217">
-        <v>43.158509213102896</v>
+        <v>43.327543455383179</v>
       </c>
       <c r="H217">
-        <v>142.00528620895545</v>
+        <v>142.4073105372922</v>
       </c>
     </row>
     <row r="218" spans="2:8">
@@ -14972,19 +14969,19 @@
         <v>631</v>
       </c>
       <c r="C218">
-        <v>36.611672842337725</v>
+        <v>36.522686036534161</v>
       </c>
       <c r="D218">
-        <v>137.08456152283767</v>
+        <v>137.12778269366422</v>
       </c>
       <c r="F218" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="G218">
-        <v>35.516357497927203</v>
+        <v>34.896415045465609</v>
       </c>
       <c r="H218">
-        <v>139.66018408801415</v>
+        <v>139.44682763432323</v>
       </c>
     </row>
     <row r="219" spans="2:8">
@@ -14992,19 +14989,19 @@
         <v>632</v>
       </c>
       <c r="C219">
-        <v>41.528902727934096</v>
+        <v>41.3361912214217</v>
       </c>
       <c r="D219">
-        <v>140.18694836006549</v>
+        <v>140.82133755355883</v>
       </c>
       <c r="F219" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="G219">
-        <v>36.19147631712201</v>
+        <v>36.357810636517982</v>
       </c>
       <c r="H219">
-        <v>140.30754342094826</v>
+        <v>140.55700872293659</v>
       </c>
     </row>
     <row r="220" spans="2:8">
@@ -15012,19 +15009,19 @@
         <v>633</v>
       </c>
       <c r="C220">
-        <v>39.993434559438533</v>
+        <v>40.045024127788608</v>
       </c>
       <c r="D220">
-        <v>140.29903337030427</v>
+        <v>140.08826559663316</v>
       </c>
       <c r="F220" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="G220">
-        <v>36.348454276526617</v>
+        <v>36.492708691076665</v>
       </c>
       <c r="H220">
-        <v>139.60657015788613</v>
+        <v>139.29880348917476</v>
       </c>
     </row>
     <row r="221" spans="2:8">
@@ -15032,19 +15029,19 @@
         <v>634</v>
       </c>
       <c r="C221">
-        <v>39.911267974113372</v>
+        <v>39.834029734760925</v>
       </c>
       <c r="D221">
-        <v>141.16581990056631</v>
+        <v>141.47741526648781</v>
       </c>
       <c r="F221" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="G221">
-        <v>37.989078017834409</v>
+        <v>38.060095610710867</v>
       </c>
       <c r="H221">
-        <v>139.39537508870831</v>
+        <v>139.23536456982546</v>
       </c>
     </row>
     <row r="222" spans="2:8">
@@ -15052,19 +15049,19 @@
         <v>635</v>
       </c>
       <c r="C222">
-        <v>38.254479362485085</v>
+        <v>38.156451363967072</v>
       </c>
       <c r="D222">
-        <v>140.87002090547148</v>
+        <v>140.92706908580772</v>
       </c>
       <c r="F222" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="G222">
-        <v>37.48200393492224</v>
+        <v>37.63184781846109</v>
       </c>
       <c r="H222">
-        <v>137.13221205726239</v>
+        <v>136.89752291232216</v>
       </c>
     </row>
     <row r="223" spans="2:8">
@@ -15072,19 +15069,19 @@
         <v>636</v>
       </c>
       <c r="C223">
-        <v>26.721487336012729</v>
+        <v>26.853629519883636</v>
       </c>
       <c r="D223">
-        <v>128.10477117822481</v>
+        <v>127.98617033570848</v>
       </c>
       <c r="F223" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="G223">
-        <v>36.611672842337725</v>
+        <v>36.522686036534161</v>
       </c>
       <c r="H223">
-        <v>137.08456152283767</v>
+        <v>137.12778269366422</v>
       </c>
     </row>
     <row r="224" spans="2:8">
@@ -15092,19 +15089,19 @@
         <v>637</v>
       </c>
       <c r="C224">
-        <v>31.186718545101872</v>
+        <v>29.923387557965011</v>
       </c>
       <c r="D224">
-        <v>130.81208583399706</v>
+        <v>129.9192417838953</v>
       </c>
       <c r="F224" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="G224">
-        <v>41.528902727934096</v>
+        <v>41.3361912214217</v>
       </c>
       <c r="H224">
-        <v>140.18694836006549</v>
+        <v>140.82133755355883</v>
       </c>
     </row>
     <row r="225" spans="2:8">
@@ -15112,19 +15109,19 @@
         <v>638</v>
       </c>
       <c r="C225">
-        <v>34.313789490388615</v>
+        <v>34.205865480462833</v>
       </c>
       <c r="D225">
-        <v>132.01023796876109</v>
+        <v>131.9398888446519</v>
       </c>
       <c r="F225" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="G225">
-        <v>39.993434559438533</v>
+        <v>40.045024127788608</v>
       </c>
       <c r="H225">
-        <v>140.29903337030427</v>
+        <v>140.08826559663316</v>
       </c>
     </row>
     <row r="226" spans="2:8">
@@ -15132,19 +15129,19 @@
         <v>639</v>
       </c>
       <c r="C226">
-        <v>34.334339818137771</v>
+        <v>34.109509727206635</v>
       </c>
       <c r="D226">
-        <v>133.27915491980451</v>
+        <v>133.38488645205345</v>
       </c>
       <c r="F226" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="G226">
-        <v>39.911267974113372</v>
+        <v>39.834029734760925</v>
       </c>
       <c r="H226">
-        <v>141.16581990056631</v>
+        <v>141.47741526648781</v>
       </c>
     </row>
     <row r="227" spans="2:8">
@@ -15152,19 +15149,19 @@
         <v>640</v>
       </c>
       <c r="C227">
-        <v>33.115690353314349</v>
+        <v>32.985359272550959</v>
       </c>
       <c r="D227">
-        <v>130.62843533461103</v>
+        <v>130.56537892541633</v>
       </c>
       <c r="F227" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="G227">
-        <v>38.254479362485085</v>
+        <v>38.156451363967072</v>
       </c>
       <c r="H227">
-        <v>140.87002090547148</v>
+        <v>140.92706908580772</v>
       </c>
     </row>
     <row r="228" spans="2:8">
@@ -15172,19 +15169,19 @@
         <v>641</v>
       </c>
       <c r="C228">
-        <v>32.338023062446382</v>
+        <v>32.310868999757552</v>
       </c>
       <c r="D228">
-        <v>131.04431989990678</v>
+        <v>131.05879274257779</v>
       </c>
       <c r="F228" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="G228">
-        <v>26.721487336012729</v>
+        <v>26.853629519883636</v>
       </c>
       <c r="H228">
-        <v>128.10477117822481</v>
+        <v>127.98617033570848</v>
       </c>
     </row>
     <row r="229" spans="2:8">
@@ -15192,19 +15189,19 @@
         <v>642</v>
       </c>
       <c r="C229">
-        <v>34.677758993260163</v>
+        <v>34.604135927255129</v>
       </c>
       <c r="D229">
-        <v>137.25730064583442</v>
+        <v>137.12778269366419</v>
       </c>
       <c r="F229" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="G229">
-        <v>31.186718545101872</v>
+        <v>29.923387557965011</v>
       </c>
       <c r="H229">
-        <v>130.81208583399706</v>
+        <v>129.9192417838953</v>
       </c>
     </row>
     <row r="230" spans="2:8">
@@ -15212,19 +15209,19 @@
         <v>643</v>
       </c>
       <c r="C230">
-        <v>34.780849662497538</v>
+        <v>34.873932036372494</v>
       </c>
       <c r="D230">
-        <v>136.42363715874816</v>
+        <v>136.43700334963813</v>
       </c>
       <c r="F230" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="G230">
-        <v>34.313789490388615</v>
+        <v>34.205865480462833</v>
       </c>
       <c r="H230">
-        <v>132.01023796876109</v>
+        <v>131.9398888446519</v>
       </c>
     </row>
     <row r="231" spans="2:8">
@@ -15232,19 +15229,19 @@
         <v>644</v>
       </c>
       <c r="C231">
-        <v>36.228646486256316</v>
+        <v>36.282867272874277</v>
       </c>
       <c r="D231">
-        <v>137.05023194742876</v>
+        <v>137.06199418470931</v>
       </c>
       <c r="F231" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="G231">
-        <v>34.334339818137771</v>
+        <v>34.109509727206635</v>
       </c>
       <c r="H231">
-        <v>133.27915491980451</v>
+        <v>133.38488645205345</v>
       </c>
     </row>
     <row r="232" spans="2:8">
@@ -15252,19 +15249,19 @@
         <v>645</v>
       </c>
       <c r="C232">
-        <v>33.950908983453743</v>
+        <v>33.8846796362755</v>
       </c>
       <c r="D232">
-        <v>134.0697330936454</v>
+        <v>133.86228034008627</v>
       </c>
       <c r="F232" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="G232">
-        <v>33.115690353314349</v>
+        <v>32.985359272550959</v>
       </c>
       <c r="H232">
-        <v>130.62843533461103</v>
+        <v>130.56537892541633</v>
       </c>
     </row>
     <row r="233" spans="2:8">
@@ -15272,19 +15269,19 @@
         <v>646</v>
       </c>
       <c r="C233">
-        <v>35.387363191003828</v>
+        <v>35.554846026049646</v>
       </c>
       <c r="D233">
-        <v>134.84839005250069</v>
+        <v>134.93561559170385</v>
       </c>
       <c r="F233" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="G233">
-        <v>32.338023062446382</v>
+        <v>32.310868999757552</v>
       </c>
       <c r="H233">
-        <v>131.04431989990678</v>
+        <v>131.05879274257779</v>
       </c>
     </row>
     <row r="234" spans="2:8">
@@ -15292,19 +15289,19 @@
         <v>647</v>
       </c>
       <c r="C234">
-        <v>36.305655858504757</v>
+        <v>36.132980545586847</v>
       </c>
       <c r="D234">
-        <v>139.88301181643868</v>
+        <v>139.69353454290396</v>
       </c>
       <c r="F234" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="G234">
-        <v>34.677758993260163</v>
+        <v>34.604135927255129</v>
       </c>
       <c r="H234">
-        <v>137.25730064583442</v>
+        <v>137.12778269366419</v>
       </c>
     </row>
     <row r="235" spans="2:8">
@@ -15312,19 +15309,19 @@
         <v>648</v>
       </c>
       <c r="C235">
-        <v>35.626964425126431</v>
+        <v>35.627112840991792</v>
       </c>
       <c r="D235">
-        <v>140.05363713209957</v>
+        <v>140.06359490577509</v>
       </c>
       <c r="F235" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="G235">
-        <v>34.780849662497538</v>
+        <v>34.873932036372494</v>
       </c>
       <c r="H235">
-        <v>136.42363715874816</v>
+        <v>136.43700334963813</v>
       </c>
     </row>
     <row r="236" spans="2:8">
@@ -15335,16 +15332,16 @@
         <v>35.233660181862312</v>
       </c>
       <c r="D236">
-        <v>138.58978349097978</v>
+        <v>138.46000000000024</v>
       </c>
       <c r="F236" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="G236">
-        <v>36.228646486256316</v>
+        <v>36.282867272874277</v>
       </c>
       <c r="H236">
-        <v>137.05023194742876</v>
+        <v>137.06199418470931</v>
       </c>
     </row>
     <row r="237" spans="2:8">
@@ -15352,19 +15349,19 @@
         <v>650</v>
       </c>
       <c r="C237">
-        <v>34.784000000000034</v>
+        <v>34.199441763579088</v>
       </c>
       <c r="D237">
-        <v>138.2132930914195</v>
+        <v>139.39748625260708</v>
       </c>
       <c r="F237" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="G237">
-        <v>33.950908983453743</v>
+        <v>33.8846796362755</v>
       </c>
       <c r="H237">
-        <v>134.0697330936454</v>
+        <v>133.86228034008627</v>
       </c>
     </row>
     <row r="238" spans="2:8">
@@ -15372,19 +15369,19 @@
         <v>651</v>
       </c>
       <c r="C238">
-        <v>35.229245727618768</v>
+        <v>35.458490272793441</v>
       </c>
       <c r="D238">
-        <v>132.64662014289334</v>
+        <v>132.53903419406228</v>
       </c>
       <c r="F238" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="G238">
-        <v>35.387363191003828</v>
+        <v>35.554846026049646</v>
       </c>
       <c r="H238">
-        <v>134.84839005250069</v>
+        <v>134.93561559170385</v>
       </c>
     </row>
     <row r="239" spans="2:8">
@@ -15392,19 +15389,19 @@
         <v>652</v>
       </c>
       <c r="C239">
-        <v>36.918571067960393</v>
+        <v>37.144715954776963</v>
       </c>
       <c r="D239">
-        <v>136.89427293726365</v>
+        <v>136.91808182137055</v>
       </c>
       <c r="F239" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="G239">
-        <v>36.305655858504757</v>
+        <v>36.132980545586847</v>
       </c>
       <c r="H239">
-        <v>139.88301181643868</v>
+        <v>139.69353454290396</v>
       </c>
     </row>
     <row r="240" spans="2:8">
@@ -15412,19 +15409,19 @@
         <v>653</v>
       </c>
       <c r="C240">
-        <v>32.985359272550959</v>
+        <v>32.821846479146494</v>
       </c>
       <c r="D240">
-        <v>132.78574110264304</v>
+        <v>133.32401072136466</v>
       </c>
       <c r="F240" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="G240">
-        <v>35.626964425126431</v>
+        <v>35.627112840991792</v>
       </c>
       <c r="H240">
-        <v>140.05363713209957</v>
+        <v>140.06359490577509</v>
       </c>
     </row>
     <row r="241" spans="2:8">
@@ -15432,19 +15429,19 @@
         <v>654</v>
       </c>
       <c r="C241">
-        <v>33.176862843163498</v>
+        <v>33.19948316867584</v>
       </c>
       <c r="D241">
-        <v>130.32210892390466</v>
+        <v>129.73127461545283</v>
       </c>
       <c r="F241" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="G241">
         <v>35.233660181862312</v>
       </c>
       <c r="H241">
-        <v>138.58978349097978</v>
+        <v>138.46000000000024</v>
       </c>
     </row>
     <row r="242" spans="2:8">
@@ -15452,19 +15449,19 @@
         <v>655</v>
       </c>
       <c r="C242">
-        <v>37.931621273035937</v>
+        <v>38.217768661493743</v>
       </c>
       <c r="D242">
-        <v>139.20012072574249</v>
+        <v>138.93098591638167</v>
       </c>
       <c r="F242" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="G242">
-        <v>34.784000000000034</v>
+        <v>34.199441763579088</v>
       </c>
       <c r="H242">
-        <v>138.2132930914195</v>
+        <v>139.39748625260708</v>
       </c>
     </row>
     <row r="243" spans="2:8">
@@ -15472,19 +15469,19 @@
         <v>656</v>
       </c>
       <c r="C243">
-        <v>37.588614516018438</v>
+        <v>37.706791182104801</v>
       </c>
       <c r="D243">
-        <v>140.81238785426279</v>
+        <v>141.07509323095616</v>
       </c>
       <c r="F243" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="G243">
-        <v>35.229245727618768</v>
+        <v>35.458490272793441</v>
       </c>
       <c r="H243">
-        <v>132.64662014289334</v>
+        <v>132.53903419406228</v>
       </c>
     </row>
     <row r="244" spans="2:8">
@@ -15492,19 +15489,19 @@
         <v>657</v>
       </c>
       <c r="C244">
-        <v>36.904959135616721</v>
+        <v>36.762504800194037</v>
       </c>
       <c r="D244">
-        <v>139.72420017893802</v>
+        <v>139.59485177947167</v>
       </c>
       <c r="F244" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="G244">
-        <v>36.918571067960393</v>
+        <v>37.144715954776963</v>
       </c>
       <c r="H244">
-        <v>136.89427293726365</v>
+        <v>136.91808182137055</v>
       </c>
     </row>
     <row r="245" spans="2:8">
@@ -15512,19 +15509,19 @@
         <v>658</v>
       </c>
       <c r="C245">
-        <v>37.725022041959647</v>
+        <v>37.781734545748513</v>
       </c>
       <c r="D245">
-        <v>139.86844606266203</v>
+        <v>139.85800581529114</v>
       </c>
       <c r="F245" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="G245">
-        <v>32.985359272550959</v>
+        <v>32.821846479146494</v>
       </c>
       <c r="H245">
-        <v>132.78574110264304</v>
+        <v>133.32401072136466</v>
       </c>
     </row>
     <row r="246" spans="2:8">
@@ -15532,19 +15529,19 @@
         <v>659</v>
       </c>
       <c r="C246">
-        <v>39.360869838266851</v>
+        <v>39.321480016973858</v>
       </c>
       <c r="D246">
-        <v>140.76855308816241</v>
+        <v>140.77007378034725</v>
       </c>
       <c r="F246" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="G246">
-        <v>33.176862843163498</v>
+        <v>33.19948316867584</v>
       </c>
       <c r="H246">
-        <v>130.32210892390466</v>
+        <v>129.73127461545283</v>
       </c>
     </row>
     <row r="247" spans="2:8">
@@ -15552,19 +15549,19 @@
         <v>660</v>
       </c>
       <c r="C247">
-        <v>42.780193454503362</v>
+        <v>42.668041855318521</v>
       </c>
       <c r="D247">
-        <v>141.21172114456672</v>
+        <v>141.20667024886589</v>
       </c>
       <c r="F247" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="G247">
-        <v>37.931621273035937</v>
+        <v>38.217768661493743</v>
       </c>
       <c r="H247">
-        <v>139.20012072574249</v>
+        <v>138.93098591638167</v>
       </c>
     </row>
     <row r="248" spans="2:8">
@@ -15572,19 +15569,19 @@
         <v>661</v>
       </c>
       <c r="C248">
-        <v>41.947320552197233</v>
+        <v>42.153430758298363</v>
       </c>
       <c r="D248">
-        <v>140.81043619739748</v>
+        <v>140.65295029849574</v>
       </c>
       <c r="F248" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="G248">
-        <v>37.588614516018438</v>
+        <v>37.706791182104801</v>
       </c>
       <c r="H248">
-        <v>140.81238785426279</v>
+        <v>141.07509323095616</v>
       </c>
     </row>
     <row r="249" spans="2:8">
@@ -15592,19 +15589,19 @@
         <v>662</v>
       </c>
       <c r="C249">
-        <v>40.167323078141273</v>
+        <v>40.206372781280358</v>
       </c>
       <c r="D249">
-        <v>141.03345633005097</v>
+        <v>140.91255691471474</v>
       </c>
       <c r="F249" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="G249">
-        <v>36.904959135616721</v>
+        <v>36.762504800194037</v>
       </c>
       <c r="H249">
-        <v>139.72420017893802</v>
+        <v>139.59485177947167</v>
       </c>
     </row>
     <row r="250" spans="2:8">
@@ -15612,19 +15609,19 @@
         <v>663</v>
       </c>
       <c r="C250">
-        <v>43.783320086235328</v>
+        <v>43.777203637245456</v>
       </c>
       <c r="D250">
-        <v>142.49621505032994</v>
+        <v>142.51304206954109</v>
       </c>
       <c r="F250" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="G250">
-        <v>37.725022041959647</v>
+        <v>37.781734545748513</v>
       </c>
       <c r="H250">
-        <v>139.86844606266203</v>
+        <v>139.85800581529114</v>
       </c>
     </row>
     <row r="251" spans="2:8">
@@ -15632,19 +15629,19 @@
         <v>664</v>
       </c>
       <c r="C251">
-        <v>43.128232811384791</v>
+        <v>42.990298318986483</v>
       </c>
       <c r="D251">
-        <v>143.30449822379012</v>
+        <v>143.20910799017963</v>
       </c>
       <c r="F251" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="G251">
-        <v>39.360869838266851</v>
+        <v>39.321480016973858</v>
       </c>
       <c r="H251">
-        <v>140.76855308816241</v>
+        <v>140.77007378034725</v>
       </c>
     </row>
     <row r="252" spans="2:8">
@@ -15652,19 +15649,19 @@
         <v>665</v>
       </c>
       <c r="C252">
-        <v>44.645578062145312</v>
+        <v>44.717402199321107</v>
       </c>
       <c r="D252">
-        <v>142.3888373625914</v>
+        <v>142.1157478271513</v>
       </c>
       <c r="F252" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="G252">
-        <v>42.780193454503362</v>
+        <v>42.668041855318521</v>
       </c>
       <c r="H252">
-        <v>141.21172114456672</v>
+        <v>141.20667024886589</v>
       </c>
     </row>
     <row r="253" spans="2:8">
@@ -15672,19 +15669,19 @@
         <v>666</v>
       </c>
       <c r="C253">
-        <v>43.555305636098922</v>
+        <v>43.456017793058123</v>
       </c>
       <c r="D253">
-        <v>144.44314691977866</v>
+        <v>144.55718502635301</v>
       </c>
       <c r="F253" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="G253">
-        <v>41.947320552197233</v>
+        <v>42.153430758298363</v>
       </c>
       <c r="H253">
-        <v>140.81043619739748</v>
+        <v>140.65295029849574</v>
       </c>
     </row>
     <row r="254" spans="2:8">
@@ -15692,19 +15689,19 @@
         <v>667</v>
       </c>
       <c r="C254">
-        <v>24.424451344948238</v>
+        <v>24.647167147537104</v>
       </c>
       <c r="D254">
-        <v>123.75988603755351</v>
+        <v>123.76139220881444</v>
       </c>
       <c r="F254" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="G254">
-        <v>40.167323078141273</v>
+        <v>40.206372781280358</v>
       </c>
       <c r="H254">
-        <v>141.03345633005097</v>
+        <v>140.91255691471474</v>
       </c>
     </row>
     <row r="255" spans="2:8">
@@ -15712,19 +15709,19 @@
         <v>668</v>
       </c>
       <c r="C255">
-        <v>25.107809154669543</v>
+        <v>24.824182694243067</v>
       </c>
       <c r="D255">
-        <v>125.86192830995979</v>
+        <v>125.78405903139652</v>
       </c>
       <c r="F255" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="G255">
-        <v>43.783320086235328</v>
+        <v>43.777203637245456</v>
       </c>
       <c r="H255">
-        <v>142.49621505032994</v>
+        <v>142.51304206954109</v>
       </c>
     </row>
     <row r="256" spans="2:8">
@@ -15732,19 +15729,19 @@
         <v>669</v>
       </c>
       <c r="C256">
-        <v>28.644477570897426</v>
+        <v>28.634538418324308</v>
       </c>
       <c r="D256">
-        <v>127.5517033100982</v>
+        <v>127.63432198477828</v>
       </c>
       <c r="F256" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="G256">
-        <v>43.128232811384791</v>
+        <v>42.990298318986483</v>
       </c>
       <c r="H256">
-        <v>143.30449822379012</v>
+        <v>143.20910799017963</v>
       </c>
     </row>
     <row r="257" spans="2:8">
@@ -15752,19 +15749,19 @@
         <v>670</v>
       </c>
       <c r="C257">
-        <v>28.399703529450854</v>
+        <v>28.342112352341974</v>
       </c>
       <c r="D257">
-        <v>129.21792730748413</v>
+        <v>129.46919173555284</v>
       </c>
       <c r="F257" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="G257">
-        <v>44.645578062145312</v>
+        <v>44.717402199321107</v>
       </c>
       <c r="H257">
-        <v>142.3888373625914</v>
+        <v>142.1157478271513</v>
       </c>
     </row>
     <row r="258" spans="2:8">
@@ -15772,19 +15769,19 @@
         <v>671</v>
       </c>
       <c r="C258">
-        <v>25.613675369966039</v>
+        <v>25.511898266503003</v>
       </c>
       <c r="D258">
-        <v>131.33260837546436</v>
+        <v>131.76893620506388</v>
       </c>
       <c r="F258" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="G258">
-        <v>43.555305636098922</v>
+        <v>43.456017793058123</v>
       </c>
       <c r="H258">
-        <v>144.44314691977866</v>
+        <v>144.55718502635301</v>
       </c>
     </row>
     <row r="259" spans="2:8">
@@ -15792,19 +15789,19 @@
         <v>672</v>
       </c>
       <c r="C259">
-        <v>27.618525615289947</v>
+        <v>27.760199175814339</v>
       </c>
       <c r="D259">
-        <v>125.82791747356694</v>
+        <v>125.88103620782169</v>
       </c>
       <c r="F259" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="G259">
-        <v>24.424451344948238</v>
+        <v>24.647167147537104</v>
       </c>
       <c r="H259">
-        <v>123.75988603755351</v>
+        <v>123.76139220881444</v>
       </c>
     </row>
     <row r="260" spans="2:8">
@@ -15812,19 +15809,19 @@
         <v>673</v>
       </c>
       <c r="C260">
-        <v>26.727683627870377</v>
+        <v>26.606723057124174</v>
       </c>
       <c r="D260">
-        <v>127.64352445927948</v>
+        <v>127.32485168540629</v>
       </c>
       <c r="F260" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="G260">
-        <v>25.107809154669543</v>
+        <v>24.824182694243067</v>
       </c>
       <c r="H260">
-        <v>125.86192830995979</v>
+        <v>125.78405903139652</v>
       </c>
     </row>
     <row r="261" spans="2:8">
@@ -15832,19 +15829,19 @@
         <v>674</v>
       </c>
       <c r="C261">
-        <v>32.838284210587084</v>
+        <v>32.796393212671738</v>
       </c>
       <c r="D261">
-        <v>132.37699501710549</v>
+        <v>132.52258740471089</v>
       </c>
       <c r="F261" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="G261">
-        <v>28.644477570897426</v>
+        <v>28.634538418324308</v>
       </c>
       <c r="H261">
-        <v>127.5517033100982</v>
+        <v>127.63432198477828</v>
       </c>
     </row>
     <row r="262" spans="2:8">
@@ -15852,19 +15849,19 @@
         <v>675</v>
       </c>
       <c r="C262">
-        <v>33.605781540023827</v>
+        <v>33.965509685513645</v>
       </c>
       <c r="D262">
-        <v>135.06616020351947</v>
+        <v>135.25457300343123</v>
       </c>
       <c r="F262" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="G262">
-        <v>28.399703529450854</v>
+        <v>28.342112352341974</v>
       </c>
       <c r="H262">
-        <v>129.21792730748413</v>
+        <v>129.46919173555284</v>
       </c>
     </row>
     <row r="263" spans="2:8">
@@ -15872,19 +15869,19 @@
         <v>676</v>
       </c>
       <c r="C263">
-        <v>31.530147176247681</v>
+        <v>31.550192137224879</v>
       </c>
       <c r="D263">
-        <v>131.57888890071339</v>
+        <v>131.70164591938115</v>
       </c>
       <c r="F263" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="G263">
-        <v>25.613675369966039</v>
+        <v>25.511898266503003</v>
       </c>
       <c r="H263">
-        <v>131.33260837546436</v>
+        <v>131.76893620506388</v>
       </c>
     </row>
     <row r="264" spans="2:8">
@@ -15892,19 +15889,19 @@
         <v>677</v>
       </c>
       <c r="C264">
-        <v>32.99133796901824</v>
+        <v>33.006234630874133</v>
       </c>
       <c r="D264">
-        <v>133.90360308216228</v>
+        <v>134.62653033705877</v>
       </c>
       <c r="F264" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="G264">
-        <v>27.618525615289947</v>
+        <v>27.760199175814339</v>
       </c>
       <c r="H264">
-        <v>125.82791747356694</v>
+        <v>125.88103620782169</v>
       </c>
     </row>
     <row r="265" spans="2:8">
@@ -15912,19 +15909,19 @@
         <v>678</v>
       </c>
       <c r="C265">
-        <v>30.260469751385287</v>
+        <v>30.285214043194767</v>
       </c>
       <c r="D265">
-        <v>129.70586495498355</v>
+        <v>129.93915805207479</v>
       </c>
       <c r="F265" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="G265">
-        <v>26.727683627870377</v>
+        <v>26.606723057124174</v>
       </c>
       <c r="H265">
-        <v>127.64352445927948</v>
+        <v>127.32485168540629</v>
       </c>
     </row>
     <row r="266" spans="2:8">
@@ -15932,19 +15929,19 @@
         <v>679</v>
       </c>
       <c r="C266">
-        <v>31.880169043997025</v>
+        <v>31.935615150249681</v>
       </c>
       <c r="D266">
-        <v>129.02328718276993</v>
+        <v>129.11096992059461</v>
       </c>
       <c r="F266" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="G266">
-        <v>32.838284210587084</v>
+        <v>32.796393212671738</v>
       </c>
       <c r="H266">
-        <v>132.37699501710549</v>
+        <v>132.52258740471089</v>
       </c>
     </row>
     <row r="267" spans="2:8">
@@ -15952,19 +15949,19 @@
         <v>680</v>
       </c>
       <c r="C267">
-        <v>34.168001890807723</v>
+        <v>34.055441721886098</v>
       </c>
       <c r="D267">
-        <v>130.66843087193791</v>
+        <v>130.59135620561543</v>
       </c>
       <c r="F267" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="G267">
-        <v>33.605781540023827</v>
+        <v>33.965509685513645</v>
       </c>
       <c r="H267">
-        <v>135.06616020351947</v>
+        <v>135.25457300343123</v>
       </c>
     </row>
     <row r="268" spans="2:8">
@@ -15972,19 +15969,19 @@
         <v>681</v>
       </c>
       <c r="C268">
-        <v>33.449768320720089</v>
+        <v>33.409055210459087</v>
       </c>
       <c r="D268">
-        <v>128.72012778262751</v>
+        <v>128.79554670645661</v>
       </c>
       <c r="F268" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="G268">
-        <v>31.530147176247681</v>
+        <v>31.550192137224879</v>
       </c>
       <c r="H268">
-        <v>131.57888890071339</v>
+        <v>131.70164591938115</v>
       </c>
     </row>
     <row r="269" spans="2:8">
@@ -15992,19 +15989,19 @@
         <v>682</v>
       </c>
       <c r="C269">
-        <v>43.467569198107689</v>
+        <v>43.198532086418936</v>
       </c>
       <c r="D269">
-        <v>140.8451250235658</v>
+        <v>140.92789175632942</v>
       </c>
       <c r="F269" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="G269">
-        <v>32.99133796901824</v>
+        <v>33.006234630874133</v>
       </c>
       <c r="H269">
-        <v>133.90360308216228</v>
+        <v>134.62653033705877</v>
       </c>
     </row>
     <row r="270" spans="2:8">
@@ -16012,19 +16009,19 @@
         <v>683</v>
       </c>
       <c r="C270">
-        <v>41.503085916868486</v>
+        <v>41.449853601398999</v>
       </c>
       <c r="D270">
-        <v>141.91802299370221</v>
+        <v>142.07930331134563</v>
       </c>
       <c r="F270" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="G270">
-        <v>30.260469751385287</v>
+        <v>30.285214043194767</v>
       </c>
       <c r="H270">
-        <v>129.70586495498355</v>
+        <v>129.93915805207479</v>
       </c>
     </row>
     <row r="271" spans="2:8">
@@ -16032,19 +16029,19 @@
         <v>684</v>
       </c>
       <c r="C271">
-        <v>41.25000463168243</v>
+        <v>41.382257626347794</v>
       </c>
       <c r="D271">
-        <v>140.24751220109255</v>
+        <v>140.21980443639964</v>
       </c>
       <c r="F271" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="G271">
-        <v>31.880169043997025</v>
+        <v>31.935615150249681</v>
       </c>
       <c r="H271">
-        <v>129.02328718276993</v>
+        <v>129.11096992059461</v>
       </c>
     </row>
     <row r="272" spans="2:8">
@@ -16052,19 +16049,19 @@
         <v>685</v>
       </c>
       <c r="C272">
-        <v>42.494097202990481</v>
+        <v>42.767607745467593</v>
       </c>
       <c r="D272">
-        <v>144.36088659713727</v>
+        <v>144.72231619899657</v>
       </c>
       <c r="F272" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="G272">
-        <v>34.168001890807723</v>
+        <v>34.055441721886098</v>
       </c>
       <c r="H272">
-        <v>130.66843087193791</v>
+        <v>130.59135620561543</v>
       </c>
     </row>
     <row r="273" spans="2:8">
@@ -16075,16 +16072,16 @@
         <v>43.947965722856047</v>
       </c>
       <c r="D273">
-        <v>144.66187355698406</v>
+        <v>144.48680019910688</v>
       </c>
       <c r="F273" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="G273">
-        <v>33.449768320720089</v>
+        <v>33.409055210459087</v>
       </c>
       <c r="H273">
-        <v>128.72012778262751</v>
+        <v>128.79554670645661</v>
       </c>
     </row>
     <row r="274" spans="2:8">
@@ -16092,19 +16089,19 @@
         <v>687</v>
       </c>
       <c r="C274">
-        <v>44.814613560885753</v>
+        <v>44.697399359293172</v>
       </c>
       <c r="D274">
-        <v>144.24463673704989</v>
+        <v>144.6438108657</v>
       </c>
       <c r="F274" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="G274">
-        <v>43.467569198107689</v>
+        <v>43.198532086418936</v>
       </c>
       <c r="H274">
-        <v>140.8451250235658</v>
+        <v>140.92789175632942</v>
       </c>
     </row>
     <row r="275" spans="2:8">
@@ -16112,19 +16109,19 @@
         <v>688</v>
       </c>
       <c r="C275">
-        <v>44.772620433183782</v>
+        <v>44.62245599564946</v>
       </c>
       <c r="D275">
-        <v>140.47760045996375</v>
+        <v>140.22939558571642</v>
       </c>
       <c r="F275" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="G275">
-        <v>41.503085916868486</v>
+        <v>41.449853601398999</v>
       </c>
       <c r="H275">
-        <v>141.91802299370221</v>
+        <v>142.07930331134563</v>
       </c>
     </row>
     <row r="276" spans="2:8">
@@ -16132,19 +16129,19 @@
         <v>689</v>
       </c>
       <c r="C276">
-        <v>45.593282516097815</v>
+        <v>45.521776359374002</v>
       </c>
       <c r="D276">
-        <v>141.87681973346676</v>
+        <v>141.89612420032034</v>
       </c>
       <c r="F276" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="G276">
-        <v>41.25000463168243</v>
+        <v>41.382257626347794</v>
       </c>
       <c r="H276">
-        <v>140.24751220109255</v>
+        <v>140.21980443639964</v>
       </c>
     </row>
     <row r="277" spans="2:8">
@@ -16152,19 +16149,19 @@
         <v>690</v>
       </c>
       <c r="C277">
-        <v>45.136267941625377</v>
+        <v>44.959701132046163</v>
       </c>
       <c r="D277">
-        <v>143.28434044747988</v>
+        <v>143.19146219971361</v>
       </c>
       <c r="F277" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="G277">
-        <v>42.494097202990481</v>
+        <v>42.767607745467593</v>
       </c>
       <c r="H277">
-        <v>144.36088659713727</v>
+        <v>144.72231619899657</v>
       </c>
     </row>
     <row r="278" spans="2:8">
@@ -16172,19 +16169,19 @@
         <v>691</v>
       </c>
       <c r="C278">
-        <v>39.128778294769006</v>
+        <v>39.345561508501049</v>
       </c>
       <c r="D278">
-        <v>139.13705161724229</v>
+        <v>139.05607831929763</v>
       </c>
       <c r="F278" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="G278">
         <v>43.947965722856047</v>
       </c>
       <c r="H278">
-        <v>144.66187355698406</v>
+        <v>144.48680019910688</v>
       </c>
     </row>
     <row r="279" spans="2:8">
@@ -16192,19 +16189,19 @@
         <v>692</v>
       </c>
       <c r="C279">
-        <v>37.848165429839419</v>
+        <v>37.877553267715399</v>
       </c>
       <c r="D279">
-        <v>138.26086497295543</v>
+        <v>138.12786820208541</v>
       </c>
       <c r="F279" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="G279">
-        <v>44.814613560885753</v>
+        <v>44.697399359293172</v>
       </c>
       <c r="H279">
-        <v>144.24463673704989</v>
+        <v>144.6438108657</v>
       </c>
     </row>
     <row r="280" spans="2:8">
@@ -16212,19 +16209,19 @@
         <v>693</v>
       </c>
       <c r="C280">
-        <v>37.339743479830958</v>
+        <v>37.315478040387561</v>
       </c>
       <c r="D280">
-        <v>136.58703046975728</v>
+        <v>136.59701420280243</v>
       </c>
       <c r="F280" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="G280">
-        <v>44.772620433183782</v>
+        <v>44.62245599564946</v>
       </c>
       <c r="H280">
-        <v>140.47760045996375</v>
+        <v>140.22939558571642</v>
       </c>
     </row>
     <row r="281" spans="2:8">
@@ -16232,19 +16229,19 @@
         <v>694</v>
       </c>
       <c r="C281">
-        <v>38.235138003058616</v>
+        <v>38.597009558695028</v>
       </c>
       <c r="D281">
-        <v>136.94067076221</v>
+        <v>136.66766900276934</v>
       </c>
       <c r="F281" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="G281">
-        <v>45.593282516097815</v>
+        <v>45.521776359374002</v>
       </c>
       <c r="H281">
-        <v>141.87681973346676</v>
+        <v>141.89612420032034</v>
       </c>
     </row>
     <row r="282" spans="2:8">
@@ -16252,19 +16249,19 @@
         <v>695</v>
       </c>
       <c r="C282">
-        <v>34.877613599360245</v>
+        <v>34.920172840852004</v>
       </c>
       <c r="D282">
-        <v>130.13660409704076</v>
+        <v>130.06597435970772</v>
       </c>
       <c r="F282" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="G282">
-        <v>45.136267941625377</v>
+        <v>44.959701132046163</v>
       </c>
       <c r="H282">
-        <v>143.28434044747988</v>
+        <v>143.19146219971361</v>
       </c>
     </row>
     <row r="283" spans="2:8">
@@ -16272,19 +16269,19 @@
         <v>696</v>
       </c>
       <c r="C283">
-        <v>35.545155354656785</v>
+        <v>35.577368491266093</v>
       </c>
       <c r="D283">
-        <v>131.94831458682509</v>
+        <v>132.02256882032972</v>
       </c>
       <c r="F283" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="G283">
-        <v>39.128778294769006</v>
+        <v>39.345561508501049</v>
       </c>
       <c r="H283">
-        <v>139.13705161724229</v>
+        <v>139.05607831929763</v>
       </c>
     </row>
     <row r="284" spans="2:8">
@@ -16292,19 +16289,19 @@
         <v>697</v>
       </c>
       <c r="C284">
-        <v>37.252062064729245</v>
+        <v>37.592768485869293</v>
       </c>
       <c r="D284">
-        <v>133.123035207388</v>
+        <v>133.24483647103926</v>
       </c>
       <c r="F284" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="G284">
-        <v>37.848165429839419</v>
+        <v>37.877553267715399</v>
       </c>
       <c r="H284">
-        <v>138.26086497295543</v>
+        <v>138.12786820208541</v>
       </c>
     </row>
     <row r="285" spans="2:8">
@@ -16312,19 +16309,19 @@
         <v>698</v>
       </c>
       <c r="C285">
-        <v>36.303315274178594</v>
+        <v>36.303742631197451</v>
       </c>
       <c r="D285">
-        <v>135.75393144151963</v>
+        <v>135.77270820318856</v>
       </c>
       <c r="F285" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="G285">
-        <v>37.339743479830958</v>
+        <v>37.315478040387561</v>
       </c>
       <c r="H285">
-        <v>136.58703046975728</v>
+        <v>136.59701420280243</v>
       </c>
     </row>
     <row r="286" spans="2:8">
@@ -16332,19 +16329,19 @@
         <v>699</v>
       </c>
       <c r="C286">
-        <v>36.170460743581494</v>
+        <v>36.327408956558621</v>
       </c>
       <c r="D286">
-        <v>134.12233717644077</v>
+        <v>134.24805199337632</v>
       </c>
       <c r="F286" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="G286">
-        <v>38.235138003058616</v>
+        <v>38.597009558695028</v>
       </c>
       <c r="H286">
-        <v>136.94067076221</v>
+        <v>136.66766900276934</v>
       </c>
     </row>
     <row r="287" spans="2:8">
@@ -16352,19 +16349,19 @@
         <v>700</v>
       </c>
       <c r="C287">
-        <v>27.204888006162541</v>
+        <v>26.989353149764732</v>
       </c>
       <c r="D287">
-        <v>142.12237465999934</v>
+        <v>141.88490915270651</v>
       </c>
       <c r="F287" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="G287">
-        <v>34.877613599360245</v>
+        <v>34.920172840852004</v>
       </c>
       <c r="H287">
-        <v>130.13660409704076</v>
+        <v>130.06597435970772</v>
       </c>
     </row>
     <row r="288" spans="2:8">
@@ -16372,19 +16369,19 @@
         <v>701</v>
       </c>
       <c r="C288">
-        <v>23.439998949464769</v>
+        <v>23.983053648171296</v>
       </c>
       <c r="D288">
-        <v>153.12021637002653</v>
+        <v>153.43640819491492</v>
       </c>
       <c r="F288" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="G288">
-        <v>35.545155354656785</v>
+        <v>35.577368491266093</v>
       </c>
       <c r="H288">
-        <v>131.94831458682509</v>
+        <v>132.02256882032972</v>
       </c>
     </row>
     <row r="289" spans="2:8">
@@ -16392,19 +16389,19 @@
         <v>702</v>
       </c>
       <c r="C289">
-        <v>24.796014527638562</v>
+        <v>24.741052240453403</v>
       </c>
       <c r="D289">
-        <v>141.26023535130909</v>
+        <v>141.39144705769962</v>
       </c>
       <c r="F289" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="G289">
-        <v>37.252062064729245</v>
+        <v>37.592768485869293</v>
       </c>
       <c r="H289">
-        <v>133.123035207388</v>
+        <v>133.24483647103926</v>
       </c>
     </row>
     <row r="290" spans="2:8">
@@ -16412,19 +16409,19 @@
         <v>703</v>
       </c>
       <c r="C290">
-        <v>23.298235018493006</v>
+        <v>22.863899417758542</v>
       </c>
       <c r="D290">
-        <v>141.64045430982983</v>
+        <v>141.18957620065129</v>
       </c>
       <c r="F290" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="G290">
-        <v>36.303315274178594</v>
+        <v>36.303742631197451</v>
       </c>
       <c r="H290">
-        <v>135.75393144151963</v>
+        <v>135.77270820318856</v>
       </c>
     </row>
     <row r="291" spans="2:8">
@@ -16432,19 +16429,19 @@
         <v>704</v>
       </c>
       <c r="C291">
-        <v>31.434970526406527</v>
+        <v>31.113914698870417</v>
       </c>
       <c r="D291">
-        <v>139.74818097983936</v>
+        <v>139.50171153477521</v>
       </c>
       <c r="F291" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="G291">
-        <v>36.170460743581494</v>
+        <v>36.327408956558621</v>
       </c>
       <c r="H291">
-        <v>134.12233717644077</v>
+        <v>134.24805199337632</v>
       </c>
     </row>
     <row r="292" spans="2:8">
@@ -16452,19 +16449,19 @@
         <v>705</v>
       </c>
       <c r="C292">
-        <v>34.397127615176323</v>
+        <v>34.205328449173521</v>
       </c>
       <c r="D292">
-        <v>137.7222660013698</v>
+        <v>137.73534153560257</v>
       </c>
       <c r="F292" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="G292">
-        <v>27.204888006162541</v>
+        <v>26.989353149764732</v>
       </c>
       <c r="H292">
-        <v>142.12237465999934</v>
+        <v>141.88490915270651</v>
       </c>
     </row>
     <row r="293" spans="2:8">
@@ -16472,19 +16469,19 @@
         <v>706</v>
       </c>
       <c r="C293">
-        <v>33.549028912729732</v>
+        <v>33.580800418809254</v>
       </c>
       <c r="D293">
-        <v>139.63363489281076</v>
+        <v>139.54096420142346</v>
       </c>
       <c r="F293" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="G293">
-        <v>23.439998949464769</v>
+        <v>23.983053648171296</v>
       </c>
       <c r="H293">
-        <v>153.12021637002653</v>
+        <v>153.43640819491492</v>
       </c>
     </row>
     <row r="294" spans="2:8">
@@ -16492,19 +16489,19 @@
         <v>707</v>
       </c>
       <c r="C294">
-        <v>37.97171208671584</v>
+        <v>37.877553267715399</v>
       </c>
       <c r="D294">
-        <v>141.96863025997928</v>
+        <v>142.22584660016591</v>
       </c>
       <c r="F294" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="G294">
-        <v>24.796014527638562</v>
+        <v>24.741052240453403</v>
       </c>
       <c r="H294">
-        <v>141.26023535130909</v>
+        <v>141.39144705769962</v>
       </c>
     </row>
     <row r="295" spans="2:8">
@@ -16512,19 +16509,19 @@
         <v>708</v>
       </c>
       <c r="C295">
-        <v>39.208144574744267</v>
+        <v>39.001703722371083</v>
       </c>
       <c r="D295">
-        <v>142.06208299152522</v>
+        <v>141.99033060027622</v>
       </c>
       <c r="F295" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="G295">
-        <v>23.298235018493006</v>
+        <v>22.863899417758542</v>
       </c>
       <c r="H295">
-        <v>141.64045430982983</v>
+        <v>141.18957620065129</v>
       </c>
     </row>
     <row r="296" spans="2:8">
@@ -16532,19 +16529,19 @@
         <v>709</v>
       </c>
       <c r="C296">
-        <v>36.679210421320136</v>
+        <v>36.528572722128587</v>
       </c>
       <c r="D296">
-        <v>141.29428382626909</v>
+        <v>141.18957620065129</v>
       </c>
       <c r="F296" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="G296">
-        <v>31.434970526406527</v>
+        <v>31.113914698870417</v>
       </c>
       <c r="H296">
-        <v>139.74818097983936</v>
+        <v>139.50171153477521</v>
       </c>
     </row>
     <row r="297" spans="2:8">
@@ -16552,74 +16549,74 @@
         <v>710</v>
       </c>
       <c r="C297">
-        <v>35.147697605955742</v>
+        <v>35.254535540185486</v>
       </c>
       <c r="D297">
-        <v>140.36658879545362</v>
+        <v>140.24751220109255</v>
       </c>
       <c r="F297" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="G297">
-        <v>34.397127615176323</v>
+        <v>34.205328449173521</v>
       </c>
       <c r="H297">
-        <v>137.7222660013698</v>
+        <v>137.73534153560257</v>
       </c>
     </row>
     <row r="298" spans="2:8">
       <c r="F298" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="G298">
-        <v>33.549028912729732</v>
+        <v>33.580800418809254</v>
       </c>
       <c r="H298">
-        <v>139.63363489281076</v>
+        <v>139.54096420142346</v>
       </c>
     </row>
     <row r="299" spans="2:8">
       <c r="F299" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="G299">
-        <v>37.97171208671584</v>
+        <v>37.877553267715399</v>
       </c>
       <c r="H299">
-        <v>141.96863025997928</v>
+        <v>142.22584660016591</v>
       </c>
     </row>
     <row r="300" spans="2:8">
       <c r="F300" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="G300">
-        <v>39.208144574744267</v>
+        <v>39.001703722371083</v>
       </c>
       <c r="H300">
-        <v>142.06208299152522</v>
+        <v>141.99033060027622</v>
       </c>
     </row>
     <row r="301" spans="2:8">
       <c r="F301" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="G301">
-        <v>36.679210421320136</v>
+        <v>36.528572722128587</v>
       </c>
       <c r="H301">
-        <v>141.29428382626909</v>
+        <v>141.18957620065129</v>
       </c>
     </row>
     <row r="302" spans="2:8">
       <c r="F302" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="G302">
-        <v>35.147697605955742</v>
+        <v>35.254535540185486</v>
       </c>
       <c r="H302">
-        <v>140.36658879545362</v>
+        <v>140.24751220109255</v>
       </c>
     </row>
   </sheetData>
@@ -16628,7 +16625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CA9F323-9B09-4CB7-833A-C7B4F6801965}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{859EFA80-2533-4AA0-AEA3-B5F9B46BFCDA}">
   <dimension ref="B9:L302"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -16692,13 +16689,13 @@
         <v>712</v>
       </c>
       <c r="J11" t="s">
+        <v>758</v>
+      </c>
+      <c r="K11" t="s">
         <v>759</v>
       </c>
-      <c r="K11" t="s">
-        <v>760</v>
-      </c>
       <c r="L11" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="12" spans="2:12">
@@ -16721,13 +16718,13 @@
         <v>713</v>
       </c>
       <c r="J12" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K12" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="L12" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="13" spans="2:12">
@@ -16750,13 +16747,13 @@
         <v>713</v>
       </c>
       <c r="J13" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K13" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="L13" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="14" spans="2:12">
@@ -16779,13 +16776,13 @@
         <v>714</v>
       </c>
       <c r="J14" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="L14" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="15" spans="2:12">
@@ -16808,13 +16805,13 @@
         <v>714</v>
       </c>
       <c r="J15" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K15" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="L15" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -16837,13 +16834,13 @@
         <v>715</v>
       </c>
       <c r="J16" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K16" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="L16" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="17" spans="2:12">
@@ -16866,13 +16863,13 @@
         <v>716</v>
       </c>
       <c r="J17" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K17" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="L17" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="18" spans="2:12">
@@ -16895,13 +16892,13 @@
         <v>717</v>
       </c>
       <c r="J18" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K18" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="L18" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="19" spans="2:12">
@@ -16924,13 +16921,13 @@
         <v>714</v>
       </c>
       <c r="J19" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K19" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="L19" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="20" spans="2:12">
@@ -16953,13 +16950,13 @@
         <v>718</v>
       </c>
       <c r="J20" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K20" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="L20" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="21" spans="2:12">
@@ -16982,13 +16979,13 @@
         <v>719</v>
       </c>
       <c r="J21" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K21" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L21" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="22" spans="2:12">
@@ -17011,13 +17008,13 @@
         <v>720</v>
       </c>
       <c r="J22" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K22" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="L22" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="23" spans="2:12">
@@ -17040,13 +17037,13 @@
         <v>721</v>
       </c>
       <c r="J23" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K23" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L23" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="24" spans="2:12">
@@ -17069,13 +17066,13 @@
         <v>722</v>
       </c>
       <c r="J24" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K24" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="L24" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="25" spans="2:12">
@@ -17098,13 +17095,13 @@
         <v>723</v>
       </c>
       <c r="J25" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K25" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="L25" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -17127,13 +17124,13 @@
         <v>722</v>
       </c>
       <c r="J26" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K26" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="L26" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -17156,13 +17153,13 @@
         <v>722</v>
       </c>
       <c r="J27" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K27" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="L27" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="28" spans="2:12">
@@ -17185,13 +17182,13 @@
         <v>721</v>
       </c>
       <c r="J28" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K28" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="L28" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="29" spans="2:12">
@@ -17214,13 +17211,13 @@
         <v>724</v>
       </c>
       <c r="J29" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K29" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L29" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="30" spans="2:12">
@@ -17243,13 +17240,13 @@
         <v>725</v>
       </c>
       <c r="J30" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K30" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="L30" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="31" spans="2:12">
@@ -17272,13 +17269,13 @@
         <v>726</v>
       </c>
       <c r="J31" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K31" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="L31" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="32" spans="2:12">
@@ -17301,13 +17298,13 @@
         <v>727</v>
       </c>
       <c r="J32" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K32" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="L32" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="33" spans="2:12">
@@ -17330,13 +17327,13 @@
         <v>716</v>
       </c>
       <c r="J33" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K33" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="L33" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="34" spans="2:12">
@@ -17359,13 +17356,13 @@
         <v>714</v>
       </c>
       <c r="J34" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K34" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="L34" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="35" spans="2:12">
@@ -17388,13 +17385,13 @@
         <v>728</v>
       </c>
       <c r="J35" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K35" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="L35" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="36" spans="2:12">
@@ -17417,13 +17414,13 @@
         <v>729</v>
       </c>
       <c r="J36" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K36" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="L36" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="37" spans="2:12">
@@ -17446,13 +17443,13 @@
         <v>730</v>
       </c>
       <c r="J37" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K37" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="L37" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="38" spans="2:12">
@@ -17475,13 +17472,13 @@
         <v>716</v>
       </c>
       <c r="J38" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K38" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="L38" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -17504,13 +17501,13 @@
         <v>715</v>
       </c>
       <c r="J39" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K39" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="L39" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="40" spans="2:12">
@@ -17533,13 +17530,13 @@
         <v>715</v>
       </c>
       <c r="J40" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K40" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="L40" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="41" spans="2:12">
@@ -17562,13 +17559,13 @@
         <v>731</v>
       </c>
       <c r="J41" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K41" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="L41" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="42" spans="2:12">
@@ -17591,13 +17588,13 @@
         <v>728</v>
       </c>
       <c r="J42" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K42" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L42" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="43" spans="2:12">
@@ -17620,13 +17617,13 @@
         <v>721</v>
       </c>
       <c r="J43" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K43" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L43" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="44" spans="2:12">
@@ -17649,13 +17646,13 @@
         <v>732</v>
       </c>
       <c r="J44" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K44" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="L44" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="45" spans="2:12">
@@ -17678,13 +17675,13 @@
         <v>733</v>
       </c>
       <c r="J45" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K45" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L45" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="46" spans="2:12">
@@ -17707,13 +17704,13 @@
         <v>728</v>
       </c>
       <c r="J46" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K46" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L46" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="47" spans="2:12">
@@ -17736,13 +17733,13 @@
         <v>712</v>
       </c>
       <c r="J47" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K47" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="L47" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="48" spans="2:12">
@@ -17765,13 +17762,13 @@
         <v>721</v>
       </c>
       <c r="J48" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K48" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L48" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="49" spans="2:12">
@@ -17794,13 +17791,13 @@
         <v>730</v>
       </c>
       <c r="J49" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K49" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L49" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="50" spans="2:12">
@@ -17823,13 +17820,13 @@
         <v>734</v>
       </c>
       <c r="J50" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K50" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="L50" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="51" spans="2:12">
@@ -17852,13 +17849,13 @@
         <v>734</v>
       </c>
       <c r="J51" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K51" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="L51" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="52" spans="2:12">
@@ -17881,13 +17878,13 @@
         <v>729</v>
       </c>
       <c r="J52" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K52" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="L52" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="53" spans="2:12">
@@ -17910,13 +17907,13 @@
         <v>720</v>
       </c>
       <c r="J53" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K53" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="L53" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="54" spans="2:12">
@@ -17939,13 +17936,13 @@
         <v>721</v>
       </c>
       <c r="J54" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K54" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="L54" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="55" spans="2:12">
@@ -17968,13 +17965,13 @@
         <v>735</v>
       </c>
       <c r="J55" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K55" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="L55" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="56" spans="2:12">
@@ -17997,13 +17994,13 @@
         <v>736</v>
       </c>
       <c r="J56" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K56" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="L56" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="57" spans="2:12">
@@ -18026,13 +18023,13 @@
         <v>737</v>
       </c>
       <c r="J57" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K57" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="L57" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="58" spans="2:12">
@@ -18055,13 +18052,13 @@
         <v>737</v>
       </c>
       <c r="J58" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K58" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="L58" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="59" spans="2:12">
@@ -18084,13 +18081,13 @@
         <v>736</v>
       </c>
       <c r="J59" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K59" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="L59" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="60" spans="2:12">
@@ -18113,13 +18110,13 @@
         <v>738</v>
       </c>
       <c r="J60" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K60" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="L60" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="61" spans="2:12">
@@ -18142,13 +18139,13 @@
         <v>739</v>
       </c>
       <c r="J61" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K61" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="L61" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="62" spans="2:12">
@@ -18171,13 +18168,13 @@
         <v>740</v>
       </c>
       <c r="J62" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K62" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="L62" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="63" spans="2:12">
@@ -18200,13 +18197,13 @@
         <v>737</v>
       </c>
       <c r="J63" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K63" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="L63" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="64" spans="2:12">
@@ -18229,13 +18226,13 @@
         <v>730</v>
       </c>
       <c r="J64" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K64" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="L64" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="65" spans="2:12">
@@ -18258,13 +18255,13 @@
         <v>735</v>
       </c>
       <c r="J65" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K65" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="L65" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="66" spans="2:12">
@@ -18287,13 +18284,13 @@
         <v>722</v>
       </c>
       <c r="J66" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K66" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="L66" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="67" spans="2:12">
@@ -18316,13 +18313,13 @@
         <v>737</v>
       </c>
       <c r="J67" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K67" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="L67" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="68" spans="2:12">
@@ -18345,13 +18342,13 @@
         <v>741</v>
       </c>
       <c r="J68" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K68" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="L68" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="69" spans="2:12">
@@ -18374,13 +18371,13 @@
         <v>742</v>
       </c>
       <c r="J69" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K69" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="L69" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="70" spans="2:12">
@@ -18403,13 +18400,13 @@
         <v>742</v>
       </c>
       <c r="J70" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K70" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="L70" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="71" spans="2:12">
@@ -18432,13 +18429,13 @@
         <v>727</v>
       </c>
       <c r="J71" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K71" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="L71" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="72" spans="2:12">
@@ -18461,13 +18458,13 @@
         <v>740</v>
       </c>
       <c r="J72" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K72" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="L72" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="73" spans="2:12">
@@ -18490,13 +18487,13 @@
         <v>743</v>
       </c>
       <c r="J73" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K73" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="L73" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="74" spans="2:12">
@@ -18519,13 +18516,13 @@
         <v>744</v>
       </c>
       <c r="J74" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K74" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="L74" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="75" spans="2:12">
@@ -18548,13 +18545,13 @@
         <v>745</v>
       </c>
       <c r="J75" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K75" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="L75" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="76" spans="2:12">
@@ -18577,13 +18574,13 @@
         <v>746</v>
       </c>
       <c r="J76" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K76" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="L76" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="77" spans="2:12">
@@ -18606,13 +18603,13 @@
         <v>746</v>
       </c>
       <c r="J77" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K77" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="L77" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="78" spans="2:12">
@@ -18635,13 +18632,13 @@
         <v>720</v>
       </c>
       <c r="J78" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K78" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="L78" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="79" spans="2:12">
@@ -18664,13 +18661,13 @@
         <v>747</v>
       </c>
       <c r="J79" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K79" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="L79" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="80" spans="2:12">
@@ -18693,13 +18690,13 @@
         <v>720</v>
       </c>
       <c r="J80" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K80" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="L80" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="81" spans="2:12">
@@ -18722,13 +18719,13 @@
         <v>747</v>
       </c>
       <c r="J81" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K81" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="L81" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="82" spans="2:12">
@@ -18751,13 +18748,13 @@
         <v>748</v>
       </c>
       <c r="J82" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K82" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="L82" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="83" spans="2:12">
@@ -18780,13 +18777,13 @@
         <v>740</v>
       </c>
       <c r="J83" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K83" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="L83" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="84" spans="2:12">
@@ -18809,13 +18806,13 @@
         <v>741</v>
       </c>
       <c r="J84" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K84" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="L84" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="85" spans="2:12">
@@ -18838,13 +18835,13 @@
         <v>712</v>
       </c>
       <c r="J85" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K85" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="L85" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="86" spans="2:12">
@@ -18867,13 +18864,13 @@
         <v>714</v>
       </c>
       <c r="J86" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K86" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="L86" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="87" spans="2:12">
@@ -18896,13 +18893,13 @@
         <v>719</v>
       </c>
       <c r="J87" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K87" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="L87" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="88" spans="2:12">
@@ -18925,13 +18922,13 @@
         <v>749</v>
       </c>
       <c r="J88" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K88" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="L88" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="89" spans="2:12">
@@ -18954,13 +18951,13 @@
         <v>722</v>
       </c>
       <c r="J89" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K89" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="L89" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
     </row>
     <row r="90" spans="2:12">
@@ -18983,13 +18980,13 @@
         <v>716</v>
       </c>
       <c r="J90" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K90" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="L90" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="91" spans="2:12">
@@ -19012,13 +19009,13 @@
         <v>716</v>
       </c>
       <c r="J91" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K91" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="L91" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="92" spans="2:12">
@@ -19041,13 +19038,13 @@
         <v>750</v>
       </c>
       <c r="J92" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K92" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="L92" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="93" spans="2:12">
@@ -19070,13 +19067,13 @@
         <v>742</v>
       </c>
       <c r="J93" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K93" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="L93" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="94" spans="2:12">
@@ -19099,13 +19096,13 @@
         <v>751</v>
       </c>
       <c r="J94" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K94" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="L94" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="95" spans="2:12">
@@ -19128,13 +19125,13 @@
         <v>751</v>
       </c>
       <c r="J95" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K95" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="L95" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="96" spans="2:12">
@@ -19157,13 +19154,13 @@
         <v>731</v>
       </c>
       <c r="J96" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K96" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="L96" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="97" spans="2:12">
@@ -19186,13 +19183,13 @@
         <v>744</v>
       </c>
       <c r="J97" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K97" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="L97" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="98" spans="2:12">
@@ -19215,13 +19212,13 @@
         <v>731</v>
       </c>
       <c r="J98" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K98" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="L98" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="99" spans="2:12">
@@ -19244,13 +19241,13 @@
         <v>727</v>
       </c>
       <c r="J99" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K99" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="L99" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="100" spans="2:12">
@@ -19273,13 +19270,13 @@
         <v>712</v>
       </c>
       <c r="J100" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K100" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="L100" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="101" spans="2:12">
@@ -19302,13 +19299,13 @@
         <v>717</v>
       </c>
       <c r="J101" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K101" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="L101" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="102" spans="2:12">
@@ -19331,13 +19328,13 @@
         <v>752</v>
       </c>
       <c r="J102" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K102" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="L102" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="103" spans="2:12">
@@ -19360,13 +19357,13 @@
         <v>749</v>
       </c>
       <c r="J103" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K103" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="L103" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="104" spans="2:12">
@@ -19389,13 +19386,13 @@
         <v>717</v>
       </c>
       <c r="J104" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K104" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="L104" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="105" spans="2:12">
@@ -19418,13 +19415,13 @@
         <v>730</v>
       </c>
       <c r="J105" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K105" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="L105" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="106" spans="2:12">
@@ -19447,13 +19444,13 @@
         <v>714</v>
       </c>
       <c r="J106" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K106" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="L106" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="107" spans="2:12">
@@ -19476,13 +19473,13 @@
         <v>714</v>
       </c>
       <c r="J107" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K107" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="L107" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="108" spans="2:12">
@@ -19505,13 +19502,13 @@
         <v>750</v>
       </c>
       <c r="J108" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K108" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="L108" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="109" spans="2:12">
@@ -19534,13 +19531,13 @@
         <v>730</v>
       </c>
       <c r="J109" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K109" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="L109" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="110" spans="2:12">
@@ -19563,13 +19560,13 @@
         <v>752</v>
       </c>
       <c r="J110" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K110" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="L110" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="111" spans="2:12">
@@ -19592,13 +19589,13 @@
         <v>714</v>
       </c>
       <c r="J111" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K111" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="L111" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="112" spans="2:12">
@@ -19621,13 +19618,13 @@
         <v>736</v>
       </c>
       <c r="J112" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K112" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="L112" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="113" spans="2:12">
@@ -19650,13 +19647,13 @@
         <v>740</v>
       </c>
       <c r="J113" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K113" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="L113" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="114" spans="2:12">
@@ -19679,13 +19676,13 @@
         <v>728</v>
       </c>
       <c r="J114" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K114" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="L114" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="115" spans="2:12">
@@ -19708,13 +19705,13 @@
         <v>724</v>
       </c>
       <c r="J115" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K115" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="L115" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="116" spans="2:12">
@@ -19737,13 +19734,13 @@
         <v>750</v>
       </c>
       <c r="J116" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K116" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="L116" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="117" spans="2:12">
@@ -19766,13 +19763,13 @@
         <v>731</v>
       </c>
       <c r="J117" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K117" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="L117" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="118" spans="2:12">
@@ -19795,13 +19792,13 @@
         <v>716</v>
       </c>
       <c r="J118" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K118" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="L118" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="119" spans="2:12">
@@ -19824,13 +19821,13 @@
         <v>723</v>
       </c>
       <c r="J119" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K119" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="L119" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="120" spans="2:12">
@@ -19853,13 +19850,13 @@
         <v>733</v>
       </c>
       <c r="J120" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K120" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="L120" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="121" spans="2:12">
@@ -19882,13 +19879,13 @@
         <v>753</v>
       </c>
       <c r="J121" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K121" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="L121" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="122" spans="2:12">
@@ -19911,13 +19908,13 @@
         <v>753</v>
       </c>
       <c r="J122" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K122" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="L122" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="123" spans="2:12">
@@ -19940,13 +19937,13 @@
         <v>753</v>
       </c>
       <c r="J123" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K123" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="L123" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="124" spans="2:12">
@@ -19969,13 +19966,13 @@
         <v>715</v>
       </c>
       <c r="J124" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K124" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="L124" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="125" spans="2:12">
@@ -19998,13 +19995,13 @@
         <v>714</v>
       </c>
       <c r="J125" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K125" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="L125" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="126" spans="2:12">
@@ -20027,13 +20024,13 @@
         <v>726</v>
       </c>
       <c r="J126" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K126" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="L126" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="127" spans="2:12">
@@ -20056,13 +20053,13 @@
         <v>731</v>
       </c>
       <c r="J127" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K127" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="L127" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="128" spans="2:12">
@@ -20085,13 +20082,13 @@
         <v>750</v>
       </c>
       <c r="J128" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K128" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="L128" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="129" spans="2:12">
@@ -20114,13 +20111,13 @@
         <v>729</v>
       </c>
       <c r="J129" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K129" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="L129" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="130" spans="2:12">
@@ -20143,13 +20140,13 @@
         <v>734</v>
       </c>
       <c r="J130" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K130" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="L130" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="131" spans="2:12">
@@ -20172,13 +20169,13 @@
         <v>729</v>
       </c>
       <c r="J131" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K131" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="L131" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="132" spans="2:12">
@@ -20201,13 +20198,13 @@
         <v>720</v>
       </c>
       <c r="J132" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K132" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="L132" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="133" spans="2:12">
@@ -20230,13 +20227,13 @@
         <v>751</v>
       </c>
       <c r="J133" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K133" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="L133" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="134" spans="2:12">
@@ -20259,13 +20256,13 @@
         <v>716</v>
       </c>
       <c r="J134" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K134" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="L134" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="135" spans="2:12">
@@ -20288,13 +20285,13 @@
         <v>754</v>
       </c>
       <c r="J135" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K135" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="L135" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="136" spans="2:12">
@@ -20317,13 +20314,13 @@
         <v>717</v>
       </c>
       <c r="J136" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K136" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="L136" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="137" spans="2:12">
@@ -20346,13 +20343,13 @@
         <v>739</v>
       </c>
       <c r="J137" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K137" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="L137" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="138" spans="2:12">
@@ -20375,13 +20372,13 @@
         <v>730</v>
       </c>
       <c r="J138" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K138" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="L138" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="139" spans="2:12">
@@ -20404,13 +20401,13 @@
         <v>730</v>
       </c>
       <c r="J139" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K139" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="L139" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="140" spans="2:12">
@@ -20433,13 +20430,13 @@
         <v>730</v>
       </c>
       <c r="J140" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K140" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="L140" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="141" spans="2:12">
@@ -20462,13 +20459,13 @@
         <v>730</v>
       </c>
       <c r="J141" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K141" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="L141" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="142" spans="2:12">
@@ -20491,13 +20488,13 @@
         <v>752</v>
       </c>
       <c r="J142" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K142" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="L142" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="143" spans="2:12">
@@ -20520,13 +20517,13 @@
         <v>744</v>
       </c>
       <c r="J143" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K143" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="L143" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="144" spans="2:12">
@@ -20549,13 +20546,13 @@
         <v>744</v>
       </c>
       <c r="J144" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K144" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="L144" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="145" spans="2:12">
@@ -20578,13 +20575,13 @@
         <v>715</v>
       </c>
       <c r="J145" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K145" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="L145" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="146" spans="2:12">
@@ -20607,13 +20604,13 @@
         <v>715</v>
       </c>
       <c r="J146" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K146" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="L146" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="147" spans="2:12">
@@ -20636,13 +20633,13 @@
         <v>715</v>
       </c>
       <c r="J147" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K147" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="L147" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="148" spans="2:12">
@@ -20665,13 +20662,13 @@
         <v>747</v>
       </c>
       <c r="J148" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K148" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="L148" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="149" spans="2:12">
@@ -20694,13 +20691,13 @@
         <v>748</v>
       </c>
       <c r="J149" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K149" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="L149" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="150" spans="2:12">
@@ -20723,13 +20720,13 @@
         <v>752</v>
       </c>
       <c r="J150" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K150" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="L150" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="151" spans="2:12">
@@ -20752,13 +20749,13 @@
         <v>732</v>
       </c>
       <c r="J151" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K151" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="L151" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="152" spans="2:12">
@@ -20781,13 +20778,13 @@
         <v>715</v>
       </c>
       <c r="J152" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K152" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="L152" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="153" spans="2:12">
@@ -20810,13 +20807,13 @@
         <v>753</v>
       </c>
       <c r="J153" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K153" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="L153" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="154" spans="2:12">
@@ -20839,13 +20836,13 @@
         <v>750</v>
       </c>
       <c r="J154" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K154" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="L154" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="155" spans="2:12">
@@ -20868,13 +20865,13 @@
         <v>750</v>
       </c>
       <c r="J155" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K155" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="L155" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="156" spans="2:12">
@@ -20897,13 +20894,13 @@
         <v>731</v>
       </c>
       <c r="J156" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K156" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="L156" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="157" spans="2:12">
@@ -20926,13 +20923,13 @@
         <v>720</v>
       </c>
       <c r="J157" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K157" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="L157" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="158" spans="2:12">
@@ -20955,13 +20952,13 @@
         <v>750</v>
       </c>
       <c r="J158" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K158" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="L158" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="159" spans="2:12">
@@ -20984,13 +20981,13 @@
         <v>750</v>
       </c>
       <c r="J159" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K159" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="L159" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="160" spans="2:12">
@@ -21013,13 +21010,13 @@
         <v>749</v>
       </c>
       <c r="J160" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K160" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="L160" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="161" spans="2:12">
@@ -21042,13 +21039,13 @@
         <v>712</v>
       </c>
       <c r="J161" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K161" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="L161" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="162" spans="2:12">
@@ -21071,13 +21068,13 @@
         <v>720</v>
       </c>
       <c r="J162" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K162" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="L162" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="163" spans="2:12">
@@ -21100,13 +21097,13 @@
         <v>727</v>
       </c>
       <c r="J163" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K163" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="L163" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="164" spans="2:12">
@@ -21129,13 +21126,13 @@
         <v>746</v>
       </c>
       <c r="J164" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K164" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="L164" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="165" spans="2:12">
@@ -21158,13 +21155,13 @@
         <v>730</v>
       </c>
       <c r="J165" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K165" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="L165" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="166" spans="2:12">
@@ -21187,13 +21184,13 @@
         <v>720</v>
       </c>
       <c r="J166" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K166" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="L166" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="167" spans="2:12">
@@ -21216,13 +21213,13 @@
         <v>712</v>
       </c>
       <c r="J167" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K167" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="L167" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="168" spans="2:12">
@@ -21245,13 +21242,13 @@
         <v>712</v>
       </c>
       <c r="J168" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K168" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="L168" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="169" spans="2:12">
@@ -21274,13 +21271,13 @@
         <v>719</v>
       </c>
       <c r="J169" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K169" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="L169" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="170" spans="2:12">
@@ -21303,13 +21300,13 @@
         <v>720</v>
       </c>
       <c r="J170" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K170" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="L170" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="171" spans="2:12">
@@ -21332,13 +21329,13 @@
         <v>743</v>
       </c>
       <c r="J171" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K171" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="L171" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="172" spans="2:12">
@@ -21361,13 +21358,13 @@
         <v>733</v>
       </c>
       <c r="J172" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K172" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="L172" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="173" spans="2:12">
@@ -21390,13 +21387,13 @@
         <v>716</v>
       </c>
       <c r="J173" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K173" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="L173" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="174" spans="2:12">
@@ -21419,13 +21416,13 @@
         <v>716</v>
       </c>
       <c r="J174" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K174" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="L174" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="175" spans="2:12">
@@ -21448,13 +21445,13 @@
         <v>716</v>
       </c>
       <c r="J175" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K175" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="L175" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="176" spans="2:12">
@@ -21477,13 +21474,13 @@
         <v>716</v>
       </c>
       <c r="J176" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K176" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="L176" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="177" spans="2:12">
@@ -21506,13 +21503,13 @@
         <v>724</v>
       </c>
       <c r="J177" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K177" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="L177" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="178" spans="2:12">
@@ -21535,13 +21532,13 @@
         <v>724</v>
       </c>
       <c r="J178" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K178" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="L178" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="179" spans="2:12">
@@ -21564,13 +21561,13 @@
         <v>724</v>
       </c>
       <c r="J179" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K179" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="L179" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="180" spans="2:12">
@@ -21593,13 +21590,13 @@
         <v>724</v>
       </c>
       <c r="J180" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K180" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="L180" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="181" spans="2:12">
@@ -21622,13 +21619,13 @@
         <v>731</v>
       </c>
       <c r="J181" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K181" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="L181" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="182" spans="2:12">
@@ -21651,13 +21648,13 @@
         <v>712</v>
       </c>
       <c r="J182" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K182" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="L182" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="183" spans="2:12">
@@ -21680,13 +21677,13 @@
         <v>755</v>
       </c>
       <c r="J183" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K183" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="L183" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="184" spans="2:12">
@@ -21709,13 +21706,13 @@
         <v>755</v>
       </c>
       <c r="J184" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K184" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="L184" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="185" spans="2:12">
@@ -21738,13 +21735,13 @@
         <v>755</v>
       </c>
       <c r="J185" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K185" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="L185" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="186" spans="2:12">
@@ -21767,13 +21764,13 @@
         <v>755</v>
       </c>
       <c r="J186" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K186" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="L186" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="187" spans="2:12">
@@ -21796,13 +21793,13 @@
         <v>755</v>
       </c>
       <c r="J187" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K187" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="L187" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="188" spans="2:12">
@@ -21825,13 +21822,13 @@
         <v>755</v>
       </c>
       <c r="J188" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K188" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="L188" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="189" spans="2:12">
@@ -21854,13 +21851,13 @@
         <v>755</v>
       </c>
       <c r="J189" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K189" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="L189" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="190" spans="2:12">
@@ -21883,13 +21880,13 @@
         <v>755</v>
       </c>
       <c r="J190" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K190" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="L190" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="191" spans="2:12">
@@ -21912,13 +21909,13 @@
         <v>755</v>
       </c>
       <c r="J191" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K191" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="L191" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="192" spans="2:12">
@@ -21941,13 +21938,13 @@
         <v>755</v>
       </c>
       <c r="J192" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K192" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="L192" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="193" spans="2:12">
@@ -21970,13 +21967,13 @@
         <v>756</v>
       </c>
       <c r="J193" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K193" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="L193" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="194" spans="2:12">
@@ -21999,13 +21996,13 @@
         <v>740</v>
       </c>
       <c r="J194" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K194" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="L194" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="195" spans="2:12">
@@ -22025,16 +22022,16 @@
         <v>711</v>
       </c>
       <c r="H195" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="J195" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K195" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="L195" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="196" spans="2:12">
@@ -22054,16 +22051,16 @@
         <v>711</v>
       </c>
       <c r="H196" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="J196" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K196" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="L196" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="197" spans="2:12">
@@ -22086,13 +22083,13 @@
         <v>744</v>
       </c>
       <c r="J197" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K197" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="L197" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="198" spans="2:12">
@@ -22115,13 +22112,13 @@
         <v>721</v>
       </c>
       <c r="J198" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K198" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="L198" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="199" spans="2:12">
@@ -22141,16 +22138,16 @@
         <v>711</v>
       </c>
       <c r="H199" t="s">
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="J199" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K199" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="L199" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="200" spans="2:12">
@@ -22170,16 +22167,16 @@
         <v>711</v>
       </c>
       <c r="H200" t="s">
-        <v>746</v>
+        <v>720</v>
       </c>
       <c r="J200" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K200" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="L200" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="201" spans="2:12">
@@ -22199,16 +22196,16 @@
         <v>711</v>
       </c>
       <c r="H201" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="J201" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K201" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="L201" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="202" spans="2:12">
@@ -22228,16 +22225,16 @@
         <v>711</v>
       </c>
       <c r="H202" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="J202" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K202" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="L202" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="203" spans="2:12">
@@ -22257,16 +22254,16 @@
         <v>711</v>
       </c>
       <c r="H203" t="s">
-        <v>748</v>
+        <v>740</v>
       </c>
       <c r="J203" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K203" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="L203" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="204" spans="2:12">
@@ -22289,13 +22286,13 @@
         <v>755</v>
       </c>
       <c r="J204" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K204" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="L204" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="205" spans="2:12">
@@ -22318,13 +22315,13 @@
         <v>755</v>
       </c>
       <c r="J205" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K205" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="L205" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="206" spans="2:12">
@@ -22347,13 +22344,13 @@
         <v>755</v>
       </c>
       <c r="J206" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K206" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="L206" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="207" spans="2:12">
@@ -22373,16 +22370,16 @@
         <v>711</v>
       </c>
       <c r="H207" t="s">
-        <v>755</v>
+        <v>740</v>
       </c>
       <c r="J207" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K207" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="L207" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="208" spans="2:12">
@@ -22405,13 +22402,13 @@
         <v>755</v>
       </c>
       <c r="J208" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K208" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="L208" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="209" spans="2:12">
@@ -22434,13 +22431,13 @@
         <v>755</v>
       </c>
       <c r="J209" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K209" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="L209" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="210" spans="2:12">
@@ -22463,13 +22460,13 @@
         <v>755</v>
       </c>
       <c r="J210" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K210" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="L210" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="211" spans="2:12">
@@ -22492,13 +22489,13 @@
         <v>755</v>
       </c>
       <c r="J211" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K211" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="L211" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="212" spans="2:12">
@@ -22521,13 +22518,13 @@
         <v>755</v>
       </c>
       <c r="J212" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K212" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="L212" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="213" spans="2:12">
@@ -22547,16 +22544,16 @@
         <v>711</v>
       </c>
       <c r="H213" t="s">
-        <v>725</v>
+        <v>740</v>
       </c>
       <c r="J213" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K213" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="L213" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="214" spans="2:12">
@@ -22579,13 +22576,13 @@
         <v>723</v>
       </c>
       <c r="J214" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K214" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="L214" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="215" spans="2:12">
@@ -22605,16 +22602,16 @@
         <v>711</v>
       </c>
       <c r="H215" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="J215" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K215" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="L215" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="216" spans="2:12">
@@ -22634,16 +22631,16 @@
         <v>711</v>
       </c>
       <c r="H216" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
       <c r="J216" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K216" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="L216" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="217" spans="2:12">
@@ -22663,16 +22660,16 @@
         <v>711</v>
       </c>
       <c r="H217" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="J217" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K217" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L217" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="218" spans="2:12">
@@ -22695,13 +22692,13 @@
         <v>732</v>
       </c>
       <c r="J218" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K218" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="L218" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="219" spans="2:12">
@@ -22721,16 +22718,16 @@
         <v>711</v>
       </c>
       <c r="H219" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="J219" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K219" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="L219" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="220" spans="2:12">
@@ -22753,13 +22750,13 @@
         <v>757</v>
       </c>
       <c r="J220" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K220" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="L220" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="221" spans="2:12">
@@ -22782,13 +22779,13 @@
         <v>738</v>
       </c>
       <c r="J221" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K221" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="L221" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="222" spans="2:12">
@@ -22811,13 +22808,13 @@
         <v>717</v>
       </c>
       <c r="J222" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K222" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="L222" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="223" spans="2:12">
@@ -22840,13 +22837,13 @@
         <v>740</v>
       </c>
       <c r="J223" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K223" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="L223" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="224" spans="2:12">
@@ -22866,16 +22863,16 @@
         <v>711</v>
       </c>
       <c r="H224" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="J224" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K224" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="L224" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="225" spans="2:12">
@@ -22898,13 +22895,13 @@
         <v>741</v>
       </c>
       <c r="J225" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K225" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="L225" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="226" spans="2:12">
@@ -22924,16 +22921,16 @@
         <v>711</v>
       </c>
       <c r="H226" t="s">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="J226" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K226" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="L226" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="227" spans="2:12">
@@ -22953,16 +22950,16 @@
         <v>711</v>
       </c>
       <c r="H227" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="J227" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K227" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="L227" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="228" spans="2:12">
@@ -22985,13 +22982,13 @@
         <v>744</v>
       </c>
       <c r="J228" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K228" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="L228" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="229" spans="2:12">
@@ -23014,13 +23011,13 @@
         <v>721</v>
       </c>
       <c r="J229" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K229" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="L229" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="230" spans="2:12">
@@ -23043,13 +23040,13 @@
         <v>734</v>
       </c>
       <c r="J230" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K230" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="L230" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="231" spans="2:12">
@@ -23072,13 +23069,13 @@
         <v>730</v>
       </c>
       <c r="J231" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K231" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="L231" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="232" spans="2:12">
@@ -23101,13 +23098,13 @@
         <v>749</v>
       </c>
       <c r="J232" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K232" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="L232" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="233" spans="2:12">
@@ -23127,16 +23124,16 @@
         <v>711</v>
       </c>
       <c r="H233" t="s">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="J233" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K233" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="L233" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="234" spans="2:12">
@@ -23156,16 +23153,16 @@
         <v>711</v>
       </c>
       <c r="H234" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="J234" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K234" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="L234" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="235" spans="2:12">
@@ -23188,13 +23185,13 @@
         <v>716</v>
       </c>
       <c r="J235" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K235" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="L235" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="236" spans="2:12">
@@ -23214,16 +23211,16 @@
         <v>711</v>
       </c>
       <c r="H236" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="J236" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K236" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="L236" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="237" spans="2:12">
@@ -23243,16 +23240,16 @@
         <v>711</v>
       </c>
       <c r="H237" t="s">
-        <v>727</v>
+        <v>740</v>
       </c>
       <c r="J237" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K237" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="L237" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="238" spans="2:12">
@@ -23272,16 +23269,16 @@
         <v>711</v>
       </c>
       <c r="H238" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="J238" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K238" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="L238" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="239" spans="2:12">
@@ -23301,16 +23298,16 @@
         <v>711</v>
       </c>
       <c r="H239" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="J239" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K239" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="L239" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="240" spans="2:12">
@@ -23330,16 +23327,16 @@
         <v>711</v>
       </c>
       <c r="H240" t="s">
-        <v>758</v>
+        <v>740</v>
       </c>
       <c r="J240" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K240" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="L240" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="241" spans="2:12">
@@ -23359,16 +23356,16 @@
         <v>711</v>
       </c>
       <c r="H241" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="J241" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K241" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="L241" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="242" spans="2:12">
@@ -23388,16 +23385,16 @@
         <v>711</v>
       </c>
       <c r="H242" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
       <c r="J242" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K242" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="L242" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="243" spans="2:12">
@@ -23417,16 +23414,16 @@
         <v>711</v>
       </c>
       <c r="H243" t="s">
-        <v>714</v>
+        <v>740</v>
       </c>
       <c r="J243" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K243" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="L243" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="244" spans="2:12">
@@ -23449,13 +23446,13 @@
         <v>715</v>
       </c>
       <c r="J244" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K244" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="L244" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="245" spans="2:12">
@@ -23478,13 +23475,13 @@
         <v>714</v>
       </c>
       <c r="J245" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K245" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="L245" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="246" spans="2:12">
@@ -23507,13 +23504,13 @@
         <v>738</v>
       </c>
       <c r="J246" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K246" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="L246" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="247" spans="2:12">
@@ -23536,13 +23533,13 @@
         <v>755</v>
       </c>
       <c r="J247" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K247" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="L247" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="248" spans="2:12">
@@ -23562,16 +23559,16 @@
         <v>711</v>
       </c>
       <c r="H248" t="s">
-        <v>755</v>
+        <v>740</v>
       </c>
       <c r="J248" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K248" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="L248" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="249" spans="2:12">
@@ -23594,13 +23591,13 @@
         <v>738</v>
       </c>
       <c r="J249" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K249" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="L249" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="250" spans="2:12">
@@ -23623,13 +23620,13 @@
         <v>755</v>
       </c>
       <c r="J250" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K250" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="L250" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="251" spans="2:12">
@@ -23652,13 +23649,13 @@
         <v>755</v>
       </c>
       <c r="J251" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K251" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="L251" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="252" spans="2:12">
@@ -23681,13 +23678,13 @@
         <v>755</v>
       </c>
       <c r="J252" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K252" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="L252" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="253" spans="2:12">
@@ -23710,13 +23707,13 @@
         <v>755</v>
       </c>
       <c r="J253" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K253" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="L253" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="254" spans="2:12">
@@ -23739,13 +23736,13 @@
         <v>740</v>
       </c>
       <c r="J254" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K254" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="L254" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="255" spans="2:12">
@@ -23768,13 +23765,13 @@
         <v>740</v>
       </c>
       <c r="J255" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K255" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="L255" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="256" spans="2:12">
@@ -23797,13 +23794,13 @@
         <v>740</v>
       </c>
       <c r="J256" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K256" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="L256" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="257" spans="2:12">
@@ -23823,16 +23820,16 @@
         <v>711</v>
       </c>
       <c r="H257" t="s">
-        <v>740</v>
+        <v>756</v>
       </c>
       <c r="J257" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K257" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="L257" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="258" spans="2:12">
@@ -23855,13 +23852,13 @@
         <v>740</v>
       </c>
       <c r="J258" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K258" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="L258" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="259" spans="2:12">
@@ -23884,13 +23881,13 @@
         <v>740</v>
       </c>
       <c r="J259" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K259" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="L259" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="260" spans="2:12">
@@ -23913,13 +23910,13 @@
         <v>740</v>
       </c>
       <c r="J260" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K260" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="L260" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="261" spans="2:12">
@@ -23942,13 +23939,13 @@
         <v>740</v>
       </c>
       <c r="J261" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K261" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="L261" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="262" spans="2:12">
@@ -23968,16 +23965,16 @@
         <v>711</v>
       </c>
       <c r="H262" t="s">
-        <v>740</v>
+        <v>719</v>
       </c>
       <c r="J262" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K262" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="L262" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="263" spans="2:12">
@@ -24000,13 +23997,13 @@
         <v>740</v>
       </c>
       <c r="J263" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K263" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="L263" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="264" spans="2:12">
@@ -24029,13 +24026,13 @@
         <v>740</v>
       </c>
       <c r="J264" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K264" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="L264" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="265" spans="2:12">
@@ -24058,13 +24055,13 @@
         <v>740</v>
       </c>
       <c r="J265" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K265" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="L265" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="266" spans="2:12">
@@ -24087,13 +24084,13 @@
         <v>740</v>
       </c>
       <c r="J266" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K266" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="L266" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="267" spans="2:12">
@@ -24116,13 +24113,13 @@
         <v>740</v>
       </c>
       <c r="J267" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K267" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="L267" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="268" spans="2:12">
@@ -24145,13 +24142,13 @@
         <v>740</v>
       </c>
       <c r="J268" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K268" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="L268" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="269" spans="2:12">
@@ -24171,16 +24168,16 @@
         <v>711</v>
       </c>
       <c r="H269" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
       <c r="J269" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K269" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="L269" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="270" spans="2:12">
@@ -24203,13 +24200,13 @@
         <v>740</v>
       </c>
       <c r="J270" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K270" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="L270" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="271" spans="2:12">
@@ -24232,13 +24229,13 @@
         <v>740</v>
       </c>
       <c r="J271" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K271" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="L271" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="272" spans="2:12">
@@ -24261,13 +24258,13 @@
         <v>740</v>
       </c>
       <c r="J272" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K272" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="L272" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="273" spans="2:12">
@@ -24290,13 +24287,13 @@
         <v>740</v>
       </c>
       <c r="J273" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K273" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="L273" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="274" spans="2:12">
@@ -24319,13 +24316,13 @@
         <v>740</v>
       </c>
       <c r="J274" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K274" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="L274" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="275" spans="2:12">
@@ -24348,13 +24345,13 @@
         <v>740</v>
       </c>
       <c r="J275" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K275" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="L275" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="276" spans="2:12">
@@ -24377,13 +24374,13 @@
         <v>740</v>
       </c>
       <c r="J276" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K276" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="L276" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="277" spans="2:12">
@@ -24406,13 +24403,13 @@
         <v>740</v>
       </c>
       <c r="J277" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K277" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="L277" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="278" spans="2:12">
@@ -24435,13 +24432,13 @@
         <v>740</v>
       </c>
       <c r="J278" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K278" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="L278" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="279" spans="2:12">
@@ -24464,13 +24461,13 @@
         <v>740</v>
       </c>
       <c r="J279" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K279" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="L279" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="280" spans="2:12">
@@ -24493,13 +24490,13 @@
         <v>740</v>
       </c>
       <c r="J280" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K280" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="L280" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="281" spans="2:12">
@@ -24522,13 +24519,13 @@
         <v>740</v>
       </c>
       <c r="J281" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K281" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="L281" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="282" spans="2:12">
@@ -24551,13 +24548,13 @@
         <v>740</v>
       </c>
       <c r="J282" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K282" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="L282" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="283" spans="2:12">
@@ -24580,13 +24577,13 @@
         <v>740</v>
       </c>
       <c r="J283" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K283" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="L283" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="284" spans="2:12">
@@ -24609,13 +24606,13 @@
         <v>740</v>
       </c>
       <c r="J284" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K284" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="L284" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="285" spans="2:12">
@@ -24638,13 +24635,13 @@
         <v>740</v>
       </c>
       <c r="J285" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K285" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="L285" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="286" spans="2:12">
@@ -24667,13 +24664,13 @@
         <v>740</v>
       </c>
       <c r="J286" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K286" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="L286" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="287" spans="2:12">
@@ -24696,13 +24693,13 @@
         <v>740</v>
       </c>
       <c r="J287" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K287" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="L287" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="288" spans="2:12">
@@ -24725,13 +24722,13 @@
         <v>740</v>
       </c>
       <c r="J288" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K288" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="L288" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="289" spans="2:12">
@@ -24754,13 +24751,13 @@
         <v>740</v>
       </c>
       <c r="J289" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K289" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="L289" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="290" spans="2:12">
@@ -24783,13 +24780,13 @@
         <v>740</v>
       </c>
       <c r="J290" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K290" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="L290" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="291" spans="2:12">
@@ -24812,13 +24809,13 @@
         <v>740</v>
       </c>
       <c r="J291" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K291" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="L291" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="292" spans="2:12">
@@ -24841,13 +24838,13 @@
         <v>740</v>
       </c>
       <c r="J292" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K292" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="L292" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="293" spans="2:12">
@@ -24870,13 +24867,13 @@
         <v>740</v>
       </c>
       <c r="J293" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K293" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="L293" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="294" spans="2:12">
@@ -24899,13 +24896,13 @@
         <v>740</v>
       </c>
       <c r="J294" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K294" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="L294" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="295" spans="2:12">
@@ -24928,13 +24925,13 @@
         <v>740</v>
       </c>
       <c r="J295" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K295" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="L295" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="296" spans="2:12">
@@ -24957,13 +24954,13 @@
         <v>740</v>
       </c>
       <c r="J296" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K296" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="L296" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="297" spans="2:12">
@@ -24983,71 +24980,71 @@
         <v>711</v>
       </c>
       <c r="H297" t="s">
-        <v>740</v>
+        <v>716</v>
       </c>
       <c r="J297" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K297" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="L297" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="298" spans="2:12">
       <c r="J298" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K298" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="L298" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="299" spans="2:12">
       <c r="J299" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K299" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="L299" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="300" spans="2:12">
       <c r="J300" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K300" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="L300" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="301" spans="2:12">
       <c r="J301" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K301" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="L301" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="302" spans="2:12">
       <c r="J302" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K302" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="L302" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_JPN_grids/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_JPN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7E52288-0F52-44B9-86A5-1F123A09065A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD26ACD0-6C5A-40E3-8C50-709133EE9EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4056" uniqueCount="1347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4056" uniqueCount="1348">
   <si>
     <t>Unit</t>
   </si>
@@ -2358,6 +2358,9 @@
   </si>
   <si>
     <t>Akita</t>
+  </si>
+  <si>
+    <t>Kōchi</t>
   </si>
   <si>
     <t>region_com</t>
@@ -10792,36 +10795,36 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C094C7AC-79A3-4491-BBED-E672EA6B5667}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{397E48EA-2EEC-4ABF-ACF0-9C3EAFCDDB18}">
   <dimension ref="B9:H302"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="9" spans="2:8">
       <c r="B9" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="F9" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="10" spans="2:8">
       <c r="B10" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="C10" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F10" t="s">
         <v>1053</v>
       </c>
-      <c r="D10" t="s">
+      <c r="G10" t="s">
         <v>1054</v>
       </c>
-      <c r="F10" t="s">
-        <v>1052</v>
-      </c>
-      <c r="G10" t="s">
-        <v>1053</v>
-      </c>
       <c r="H10" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="11" spans="2:8">
@@ -10835,7 +10838,7 @@
         <v>138.80177043536111</v>
       </c>
       <c r="F11" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="G11">
         <v>36.623159551188849</v>
@@ -10855,7 +10858,7 @@
         <v>133.95401090047395</v>
       </c>
       <c r="F12" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="G12">
         <v>34.16492140881175</v>
@@ -10875,7 +10878,7 @@
         <v>133.86250228190178</v>
       </c>
       <c r="F13" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="G13">
         <v>34.302173069560816</v>
@@ -10895,7 +10898,7 @@
         <v>141.02183643624105</v>
       </c>
       <c r="F14" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="G14">
         <v>37.316218892491598</v>
@@ -10915,7 +10918,7 @@
         <v>140.72295560659705</v>
       </c>
       <c r="F15" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="G15">
         <v>37.141850931652939</v>
@@ -10935,7 +10938,7 @@
         <v>139.91772358683002</v>
       </c>
       <c r="F16" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="G16">
         <v>36.65527049556583</v>
@@ -10955,7 +10958,7 @@
         <v>140.45810292549854</v>
       </c>
       <c r="F17" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="G17">
         <v>35.865258454640866</v>
@@ -10975,7 +10978,7 @@
         <v>140.84893075302352</v>
       </c>
       <c r="F18" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="G18">
         <v>38.604776865796879</v>
@@ -10995,7 +10998,7 @@
         <v>140.96068542100087</v>
       </c>
       <c r="F19" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="G19">
         <v>37.359425564472978</v>
@@ -11015,7 +11018,7 @@
         <v>135.58694108806569</v>
       </c>
       <c r="F20" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="G20">
         <v>34.402512992032868</v>
@@ -11035,7 +11038,7 @@
         <v>135.50211531023922</v>
       </c>
       <c r="F21" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="G21">
         <v>34.213923715840174</v>
@@ -11055,7 +11058,7 @@
         <v>135.3461014713138</v>
       </c>
       <c r="F22" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="G22">
         <v>34.984222780255479</v>
@@ -11075,7 +11078,7 @@
         <v>137.70854060707654</v>
       </c>
       <c r="F23" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="G23">
         <v>35.07143216942076</v>
@@ -11095,7 +11098,7 @@
         <v>139.4364465197805</v>
       </c>
       <c r="F24" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="G24">
         <v>35.962037835496112</v>
@@ -11115,7 +11118,7 @@
         <v>139.90353088187334</v>
       </c>
       <c r="F25" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G25">
         <v>36.167130274968521</v>
@@ -11135,7 +11138,7 @@
         <v>139.37072375217352</v>
       </c>
       <c r="F26" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="G26">
         <v>35.928728165249211</v>
@@ -11155,7 +11158,7 @@
         <v>139.23954260184681</v>
       </c>
       <c r="F27" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="G27">
         <v>35.851788162102174</v>
@@ -11175,7 +11178,7 @@
         <v>137.72908932599771</v>
       </c>
       <c r="F28" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="G28">
         <v>35.162272886797354</v>
@@ -11195,7 +11198,7 @@
         <v>139.22338930422998</v>
       </c>
       <c r="F29" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="G29">
         <v>35.71470374426972</v>
@@ -11215,7 +11218,7 @@
         <v>139.22566862063019</v>
       </c>
       <c r="F30" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="G30">
         <v>35.400444620287395</v>
@@ -11235,7 +11238,7 @@
         <v>138.79989115700727</v>
       </c>
       <c r="F31" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="G31">
         <v>35.590726684810875</v>
@@ -11255,7 +11258,7 @@
         <v>138.96317390902462</v>
       </c>
       <c r="F32" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="G32">
         <v>35.372238518852974</v>
@@ -11275,7 +11278,7 @@
         <v>140.16653208165212</v>
       </c>
       <c r="F33" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="G33">
         <v>35.499051212291768</v>
@@ -11295,7 +11298,7 @@
         <v>140.9495383195725</v>
       </c>
       <c r="F34" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G34">
         <v>37.535340448744797</v>
@@ -11315,7 +11318,7 @@
         <v>135.71481347221845</v>
       </c>
       <c r="F35" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G35">
         <v>34.734669337370775</v>
@@ -11335,7 +11338,7 @@
         <v>135.89763769563652</v>
       </c>
       <c r="F36" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="G36">
         <v>34.865486852490449</v>
@@ -11355,7 +11358,7 @@
         <v>136.93748324308584</v>
       </c>
       <c r="F37" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="G37">
         <v>35.527092198043391</v>
@@ -11375,7 +11378,7 @@
         <v>140.06957983959583</v>
       </c>
       <c r="F38" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="G38">
         <v>35.781310478950395</v>
@@ -11395,7 +11398,7 @@
         <v>140.15286635448939</v>
       </c>
       <c r="F39" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="G39">
         <v>36.52251279266028</v>
@@ -11415,7 +11418,7 @@
         <v>139.83246221583255</v>
       </c>
       <c r="F40" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="G40">
         <v>36.712761848859408</v>
@@ -11435,7 +11438,7 @@
         <v>135.61912454072566</v>
       </c>
       <c r="F41" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="G41">
         <v>34.96965036789733</v>
@@ -11455,7 +11458,7 @@
         <v>135.90243240056623</v>
       </c>
       <c r="F42" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="G42">
         <v>34.448778413299458</v>
@@ -11475,7 +11478,7 @@
         <v>137.26239319012302</v>
       </c>
       <c r="F43" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="G43">
         <v>35.105965944995894</v>
@@ -11495,7 +11498,7 @@
         <v>136.82594005142843</v>
       </c>
       <c r="F44" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="G44">
         <v>36.499195713422203</v>
@@ -11515,7 +11518,7 @@
         <v>136.7170002183575</v>
       </c>
       <c r="F45" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="G45">
         <v>36.500393255821443</v>
@@ -11535,7 +11538,7 @@
         <v>135.64795104006993</v>
       </c>
       <c r="F46" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="G46">
         <v>34.5973116203552</v>
@@ -11555,7 +11558,7 @@
         <v>138.83246934123443</v>
       </c>
       <c r="F47" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="G47">
         <v>36.547838660667693</v>
@@ -11575,7 +11578,7 @@
         <v>137.45239068692709</v>
       </c>
       <c r="F48" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="G48">
         <v>34.890777361936721</v>
@@ -11595,7 +11598,7 @@
         <v>136.96265986651665</v>
       </c>
       <c r="F49" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="G49">
         <v>35.635668447344635</v>
@@ -11615,7 +11618,7 @@
         <v>136.51456115331234</v>
       </c>
       <c r="F50" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="G50">
         <v>35.193003060430279</v>
@@ -11635,7 +11638,7 @@
         <v>136.45106186446196</v>
       </c>
       <c r="F51" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="G51">
         <v>35.203342007191587</v>
@@ -11655,7 +11658,7 @@
         <v>136.29336601111871</v>
       </c>
       <c r="F52" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G52">
         <v>35.095109605490656</v>
@@ -11675,7 +11678,7 @@
         <v>135.11013357438321</v>
       </c>
       <c r="F53" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="G53">
         <v>34.931631944821412</v>
@@ -11695,7 +11698,7 @@
         <v>137.29809780148221</v>
       </c>
       <c r="F54" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="G54">
         <v>35.210233689303443</v>
@@ -11715,7 +11718,7 @@
         <v>132.70939419496085</v>
       </c>
       <c r="F55" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="G55">
         <v>34.488899953033631</v>
@@ -11735,7 +11738,7 @@
         <v>133.39500139141035</v>
       </c>
       <c r="F56" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="G56">
         <v>33.944279016269924</v>
@@ -11755,7 +11758,7 @@
         <v>130.62404746626811</v>
       </c>
       <c r="F57" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="G57">
         <v>33.491618269579163</v>
@@ -11775,7 +11778,7 @@
         <v>130.36472007060911</v>
       </c>
       <c r="F58" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="G58">
         <v>33.470083483004061</v>
@@ -11795,7 +11798,7 @@
         <v>132.92821331235666</v>
       </c>
       <c r="F59" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="G59">
         <v>33.79201549752927</v>
@@ -11815,7 +11818,7 @@
         <v>141.17616155822515</v>
       </c>
       <c r="F60" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="G60">
         <v>39.90505248701556</v>
@@ -11835,7 +11838,7 @@
         <v>129.92909232659014</v>
       </c>
       <c r="F61" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="G61">
         <v>33.350251889794762</v>
@@ -11855,7 +11858,7 @@
         <v>129.83491441267549</v>
       </c>
       <c r="F62" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="G62">
         <v>33.515582068392803</v>
@@ -11875,7 +11878,7 @@
         <v>130.80444891114544</v>
       </c>
       <c r="F63" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="G63">
         <v>33.809905742139442</v>
@@ -11895,7 +11898,7 @@
         <v>136.72358330816681</v>
       </c>
       <c r="F64" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="G64">
         <v>35.584257599900546</v>
@@ -11915,7 +11918,7 @@
         <v>132.25764638741936</v>
       </c>
       <c r="F65" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="G65">
         <v>34.412363937355089</v>
@@ -11935,7 +11938,7 @@
         <v>138.93642749968816</v>
       </c>
       <c r="F66" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="G66">
         <v>36.031277392158273</v>
@@ -11955,7 +11958,7 @@
         <v>131.01563614443441</v>
       </c>
       <c r="F67" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="G67">
         <v>33.607991608822481</v>
@@ -11975,7 +11978,7 @@
         <v>131.0932403187953</v>
       </c>
       <c r="F68" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="G68">
         <v>34.163080826303833</v>
@@ -11995,7 +11998,7 @@
         <v>137.99699148650129</v>
       </c>
       <c r="F69" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="G69">
         <v>35.710010548181799</v>
@@ -12015,7 +12018,7 @@
         <v>137.98740065939847</v>
       </c>
       <c r="F70" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="G70">
         <v>36.063822401692441</v>
@@ -12035,7 +12038,7 @@
         <v>138.06316947909724</v>
       </c>
       <c r="F71" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="G71">
         <v>34.808204237724084</v>
@@ -12055,7 +12058,7 @@
         <v>139.98010146039354</v>
       </c>
       <c r="F72" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="G72">
         <v>35.463760116184766</v>
@@ -12075,7 +12078,7 @@
         <v>130.65571883093563</v>
       </c>
       <c r="F73" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="G73">
         <v>31.957566960028267</v>
@@ -12095,7 +12098,7 @@
         <v>130.79932246595934</v>
       </c>
       <c r="F74" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="G74">
         <v>32.614196415120603</v>
@@ -12115,7 +12118,7 @@
         <v>131.72943865137833</v>
       </c>
       <c r="F75" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="G75">
         <v>33.13401562004119</v>
@@ -12135,7 +12138,7 @@
         <v>131.38565953692876</v>
       </c>
       <c r="F76" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="G76">
         <v>32.250790927091856</v>
@@ -12155,7 +12158,7 @@
         <v>131.1942495227193</v>
       </c>
       <c r="F77" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="G77">
         <v>31.921816379278063</v>
@@ -12175,7 +12178,7 @@
         <v>134.6016239057528</v>
       </c>
       <c r="F78" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="G78">
         <v>35.063269231517701</v>
@@ -12195,7 +12198,7 @@
         <v>134.02522903294857</v>
       </c>
       <c r="F79" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="G79">
         <v>34.887992263344749</v>
@@ -12215,7 +12218,7 @@
         <v>134.42591403567502</v>
       </c>
       <c r="F80" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="G80">
         <v>34.861843414722763</v>
@@ -12235,7 +12238,7 @@
         <v>133.38849243239446</v>
       </c>
       <c r="F81" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="G81">
         <v>34.803558863629867</v>
@@ -12255,7 +12258,7 @@
         <v>133.40586917675526</v>
       </c>
       <c r="F82" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="G82">
         <v>35.295973542322862</v>
@@ -12275,7 +12278,7 @@
         <v>133.78319068983876</v>
       </c>
       <c r="F83" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G83">
         <v>34.457906539847727</v>
@@ -12295,7 +12298,7 @@
         <v>131.82627354738659</v>
       </c>
       <c r="F84" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="G84">
         <v>34.200093958841528</v>
@@ -12315,7 +12318,7 @@
         <v>139.22353939760555</v>
       </c>
       <c r="F85" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G85">
         <v>36.57931508910017</v>
@@ -12335,7 +12338,7 @@
         <v>140.80525197784883</v>
       </c>
       <c r="F86" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="G86">
         <v>37.381807329228366</v>
@@ -12355,7 +12358,7 @@
         <v>135.33715318384688</v>
       </c>
       <c r="F87" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="G87">
         <v>34.211616497136646</v>
@@ -12375,7 +12378,7 @@
         <v>134.40861283503324</v>
       </c>
       <c r="F88" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="G88">
         <v>34.000763351330342</v>
@@ -12395,7 +12398,7 @@
         <v>139.21300372758429</v>
       </c>
       <c r="F89" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="G89">
         <v>36.219906325405837</v>
@@ -12415,7 +12418,7 @@
         <v>139.83661319523603</v>
       </c>
       <c r="F90" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="G90">
         <v>35.343898881203259</v>
@@ -12435,7 +12438,7 @@
         <v>140.02788035567903</v>
       </c>
       <c r="F91" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="G91">
         <v>35.343352324848951</v>
@@ -12455,7 +12458,7 @@
         <v>136.41546992363067</v>
       </c>
       <c r="F92" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="G92">
         <v>35.996020957962997</v>
@@ -12475,7 +12478,7 @@
         <v>137.88397061557541</v>
       </c>
       <c r="F93" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="G93">
         <v>36.137503274067335</v>
@@ -12495,7 +12498,7 @@
         <v>131.97979992173993</v>
       </c>
       <c r="F94" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="G94">
         <v>34.697486518391401</v>
@@ -12515,7 +12518,7 @@
         <v>133.11610242421423</v>
       </c>
       <c r="F95" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="G95">
         <v>35.470241157388045</v>
@@ -12535,7 +12538,7 @@
         <v>135.48469961836187</v>
       </c>
       <c r="F96" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="G96">
         <v>34.990387052647066</v>
@@ -12555,7 +12558,7 @@
         <v>130.90270499954008</v>
       </c>
       <c r="F97" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="G97">
         <v>32.909226897681798</v>
@@ -12575,7 +12578,7 @@
         <v>135.64462162700926</v>
       </c>
       <c r="F98" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="G98">
         <v>35.136785367773712</v>
@@ -12595,7 +12598,7 @@
         <v>138.04906886461768</v>
       </c>
       <c r="F99" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="G99">
         <v>34.863332048008239</v>
@@ -12615,7 +12618,7 @@
         <v>139.30483820209852</v>
       </c>
       <c r="F100" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="G100">
         <v>36.326085164714421</v>
@@ -12635,7 +12638,7 @@
         <v>140.64403184405094</v>
       </c>
       <c r="F101" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="G101">
         <v>38.254801587089091</v>
@@ -12655,7 +12658,7 @@
         <v>141.17318529712139</v>
       </c>
       <c r="F102" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="G102">
         <v>40.78296544539743</v>
@@ -12675,7 +12678,7 @@
         <v>134.63656431903473</v>
       </c>
       <c r="F103" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="G103">
         <v>33.827824780612865</v>
@@ -12695,7 +12698,7 @@
         <v>140.75152492552408</v>
       </c>
       <c r="F104" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="G104">
         <v>38.352304032247361</v>
@@ -12715,7 +12718,7 @@
         <v>136.6608688257156</v>
       </c>
       <c r="F105" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="G105">
         <v>35.735051436097457</v>
@@ -12735,7 +12738,7 @@
         <v>140.94904314929377</v>
       </c>
       <c r="F106" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="G106">
         <v>37.85105814374495</v>
@@ -12755,7 +12758,7 @@
         <v>140.94113293098712</v>
       </c>
       <c r="F107" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="G107">
         <v>37.844730745516557</v>
@@ -12775,7 +12778,7 @@
         <v>136.02064253754861</v>
       </c>
       <c r="F108" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="G108">
         <v>35.751901182366495</v>
@@ -12795,7 +12798,7 @@
         <v>137.05971491227285</v>
       </c>
       <c r="F109" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="G109">
         <v>36.070189422281686</v>
@@ -12815,7 +12818,7 @@
         <v>141.38653983141012</v>
       </c>
       <c r="F110" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="G110">
         <v>41.187613246344768</v>
@@ -12835,7 +12838,7 @@
         <v>139.90848727441983</v>
       </c>
       <c r="F111" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="G111">
         <v>37.344902507375927</v>
@@ -12855,7 +12858,7 @@
         <v>132.31197455192955</v>
       </c>
       <c r="F112" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="G112">
         <v>33.488989843085079</v>
@@ -12875,7 +12878,7 @@
         <v>135.15440900189861</v>
       </c>
       <c r="F113" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="G113">
         <v>33.860371739222863</v>
@@ -12895,7 +12898,7 @@
         <v>135.82246848008975</v>
       </c>
       <c r="F114" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="G114">
         <v>34.112988242957435</v>
@@ -12915,7 +12918,7 @@
         <v>139.79080912025844</v>
       </c>
       <c r="F115" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="G115">
         <v>35.647882725800528</v>
@@ -12935,7 +12938,7 @@
         <v>135.9722405327953</v>
       </c>
       <c r="F116" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="G116">
         <v>35.556434741181334</v>
@@ -12955,7 +12958,7 @@
         <v>135.26635354845138</v>
       </c>
       <c r="F117" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="G117">
         <v>35.351099606986459</v>
@@ -12975,7 +12978,7 @@
         <v>139.91058845823864</v>
       </c>
       <c r="F118" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="G118">
         <v>35.930809236247349</v>
@@ -12995,7 +12998,7 @@
         <v>139.83263097329305</v>
       </c>
       <c r="F119" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="G119">
         <v>36.106697327015418</v>
@@ -13015,7 +13018,7 @@
         <v>136.83804195925802</v>
       </c>
       <c r="F120" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="G120">
         <v>36.995998879309816</v>
@@ -13035,7 +13038,7 @@
         <v>138.59820514421614</v>
       </c>
       <c r="F121" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="G121">
         <v>37.425338985543583</v>
@@ -13055,7 +13058,7 @@
         <v>138.74669119999999</v>
       </c>
       <c r="F122" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="G122">
         <v>36.833393683160601</v>
@@ -13075,7 +13078,7 @@
         <v>138.74501577195321</v>
       </c>
       <c r="F123" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="G123">
         <v>36.622841071131219</v>
@@ -13095,7 +13098,7 @@
         <v>139.38204658642061</v>
       </c>
       <c r="F124" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="G124">
         <v>37.025403708186893</v>
@@ -13115,7 +13118,7 @@
         <v>141.00975359999998</v>
       </c>
       <c r="F125" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="G125">
         <v>37.381484291677808</v>
@@ -13135,7 +13138,7 @@
         <v>138.9077149736554</v>
       </c>
       <c r="F126" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="G126">
         <v>36.371120610978807</v>
@@ -13155,7 +13158,7 @@
         <v>135.91735309240229</v>
       </c>
       <c r="F127" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="G127">
         <v>37.237118883574631</v>
@@ -13175,7 +13178,7 @@
         <v>135.65658974924909</v>
       </c>
       <c r="F128" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="G128">
         <v>35.708267733884668</v>
@@ -13195,7 +13198,7 @@
         <v>136.29851369999997</v>
       </c>
       <c r="F129" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="G129">
         <v>34.838968568013591</v>
@@ -13215,7 +13218,7 @@
         <v>136.43987240000001</v>
       </c>
       <c r="F130" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="G130">
         <v>35.539462784211032</v>
@@ -13235,7 +13238,7 @@
         <v>136.1105518</v>
       </c>
       <c r="F131" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="G131">
         <v>35.10344718137253</v>
@@ -13255,7 +13258,7 @@
         <v>135.09373984404087</v>
       </c>
       <c r="F132" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="G132">
         <v>35.202859981475441</v>
@@ -13275,7 +13278,7 @@
         <v>132.99172771294303</v>
       </c>
       <c r="F133" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="G133">
         <v>35.515618181799375</v>
@@ -13295,7 +13298,7 @@
         <v>140.02967839999999</v>
       </c>
       <c r="F134" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="G134">
         <v>34.961593435279937</v>
@@ -13315,7 +13318,7 @@
         <v>129.68433039999996</v>
       </c>
       <c r="F135" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="G135">
         <v>35.53899968060265</v>
@@ -13335,7 +13338,7 @@
         <v>140.75025629999996</v>
       </c>
       <c r="F136" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="G136">
         <v>35.315672781592291</v>
@@ -13355,7 +13358,7 @@
         <v>129.9236435</v>
       </c>
       <c r="F137" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="G137">
         <v>33.348565879568348</v>
@@ -13375,7 +13378,7 @@
         <v>136.65407619999999</v>
       </c>
       <c r="F138" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="G138">
         <v>37.842662384191179</v>
@@ -13395,7 +13398,7 @@
         <v>136.6633563</v>
       </c>
       <c r="F139" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="G139">
         <v>33.393767779614286</v>
@@ -13415,7 +13418,7 @@
         <v>136.65658429999999</v>
       </c>
       <c r="F140" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="G140">
         <v>35.675360981964779</v>
@@ -13435,7 +13438,7 @@
         <v>136.6639787</v>
       </c>
       <c r="F141" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="G141">
         <v>35.633574681921566</v>
@@ -13455,7 +13458,7 @@
         <v>140.91210482362231</v>
       </c>
       <c r="F142" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="G142">
         <v>35.650100581938673</v>
@@ -13475,7 +13478,7 @@
         <v>130.0443314</v>
       </c>
       <c r="F143" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="G143">
         <v>35.706360981996944</v>
@@ -13495,7 +13498,7 @@
         <v>130.0722404</v>
       </c>
       <c r="F144" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="G144">
         <v>41.508651564773203</v>
@@ -13515,7 +13518,7 @@
         <v>139.82014500000002</v>
       </c>
       <c r="F145" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="G145">
         <v>32.484738478698453</v>
@@ -13535,7 +13538,7 @@
         <v>139.66736009999997</v>
       </c>
       <c r="F146" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="G146">
         <v>32.465651478679419</v>
@@ -13555,7 +13558,7 @@
         <v>139.67164638616484</v>
       </c>
       <c r="F147" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="G147">
         <v>36.716571783040472</v>
@@ -13575,7 +13578,7 @@
         <v>134.14717879997406</v>
       </c>
       <c r="F148" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="G148">
         <v>37.012263983344255</v>
@@ -13595,7 +13598,7 @@
         <v>134.18795782269976</v>
       </c>
       <c r="F149" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="G149">
         <v>36.831030068493966</v>
@@ -13615,7 +13618,7 @@
         <v>141.1459764</v>
       </c>
       <c r="F150" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="G150">
         <v>34.656600980925262</v>
@@ -13635,7 +13638,7 @@
         <v>136.85355660000005</v>
       </c>
       <c r="F151" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="G151">
         <v>35.208514496067693</v>
@@ -13655,7 +13658,7 @@
         <v>139.86426240000003</v>
       </c>
       <c r="F152" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="G152">
         <v>40.755782887038599</v>
@@ -13675,7 +13678,7 @@
         <v>138.76684369999998</v>
       </c>
       <c r="F153" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="G153">
         <v>36.459874082775926</v>
@@ -13695,7 +13698,7 @@
         <v>135.97127599999999</v>
       </c>
       <c r="F154" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="G154">
         <v>36.993515983324997</v>
@@ -13715,7 +13718,7 @@
         <v>135.98637149999996</v>
       </c>
       <c r="F155" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="G155">
         <v>36.845897183173513</v>
@@ -13735,7 +13738,7 @@
         <v>135.31301980000001</v>
       </c>
       <c r="F156" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="G156">
         <v>35.539115781823647</v>
@@ -13755,7 +13758,7 @@
         <v>135.36116000000004</v>
       </c>
       <c r="F157" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="G157">
         <v>35.533805881818225</v>
@@ -13775,7 +13778,7 @@
         <v>135.50414703991692</v>
       </c>
       <c r="F158" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="G158">
         <v>35.283431681558874</v>
@@ -13795,7 +13798,7 @@
         <v>135.46966040000004</v>
       </c>
       <c r="F159" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="G159">
         <v>35.08315948135143</v>
@@ -13815,7 +13818,7 @@
         <v>134.65037140000004</v>
       </c>
       <c r="F160" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="G160">
         <v>35.52070181861027</v>
@@ -13835,7 +13838,7 @@
         <v>138.70539420000003</v>
       </c>
       <c r="F161" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="G161">
         <v>35.48131578176384</v>
@@ -13855,7 +13858,7 @@
         <v>134.71815123527378</v>
       </c>
       <c r="F162" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="G162">
         <v>33.860734580091119</v>
@@ -13875,7 +13878,7 @@
         <v>138.14599129416126</v>
       </c>
       <c r="F163" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="G163">
         <v>36.033951482335901</v>
@@ -13895,7 +13898,7 @@
         <v>131.35489939999999</v>
       </c>
       <c r="F164" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="G164">
         <v>35.128425766214498</v>
@@ -13915,7 +13918,7 @@
         <v>137.04902529999998</v>
       </c>
       <c r="F165" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="G165">
         <v>34.624290259299336</v>
@@ -13935,7 +13938,7 @@
         <v>134.85631707609716</v>
       </c>
       <c r="F166" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="G166">
         <v>32.318128478532813</v>
@@ -13955,7 +13958,7 @@
         <v>138.96215179999999</v>
       </c>
       <c r="F167" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="G167">
         <v>36.079947782383513</v>
@@ -13975,7 +13978,7 @@
         <v>138.94781469999998</v>
       </c>
       <c r="F168" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="G168">
         <v>35.236783699163318</v>
@@ -13995,7 +13998,7 @@
         <v>135.1978422</v>
       </c>
       <c r="F169" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="G169">
         <v>36.527150382845349</v>
@@ -14015,7 +14018,7 @@
         <v>134.56571169999998</v>
       </c>
       <c r="F170" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="G170">
         <v>36.531049382849403</v>
@@ -14035,7 +14038,7 @@
         <v>130.18954854445479</v>
       </c>
       <c r="F171" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="G171">
         <v>33.860709380091059</v>
@@ -14055,7 +14058,7 @@
         <v>136.7293475498264</v>
       </c>
       <c r="F172" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="G172">
         <v>34.973205081237758</v>
@@ -14075,7 +14078,7 @@
         <v>139.9691358</v>
       </c>
       <c r="F173" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="G173">
         <v>31.831554494509291</v>
@@ -14095,7 +14098,7 @@
         <v>139.95336681437402</v>
       </c>
       <c r="F174" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="G174">
         <v>37.06119413998394</v>
@@ -14115,7 +14118,7 @@
         <v>139.92874660000001</v>
       </c>
       <c r="F175" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="G175">
         <v>35.690483081980481</v>
@@ -14135,7 +14138,7 @@
         <v>139.88276669999999</v>
       </c>
       <c r="F176" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="G176">
         <v>35.691145203332042</v>
@@ -14155,7 +14158,7 @@
         <v>139.8673253</v>
       </c>
       <c r="F177" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="G177">
         <v>35.673833481963186</v>
@@ -14175,7 +14178,7 @@
         <v>139.85114659999999</v>
       </c>
       <c r="F178" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="G178">
         <v>35.637957981926078</v>
@@ -14195,7 +14198,7 @@
         <v>139.84061359999998</v>
       </c>
       <c r="F179" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="G179">
         <v>35.643357481931645</v>
@@ -14215,7 +14218,7 @@
         <v>139.80703298771471</v>
       </c>
       <c r="F180" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="G180">
         <v>35.647114881935543</v>
@@ -14235,7 +14238,7 @@
         <v>135.34489300000001</v>
       </c>
       <c r="F181" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="G181">
         <v>35.647820481936307</v>
@@ -14255,7 +14258,7 @@
         <v>138.62571410000004</v>
       </c>
       <c r="F182" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="G182">
         <v>35.642827600842622</v>
@@ -14275,7 +14278,7 @@
         <v>141.45121793661826</v>
       </c>
       <c r="F183" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="G183">
         <v>36.579104053018241</v>
@@ -14295,7 +14298,7 @@
         <v>140.58515938711835</v>
       </c>
       <c r="F184" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="G184">
         <v>35.590406542941842</v>
@@ -14315,7 +14318,7 @@
         <v>141.03539173232843</v>
       </c>
       <c r="F185" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="G185">
         <v>35.524235781808308</v>
@@ -14335,7 +14338,7 @@
         <v>141.05492399999997</v>
       </c>
       <c r="F186" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="G186">
         <v>36.081367082384993</v>
@@ -14355,7 +14358,7 @@
         <v>141.2221878926961</v>
       </c>
       <c r="F187" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="G187">
         <v>37.025086041614799</v>
@@ -14375,7 +14378,7 @@
         <v>140.60642612495218</v>
       </c>
       <c r="F188" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="G188">
         <v>43.234266159817281</v>
@@ -14395,7 +14398,7 @@
         <v>141.80450293753924</v>
       </c>
       <c r="F189" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="G189">
         <v>41.916289110672011</v>
@@ -14415,7 +14418,7 @@
         <v>141.78185613570739</v>
       </c>
       <c r="F190" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="G190">
         <v>42.749349494630721</v>
@@ -14435,7 +14438,7 @@
         <v>140.5164523543362</v>
       </c>
       <c r="F191" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="G191">
         <v>43.103426189125337</v>
@@ -14455,7 +14458,7 @@
         <v>141.1341659</v>
       </c>
       <c r="F192" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G192">
         <v>43.058029756113321</v>
@@ -14469,13 +14472,13 @@
         <v>606</v>
       </c>
       <c r="C193">
-        <v>28.263927362997119</v>
+        <v>28.403760866267952</v>
       </c>
       <c r="D193">
-        <v>129.33184438251254</v>
+        <v>129.62425485007154</v>
       </c>
       <c r="F193" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="G193">
         <v>41.888040971612753</v>
@@ -14489,13 +14492,13 @@
         <v>607</v>
       </c>
       <c r="C194">
-        <v>26.853629519883636</v>
+        <v>26.437121286940336</v>
       </c>
       <c r="D194">
-        <v>127.98617033570848</v>
+        <v>127.94749044991164</v>
       </c>
       <c r="F194" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="G194">
         <v>42.612540162775971</v>
@@ -14509,13 +14512,13 @@
         <v>608</v>
       </c>
       <c r="C195">
-        <v>33.659849545344365</v>
+        <v>33.435019454413229</v>
       </c>
       <c r="D195">
-        <v>129.68428282334222</v>
+        <v>129.82525819967407</v>
       </c>
       <c r="F195" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="G195">
         <v>42.714095832936565</v>
@@ -14529,13 +14532,13 @@
         <v>609</v>
       </c>
       <c r="C196">
-        <v>30.737058363239601</v>
+        <v>31.186718545101872</v>
       </c>
       <c r="D196">
-        <v>130.61472030713247</v>
+        <v>130.81208583399706</v>
       </c>
       <c r="F196" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="G196">
         <v>43.039701541285162</v>
@@ -14549,13 +14552,13 @@
         <v>610</v>
       </c>
       <c r="C197">
-        <v>32.431931356412775</v>
+        <v>32.535699090688681</v>
       </c>
       <c r="D197">
-        <v>130.39458183486042</v>
+        <v>130.81208583399706</v>
       </c>
       <c r="F197" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="G197">
         <v>43.054394789084093</v>
@@ -14569,19 +14572,19 @@
         <v>611</v>
       </c>
       <c r="C198">
-        <v>35.233660181862305</v>
+        <v>35.087966156787431</v>
       </c>
       <c r="D198">
-        <v>137.47317236567724</v>
+        <v>137.14688624260751</v>
       </c>
       <c r="F198" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="G198">
-        <v>28.263927362997119</v>
+        <v>28.403760866267952</v>
       </c>
       <c r="H198">
-        <v>129.33184438251254</v>
+        <v>129.62425485007154</v>
       </c>
     </row>
     <row r="199" spans="2:8">
@@ -14589,19 +14592,19 @@
         <v>612</v>
       </c>
       <c r="C199">
-        <v>34.334339818137757</v>
+        <v>34.707949188537874</v>
       </c>
       <c r="D199">
-        <v>135.14067068455017</v>
+        <v>135.24391188699428</v>
       </c>
       <c r="F199" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="G199">
-        <v>26.853629519883636</v>
+        <v>26.437121286940336</v>
       </c>
       <c r="H199">
-        <v>127.98617033570848</v>
+        <v>127.94749044991164</v>
       </c>
     </row>
     <row r="200" spans="2:8">
@@ -14609,19 +14612,19 @@
         <v>613</v>
       </c>
       <c r="C200">
-        <v>35.458490272793441</v>
+        <v>31.938760417794487</v>
       </c>
       <c r="D200">
-        <v>134.51268946270827</v>
+        <v>131.3068894775561</v>
       </c>
       <c r="F200" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="G200">
-        <v>33.659849545344365</v>
+        <v>33.435019454413229</v>
       </c>
       <c r="H200">
-        <v>129.68428282334222</v>
+        <v>129.82525819967407</v>
       </c>
     </row>
     <row r="201" spans="2:8">
@@ -14629,19 +14632,19 @@
         <v>614</v>
       </c>
       <c r="C201">
-        <v>34.933886727287465</v>
+        <v>33.214877451158252</v>
       </c>
       <c r="D201">
-        <v>132.6212698302559</v>
+        <v>131.85800087797219</v>
       </c>
       <c r="F201" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="G201">
-        <v>30.737058363239601</v>
+        <v>31.186718545101872</v>
       </c>
       <c r="H201">
-        <v>130.61472030713247</v>
+        <v>130.81208583399706</v>
       </c>
     </row>
     <row r="202" spans="2:8">
@@ -14649,19 +14652,19 @@
         <v>615</v>
       </c>
       <c r="C202">
-        <v>31.546446690591694</v>
+        <v>34.473438915726867</v>
       </c>
       <c r="D202">
-        <v>131.40418241459082</v>
+        <v>132.44984778916526</v>
       </c>
       <c r="F202" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="G202">
-        <v>32.431931356412775</v>
+        <v>32.535699090688681</v>
       </c>
       <c r="H202">
-        <v>130.39458183486042</v>
+        <v>130.81208583399706</v>
       </c>
     </row>
     <row r="203" spans="2:8">
@@ -14669,19 +14672,19 @@
         <v>616</v>
       </c>
       <c r="C203">
-        <v>33.340354152968537</v>
+        <v>35.308061608240791</v>
       </c>
       <c r="D203">
-        <v>132.3962038785682</v>
+        <v>133.79022259650586</v>
       </c>
       <c r="F203" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="G203">
-        <v>35.233660181862305</v>
+        <v>35.087966156787431</v>
       </c>
       <c r="H203">
-        <v>137.47317236567724</v>
+        <v>137.14688624260751</v>
       </c>
     </row>
     <row r="204" spans="2:8">
@@ -14689,19 +14692,19 @@
         <v>617</v>
       </c>
       <c r="C204">
-        <v>43.969915143757859</v>
+        <v>43.824758326357014</v>
       </c>
       <c r="D204">
-        <v>144.34572196185522</v>
+        <v>144.24247770518093</v>
       </c>
       <c r="F204" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="G204">
-        <v>34.334339818137757</v>
+        <v>34.707949188537874</v>
       </c>
       <c r="H204">
-        <v>135.14067068455017</v>
+        <v>135.24391188699428</v>
       </c>
     </row>
     <row r="205" spans="2:8">
@@ -14709,19 +14712,19 @@
         <v>618</v>
       </c>
       <c r="C205">
-        <v>43.147679382638273</v>
+        <v>43.29039933952194</v>
       </c>
       <c r="D205">
-        <v>145.02240376824813</v>
+        <v>144.83899676653832</v>
       </c>
       <c r="F205" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="G205">
-        <v>35.458490272793441</v>
+        <v>31.938760417794487</v>
       </c>
       <c r="H205">
-        <v>134.51268946270827</v>
+        <v>131.3068894775561</v>
       </c>
     </row>
     <row r="206" spans="2:8">
@@ -14729,19 +14732,19 @@
         <v>619</v>
       </c>
       <c r="C206">
-        <v>42.877883273520922</v>
+        <v>42.904367131388497</v>
       </c>
       <c r="D206">
-        <v>143.64084508019593</v>
+        <v>143.43877200055002</v>
       </c>
       <c r="F206" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="G206">
-        <v>34.933886727287465</v>
+        <v>33.214877451158252</v>
       </c>
       <c r="H206">
-        <v>132.6212698302559</v>
+        <v>131.85800087797219</v>
       </c>
     </row>
     <row r="207" spans="2:8">
@@ -14749,19 +14752,19 @@
         <v>620</v>
       </c>
       <c r="C207">
-        <v>44.09838948143279</v>
+        <v>44.02764494294621</v>
       </c>
       <c r="D207">
-        <v>141.66718981154995</v>
+        <v>141.98230705528843</v>
       </c>
       <c r="F207" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="G207">
-        <v>31.546446690591694</v>
+        <v>34.473438915726867</v>
       </c>
       <c r="H207">
-        <v>131.40418241459082</v>
+        <v>132.44984778916526</v>
       </c>
     </row>
     <row r="208" spans="2:8">
@@ -14769,19 +14772,19 @@
         <v>621</v>
       </c>
       <c r="C208">
-        <v>44.776448485828283</v>
+        <v>44.866389962657003</v>
       </c>
       <c r="D208">
-        <v>142.37989865856099</v>
+        <v>142.2268015903324</v>
       </c>
       <c r="F208" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="G208">
-        <v>33.340354152968537</v>
+        <v>35.308061608240791</v>
       </c>
       <c r="H208">
-        <v>132.3962038785682</v>
+        <v>133.79022259650586</v>
       </c>
     </row>
     <row r="209" spans="2:8">
@@ -14789,19 +14792,19 @@
         <v>622</v>
       </c>
       <c r="C209">
-        <v>43.05774734626582</v>
+        <v>42.952035290389645</v>
       </c>
       <c r="D209">
-        <v>140.77904494065928</v>
+        <v>140.85749327909829</v>
       </c>
       <c r="F209" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="G209">
-        <v>43.969915143757859</v>
+        <v>43.824758326357014</v>
       </c>
       <c r="H209">
-        <v>144.34572196185522</v>
+        <v>144.24247770518093</v>
       </c>
     </row>
     <row r="210" spans="2:8">
@@ -14809,19 +14812,19 @@
         <v>623</v>
       </c>
       <c r="C210">
-        <v>42.178411879512936</v>
+        <v>42.428223091658637</v>
       </c>
       <c r="D210">
-        <v>140.29659587499023</v>
+        <v>140.18694836006549</v>
       </c>
       <c r="F210" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="G210">
-        <v>43.147679382638273</v>
+        <v>43.29039933952194</v>
       </c>
       <c r="H210">
-        <v>145.02240376824813</v>
+        <v>144.83899676653832</v>
       </c>
     </row>
     <row r="211" spans="2:8">
@@ -14829,19 +14832,19 @@
         <v>624</v>
       </c>
       <c r="C211">
-        <v>42.353279728014932</v>
+        <v>42.439170214390096</v>
       </c>
       <c r="D211">
-        <v>142.48954617348576</v>
+        <v>142.27918947110257</v>
       </c>
       <c r="F211" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="G211">
-        <v>42.877883273520922</v>
+        <v>42.904367131388497</v>
       </c>
       <c r="H211">
-        <v>143.64084508019593</v>
+        <v>143.43877200055002</v>
       </c>
     </row>
     <row r="212" spans="2:8">
@@ -14849,19 +14852,19 @@
         <v>625</v>
       </c>
       <c r="C212">
-        <v>43.327543455383179</v>
+        <v>43.158509213102896</v>
       </c>
       <c r="D212">
-        <v>142.4073105372922</v>
+        <v>142.00528620895545</v>
       </c>
       <c r="F212" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="G212">
-        <v>44.09838948143279</v>
+        <v>44.02764494294621</v>
       </c>
       <c r="H212">
-        <v>141.66718981154995</v>
+        <v>141.98230705528843</v>
       </c>
     </row>
     <row r="213" spans="2:8">
@@ -14869,19 +14872,19 @@
         <v>626</v>
       </c>
       <c r="C213">
-        <v>34.896415045465609</v>
+        <v>35.516357497927203</v>
       </c>
       <c r="D213">
-        <v>139.44682763432323</v>
+        <v>139.66018408801415</v>
       </c>
       <c r="F213" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="G213">
-        <v>44.776448485828283</v>
+        <v>44.866389962657003</v>
       </c>
       <c r="H213">
-        <v>142.37989865856099</v>
+        <v>142.2268015903324</v>
       </c>
     </row>
     <row r="214" spans="2:8">
@@ -14889,19 +14892,19 @@
         <v>627</v>
       </c>
       <c r="C214">
-        <v>36.357810636517982</v>
+        <v>36.19147631712201</v>
       </c>
       <c r="D214">
-        <v>140.55700872293659</v>
+        <v>140.30754342094826</v>
       </c>
       <c r="F214" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="G214">
-        <v>43.05774734626582</v>
+        <v>42.952035290389645</v>
       </c>
       <c r="H214">
-        <v>140.77904494065928</v>
+        <v>140.85749327909829</v>
       </c>
     </row>
     <row r="215" spans="2:8">
@@ -14909,19 +14912,19 @@
         <v>628</v>
       </c>
       <c r="C215">
-        <v>36.492708691076665</v>
+        <v>36.348454276526617</v>
       </c>
       <c r="D215">
-        <v>139.29880348917476</v>
+        <v>139.60657015788613</v>
       </c>
       <c r="F215" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="G215">
-        <v>42.178411879512936</v>
+        <v>42.428223091658637</v>
       </c>
       <c r="H215">
-        <v>140.29659587499023</v>
+        <v>140.18694836006549</v>
       </c>
     </row>
     <row r="216" spans="2:8">
@@ -14929,19 +14932,19 @@
         <v>629</v>
       </c>
       <c r="C216">
-        <v>38.060095610710867</v>
+        <v>37.989078017834409</v>
       </c>
       <c r="D216">
-        <v>139.23536456982546</v>
+        <v>139.39537508870831</v>
       </c>
       <c r="F216" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="G216">
-        <v>42.353279728014932</v>
+        <v>42.439170214390096</v>
       </c>
       <c r="H216">
-        <v>142.48954617348576</v>
+        <v>142.27918947110257</v>
       </c>
     </row>
     <row r="217" spans="2:8">
@@ -14949,19 +14952,19 @@
         <v>630</v>
       </c>
       <c r="C217">
-        <v>37.63184781846109</v>
+        <v>37.48200393492224</v>
       </c>
       <c r="D217">
-        <v>136.89752291232216</v>
+        <v>137.13221205726239</v>
       </c>
       <c r="F217" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="G217">
-        <v>43.327543455383179</v>
+        <v>43.158509213102896</v>
       </c>
       <c r="H217">
-        <v>142.4073105372922</v>
+        <v>142.00528620895545</v>
       </c>
     </row>
     <row r="218" spans="2:8">
@@ -14969,19 +14972,19 @@
         <v>631</v>
       </c>
       <c r="C218">
-        <v>36.522686036534161</v>
+        <v>36.611672842337725</v>
       </c>
       <c r="D218">
-        <v>137.12778269366422</v>
+        <v>137.08456152283767</v>
       </c>
       <c r="F218" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G218">
-        <v>34.896415045465609</v>
+        <v>35.516357497927203</v>
       </c>
       <c r="H218">
-        <v>139.44682763432323</v>
+        <v>139.66018408801415</v>
       </c>
     </row>
     <row r="219" spans="2:8">
@@ -14989,19 +14992,19 @@
         <v>632</v>
       </c>
       <c r="C219">
-        <v>41.3361912214217</v>
+        <v>41.528902727934096</v>
       </c>
       <c r="D219">
-        <v>140.82133755355883</v>
+        <v>140.18694836006549</v>
       </c>
       <c r="F219" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="G219">
-        <v>36.357810636517982</v>
+        <v>36.19147631712201</v>
       </c>
       <c r="H219">
-        <v>140.55700872293659</v>
+        <v>140.30754342094826</v>
       </c>
     </row>
     <row r="220" spans="2:8">
@@ -15009,19 +15012,19 @@
         <v>633</v>
       </c>
       <c r="C220">
-        <v>40.045024127788608</v>
+        <v>39.993434559438533</v>
       </c>
       <c r="D220">
-        <v>140.08826559663316</v>
+        <v>140.29903337030427</v>
       </c>
       <c r="F220" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="G220">
-        <v>36.492708691076665</v>
+        <v>36.348454276526617</v>
       </c>
       <c r="H220">
-        <v>139.29880348917476</v>
+        <v>139.60657015788613</v>
       </c>
     </row>
     <row r="221" spans="2:8">
@@ -15029,19 +15032,19 @@
         <v>634</v>
       </c>
       <c r="C221">
-        <v>39.834029734760925</v>
+        <v>39.911267974113372</v>
       </c>
       <c r="D221">
-        <v>141.47741526648781</v>
+        <v>141.16581990056631</v>
       </c>
       <c r="F221" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="G221">
-        <v>38.060095610710867</v>
+        <v>37.989078017834409</v>
       </c>
       <c r="H221">
-        <v>139.23536456982546</v>
+        <v>139.39537508870831</v>
       </c>
     </row>
     <row r="222" spans="2:8">
@@ -15049,19 +15052,19 @@
         <v>635</v>
       </c>
       <c r="C222">
-        <v>38.156451363967072</v>
+        <v>38.254479362485085</v>
       </c>
       <c r="D222">
-        <v>140.92706908580772</v>
+        <v>140.87002090547148</v>
       </c>
       <c r="F222" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="G222">
-        <v>37.63184781846109</v>
+        <v>37.48200393492224</v>
       </c>
       <c r="H222">
-        <v>136.89752291232216</v>
+        <v>137.13221205726239</v>
       </c>
     </row>
     <row r="223" spans="2:8">
@@ -15069,19 +15072,19 @@
         <v>636</v>
       </c>
       <c r="C223">
-        <v>26.853629519883636</v>
+        <v>26.721487336012729</v>
       </c>
       <c r="D223">
-        <v>127.98617033570848</v>
+        <v>128.10477117822481</v>
       </c>
       <c r="F223" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="G223">
-        <v>36.522686036534161</v>
+        <v>36.611672842337725</v>
       </c>
       <c r="H223">
-        <v>137.12778269366422</v>
+        <v>137.08456152283767</v>
       </c>
     </row>
     <row r="224" spans="2:8">
@@ -15089,19 +15092,19 @@
         <v>637</v>
       </c>
       <c r="C224">
-        <v>29.923387557965011</v>
+        <v>31.186718545101872</v>
       </c>
       <c r="D224">
-        <v>129.9192417838953</v>
+        <v>130.81208583399706</v>
       </c>
       <c r="F224" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="G224">
-        <v>41.3361912214217</v>
+        <v>41.528902727934096</v>
       </c>
       <c r="H224">
-        <v>140.82133755355883</v>
+        <v>140.18694836006549</v>
       </c>
     </row>
     <row r="225" spans="2:8">
@@ -15109,19 +15112,19 @@
         <v>638</v>
       </c>
       <c r="C225">
-        <v>34.205865480462833</v>
+        <v>34.313789490388615</v>
       </c>
       <c r="D225">
-        <v>131.9398888446519</v>
+        <v>132.01023796876109</v>
       </c>
       <c r="F225" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="G225">
-        <v>40.045024127788608</v>
+        <v>39.993434559438533</v>
       </c>
       <c r="H225">
-        <v>140.08826559663316</v>
+        <v>140.29903337030427</v>
       </c>
     </row>
     <row r="226" spans="2:8">
@@ -15129,19 +15132,19 @@
         <v>639</v>
       </c>
       <c r="C226">
-        <v>34.109509727206635</v>
+        <v>34.334339818137771</v>
       </c>
       <c r="D226">
-        <v>133.38488645205345</v>
+        <v>133.27915491980451</v>
       </c>
       <c r="F226" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="G226">
-        <v>39.834029734760925</v>
+        <v>39.911267974113372</v>
       </c>
       <c r="H226">
-        <v>141.47741526648781</v>
+        <v>141.16581990056631</v>
       </c>
     </row>
     <row r="227" spans="2:8">
@@ -15149,19 +15152,19 @@
         <v>640</v>
       </c>
       <c r="C227">
-        <v>32.985359272550959</v>
+        <v>33.115690353314349</v>
       </c>
       <c r="D227">
-        <v>130.56537892541633</v>
+        <v>130.62843533461103</v>
       </c>
       <c r="F227" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="G227">
-        <v>38.156451363967072</v>
+        <v>38.254479362485085</v>
       </c>
       <c r="H227">
-        <v>140.92706908580772</v>
+        <v>140.87002090547148</v>
       </c>
     </row>
     <row r="228" spans="2:8">
@@ -15169,19 +15172,19 @@
         <v>641</v>
       </c>
       <c r="C228">
-        <v>32.310868999757552</v>
+        <v>32.338023062446382</v>
       </c>
       <c r="D228">
-        <v>131.05879274257779</v>
+        <v>131.04431989990678</v>
       </c>
       <c r="F228" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="G228">
-        <v>26.853629519883636</v>
+        <v>26.721487336012729</v>
       </c>
       <c r="H228">
-        <v>127.98617033570848</v>
+        <v>128.10477117822481</v>
       </c>
     </row>
     <row r="229" spans="2:8">
@@ -15189,19 +15192,19 @@
         <v>642</v>
       </c>
       <c r="C229">
-        <v>34.604135927255129</v>
+        <v>34.677758993260163</v>
       </c>
       <c r="D229">
-        <v>137.12778269366419</v>
+        <v>137.25730064583442</v>
       </c>
       <c r="F229" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="G229">
-        <v>29.923387557965011</v>
+        <v>31.186718545101872</v>
       </c>
       <c r="H229">
-        <v>129.9192417838953</v>
+        <v>130.81208583399706</v>
       </c>
     </row>
     <row r="230" spans="2:8">
@@ -15209,19 +15212,19 @@
         <v>643</v>
       </c>
       <c r="C230">
-        <v>34.873932036372494</v>
+        <v>34.780849662497538</v>
       </c>
       <c r="D230">
-        <v>136.43700334963813</v>
+        <v>136.42363715874816</v>
       </c>
       <c r="F230" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="G230">
-        <v>34.205865480462833</v>
+        <v>34.313789490388615</v>
       </c>
       <c r="H230">
-        <v>131.9398888446519</v>
+        <v>132.01023796876109</v>
       </c>
     </row>
     <row r="231" spans="2:8">
@@ -15229,19 +15232,19 @@
         <v>644</v>
       </c>
       <c r="C231">
-        <v>36.282867272874277</v>
+        <v>36.228646486256316</v>
       </c>
       <c r="D231">
-        <v>137.06199418470931</v>
+        <v>137.05023194742876</v>
       </c>
       <c r="F231" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="G231">
-        <v>34.109509727206635</v>
+        <v>34.334339818137771</v>
       </c>
       <c r="H231">
-        <v>133.38488645205345</v>
+        <v>133.27915491980451</v>
       </c>
     </row>
     <row r="232" spans="2:8">
@@ -15249,19 +15252,19 @@
         <v>645</v>
       </c>
       <c r="C232">
-        <v>33.8846796362755</v>
+        <v>33.950908983453743</v>
       </c>
       <c r="D232">
-        <v>133.86228034008627</v>
+        <v>134.0697330936454</v>
       </c>
       <c r="F232" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="G232">
-        <v>32.985359272550959</v>
+        <v>33.115690353314349</v>
       </c>
       <c r="H232">
-        <v>130.56537892541633</v>
+        <v>130.62843533461103</v>
       </c>
     </row>
     <row r="233" spans="2:8">
@@ -15269,19 +15272,19 @@
         <v>646</v>
       </c>
       <c r="C233">
-        <v>35.554846026049646</v>
+        <v>35.387363191003828</v>
       </c>
       <c r="D233">
-        <v>134.93561559170385</v>
+        <v>134.84839005250069</v>
       </c>
       <c r="F233" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="G233">
-        <v>32.310868999757552</v>
+        <v>32.338023062446382</v>
       </c>
       <c r="H233">
-        <v>131.05879274257779</v>
+        <v>131.04431989990678</v>
       </c>
     </row>
     <row r="234" spans="2:8">
@@ -15289,19 +15292,19 @@
         <v>647</v>
       </c>
       <c r="C234">
-        <v>36.132980545586847</v>
+        <v>36.305655858504757</v>
       </c>
       <c r="D234">
-        <v>139.69353454290396</v>
+        <v>139.88301181643868</v>
       </c>
       <c r="F234" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="G234">
-        <v>34.604135927255129</v>
+        <v>34.677758993260163</v>
       </c>
       <c r="H234">
-        <v>137.12778269366419</v>
+        <v>137.25730064583442</v>
       </c>
     </row>
     <row r="235" spans="2:8">
@@ -15309,19 +15312,19 @@
         <v>648</v>
       </c>
       <c r="C235">
-        <v>35.627112840991792</v>
+        <v>35.626964425126431</v>
       </c>
       <c r="D235">
-        <v>140.06359490577509</v>
+        <v>140.05363713209957</v>
       </c>
       <c r="F235" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="G235">
-        <v>34.873932036372494</v>
+        <v>34.780849662497538</v>
       </c>
       <c r="H235">
-        <v>136.43700334963813</v>
+        <v>136.42363715874816</v>
       </c>
     </row>
     <row r="236" spans="2:8">
@@ -15332,16 +15335,16 @@
         <v>35.233660181862312</v>
       </c>
       <c r="D236">
-        <v>138.46000000000024</v>
+        <v>138.58978349097978</v>
       </c>
       <c r="F236" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="G236">
-        <v>36.282867272874277</v>
+        <v>36.228646486256316</v>
       </c>
       <c r="H236">
-        <v>137.06199418470931</v>
+        <v>137.05023194742876</v>
       </c>
     </row>
     <row r="237" spans="2:8">
@@ -15349,19 +15352,19 @@
         <v>650</v>
       </c>
       <c r="C237">
-        <v>34.199441763579088</v>
+        <v>34.784000000000034</v>
       </c>
       <c r="D237">
-        <v>139.39748625260708</v>
+        <v>138.2132930914195</v>
       </c>
       <c r="F237" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="G237">
-        <v>33.8846796362755</v>
+        <v>33.950908983453743</v>
       </c>
       <c r="H237">
-        <v>133.86228034008627</v>
+        <v>134.0697330936454</v>
       </c>
     </row>
     <row r="238" spans="2:8">
@@ -15369,19 +15372,19 @@
         <v>651</v>
       </c>
       <c r="C238">
-        <v>35.458490272793441</v>
+        <v>35.229245727618768</v>
       </c>
       <c r="D238">
-        <v>132.53903419406228</v>
+        <v>132.64662014289334</v>
       </c>
       <c r="F238" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="G238">
-        <v>35.554846026049646</v>
+        <v>35.387363191003828</v>
       </c>
       <c r="H238">
-        <v>134.93561559170385</v>
+        <v>134.84839005250069</v>
       </c>
     </row>
     <row r="239" spans="2:8">
@@ -15389,19 +15392,19 @@
         <v>652</v>
       </c>
       <c r="C239">
-        <v>37.144715954776963</v>
+        <v>36.918571067960393</v>
       </c>
       <c r="D239">
-        <v>136.91808182137055</v>
+        <v>136.89427293726365</v>
       </c>
       <c r="F239" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="G239">
-        <v>36.132980545586847</v>
+        <v>36.305655858504757</v>
       </c>
       <c r="H239">
-        <v>139.69353454290396</v>
+        <v>139.88301181643868</v>
       </c>
     </row>
     <row r="240" spans="2:8">
@@ -15409,19 +15412,19 @@
         <v>653</v>
       </c>
       <c r="C240">
-        <v>32.821846479146494</v>
+        <v>32.985359272550959</v>
       </c>
       <c r="D240">
-        <v>133.32401072136466</v>
+        <v>132.78574110264304</v>
       </c>
       <c r="F240" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="G240">
-        <v>35.627112840991792</v>
+        <v>35.626964425126431</v>
       </c>
       <c r="H240">
-        <v>140.06359490577509</v>
+        <v>140.05363713209957</v>
       </c>
     </row>
     <row r="241" spans="2:8">
@@ -15429,19 +15432,19 @@
         <v>654</v>
       </c>
       <c r="C241">
-        <v>33.19948316867584</v>
+        <v>33.176862843163498</v>
       </c>
       <c r="D241">
-        <v>129.73127461545283</v>
+        <v>130.32210892390466</v>
       </c>
       <c r="F241" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="G241">
         <v>35.233660181862312</v>
       </c>
       <c r="H241">
-        <v>138.46000000000024</v>
+        <v>138.58978349097978</v>
       </c>
     </row>
     <row r="242" spans="2:8">
@@ -15449,19 +15452,19 @@
         <v>655</v>
       </c>
       <c r="C242">
-        <v>38.217768661493743</v>
+        <v>37.931621273035937</v>
       </c>
       <c r="D242">
-        <v>138.93098591638167</v>
+        <v>139.20012072574249</v>
       </c>
       <c r="F242" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G242">
-        <v>34.199441763579088</v>
+        <v>34.784000000000034</v>
       </c>
       <c r="H242">
-        <v>139.39748625260708</v>
+        <v>138.2132930914195</v>
       </c>
     </row>
     <row r="243" spans="2:8">
@@ -15469,19 +15472,19 @@
         <v>656</v>
       </c>
       <c r="C243">
-        <v>37.706791182104801</v>
+        <v>37.588614516018438</v>
       </c>
       <c r="D243">
-        <v>141.07509323095616</v>
+        <v>140.81238785426279</v>
       </c>
       <c r="F243" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="G243">
-        <v>35.458490272793441</v>
+        <v>35.229245727618768</v>
       </c>
       <c r="H243">
-        <v>132.53903419406228</v>
+        <v>132.64662014289334</v>
       </c>
     </row>
     <row r="244" spans="2:8">
@@ -15489,19 +15492,19 @@
         <v>657</v>
       </c>
       <c r="C244">
-        <v>36.762504800194037</v>
+        <v>36.904959135616721</v>
       </c>
       <c r="D244">
-        <v>139.59485177947167</v>
+        <v>139.72420017893802</v>
       </c>
       <c r="F244" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="G244">
-        <v>37.144715954776963</v>
+        <v>36.918571067960393</v>
       </c>
       <c r="H244">
-        <v>136.91808182137055</v>
+        <v>136.89427293726365</v>
       </c>
     </row>
     <row r="245" spans="2:8">
@@ -15509,19 +15512,19 @@
         <v>658</v>
       </c>
       <c r="C245">
-        <v>37.781734545748513</v>
+        <v>37.725022041959647</v>
       </c>
       <c r="D245">
-        <v>139.85800581529114</v>
+        <v>139.86844606266203</v>
       </c>
       <c r="F245" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="G245">
-        <v>32.821846479146494</v>
+        <v>32.985359272550959</v>
       </c>
       <c r="H245">
-        <v>133.32401072136466</v>
+        <v>132.78574110264304</v>
       </c>
     </row>
     <row r="246" spans="2:8">
@@ -15529,19 +15532,19 @@
         <v>659</v>
       </c>
       <c r="C246">
-        <v>39.321480016973858</v>
+        <v>39.360869838266851</v>
       </c>
       <c r="D246">
-        <v>140.77007378034725</v>
+        <v>140.76855308816241</v>
       </c>
       <c r="F246" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="G246">
-        <v>33.19948316867584</v>
+        <v>33.176862843163498</v>
       </c>
       <c r="H246">
-        <v>129.73127461545283</v>
+        <v>130.32210892390466</v>
       </c>
     </row>
     <row r="247" spans="2:8">
@@ -15549,19 +15552,19 @@
         <v>660</v>
       </c>
       <c r="C247">
-        <v>42.668041855318521</v>
+        <v>42.780193454503362</v>
       </c>
       <c r="D247">
-        <v>141.20667024886589</v>
+        <v>141.21172114456672</v>
       </c>
       <c r="F247" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="G247">
-        <v>38.217768661493743</v>
+        <v>37.931621273035937</v>
       </c>
       <c r="H247">
-        <v>138.93098591638167</v>
+        <v>139.20012072574249</v>
       </c>
     </row>
     <row r="248" spans="2:8">
@@ -15569,19 +15572,19 @@
         <v>661</v>
       </c>
       <c r="C248">
-        <v>42.153430758298363</v>
+        <v>41.947320552197233</v>
       </c>
       <c r="D248">
-        <v>140.65295029849574</v>
+        <v>140.81043619739748</v>
       </c>
       <c r="F248" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="G248">
-        <v>37.706791182104801</v>
+        <v>37.588614516018438</v>
       </c>
       <c r="H248">
-        <v>141.07509323095616</v>
+        <v>140.81238785426279</v>
       </c>
     </row>
     <row r="249" spans="2:8">
@@ -15589,19 +15592,19 @@
         <v>662</v>
       </c>
       <c r="C249">
-        <v>40.206372781280358</v>
+        <v>40.167323078141273</v>
       </c>
       <c r="D249">
-        <v>140.91255691471474</v>
+        <v>141.03345633005097</v>
       </c>
       <c r="F249" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="G249">
-        <v>36.762504800194037</v>
+        <v>36.904959135616721</v>
       </c>
       <c r="H249">
-        <v>139.59485177947167</v>
+        <v>139.72420017893802</v>
       </c>
     </row>
     <row r="250" spans="2:8">
@@ -15609,19 +15612,19 @@
         <v>663</v>
       </c>
       <c r="C250">
-        <v>43.777203637245456</v>
+        <v>43.783320086235328</v>
       </c>
       <c r="D250">
-        <v>142.51304206954109</v>
+        <v>142.49621505032994</v>
       </c>
       <c r="F250" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="G250">
-        <v>37.781734545748513</v>
+        <v>37.725022041959647</v>
       </c>
       <c r="H250">
-        <v>139.85800581529114</v>
+        <v>139.86844606266203</v>
       </c>
     </row>
     <row r="251" spans="2:8">
@@ -15629,19 +15632,19 @@
         <v>664</v>
       </c>
       <c r="C251">
-        <v>42.990298318986483</v>
+        <v>43.128232811384791</v>
       </c>
       <c r="D251">
-        <v>143.20910799017963</v>
+        <v>143.30449822379012</v>
       </c>
       <c r="F251" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="G251">
-        <v>39.321480016973858</v>
+        <v>39.360869838266851</v>
       </c>
       <c r="H251">
-        <v>140.77007378034725</v>
+        <v>140.76855308816241</v>
       </c>
     </row>
     <row r="252" spans="2:8">
@@ -15649,19 +15652,19 @@
         <v>665</v>
       </c>
       <c r="C252">
-        <v>44.717402199321107</v>
+        <v>44.645578062145312</v>
       </c>
       <c r="D252">
-        <v>142.1157478271513</v>
+        <v>142.3888373625914</v>
       </c>
       <c r="F252" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="G252">
-        <v>42.668041855318521</v>
+        <v>42.780193454503362</v>
       </c>
       <c r="H252">
-        <v>141.20667024886589</v>
+        <v>141.21172114456672</v>
       </c>
     </row>
     <row r="253" spans="2:8">
@@ -15669,19 +15672,19 @@
         <v>666</v>
       </c>
       <c r="C253">
-        <v>43.456017793058123</v>
+        <v>43.555305636098922</v>
       </c>
       <c r="D253">
-        <v>144.55718502635301</v>
+        <v>144.44314691977866</v>
       </c>
       <c r="F253" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="G253">
-        <v>42.153430758298363</v>
+        <v>41.947320552197233</v>
       </c>
       <c r="H253">
-        <v>140.65295029849574</v>
+        <v>140.81043619739748</v>
       </c>
     </row>
     <row r="254" spans="2:8">
@@ -15689,19 +15692,19 @@
         <v>667</v>
       </c>
       <c r="C254">
-        <v>24.647167147537104</v>
+        <v>24.424451344948238</v>
       </c>
       <c r="D254">
-        <v>123.76139220881444</v>
+        <v>123.75988603755351</v>
       </c>
       <c r="F254" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="G254">
-        <v>40.206372781280358</v>
+        <v>40.167323078141273</v>
       </c>
       <c r="H254">
-        <v>140.91255691471474</v>
+        <v>141.03345633005097</v>
       </c>
     </row>
     <row r="255" spans="2:8">
@@ -15709,19 +15712,19 @@
         <v>668</v>
       </c>
       <c r="C255">
-        <v>24.824182694243067</v>
+        <v>25.107809154669543</v>
       </c>
       <c r="D255">
-        <v>125.78405903139652</v>
+        <v>125.86192830995979</v>
       </c>
       <c r="F255" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="G255">
-        <v>43.777203637245456</v>
+        <v>43.783320086235328</v>
       </c>
       <c r="H255">
-        <v>142.51304206954109</v>
+        <v>142.49621505032994</v>
       </c>
     </row>
     <row r="256" spans="2:8">
@@ -15729,19 +15732,19 @@
         <v>669</v>
       </c>
       <c r="C256">
-        <v>28.634538418324308</v>
+        <v>28.644477570897426</v>
       </c>
       <c r="D256">
-        <v>127.63432198477828</v>
+        <v>127.5517033100982</v>
       </c>
       <c r="F256" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="G256">
-        <v>42.990298318986483</v>
+        <v>43.128232811384791</v>
       </c>
       <c r="H256">
-        <v>143.20910799017963</v>
+        <v>143.30449822379012</v>
       </c>
     </row>
     <row r="257" spans="2:8">
@@ -15749,19 +15752,19 @@
         <v>670</v>
       </c>
       <c r="C257">
-        <v>28.342112352341974</v>
+        <v>28.399703529450854</v>
       </c>
       <c r="D257">
-        <v>129.46919173555284</v>
+        <v>129.21792730748413</v>
       </c>
       <c r="F257" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="G257">
-        <v>44.717402199321107</v>
+        <v>44.645578062145312</v>
       </c>
       <c r="H257">
-        <v>142.1157478271513</v>
+        <v>142.3888373625914</v>
       </c>
     </row>
     <row r="258" spans="2:8">
@@ -15769,19 +15772,19 @@
         <v>671</v>
       </c>
       <c r="C258">
-        <v>25.511898266503003</v>
+        <v>25.613675369966039</v>
       </c>
       <c r="D258">
-        <v>131.76893620506388</v>
+        <v>131.33260837546436</v>
       </c>
       <c r="F258" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="G258">
-        <v>43.456017793058123</v>
+        <v>43.555305636098922</v>
       </c>
       <c r="H258">
-        <v>144.55718502635301</v>
+        <v>144.44314691977866</v>
       </c>
     </row>
     <row r="259" spans="2:8">
@@ -15789,19 +15792,19 @@
         <v>672</v>
       </c>
       <c r="C259">
-        <v>27.760199175814339</v>
+        <v>27.618525615289947</v>
       </c>
       <c r="D259">
-        <v>125.88103620782169</v>
+        <v>125.82791747356694</v>
       </c>
       <c r="F259" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="G259">
-        <v>24.647167147537104</v>
+        <v>24.424451344948238</v>
       </c>
       <c r="H259">
-        <v>123.76139220881444</v>
+        <v>123.75988603755351</v>
       </c>
     </row>
     <row r="260" spans="2:8">
@@ -15809,19 +15812,19 @@
         <v>673</v>
       </c>
       <c r="C260">
-        <v>26.606723057124174</v>
+        <v>26.727683627870377</v>
       </c>
       <c r="D260">
-        <v>127.32485168540629</v>
+        <v>127.64352445927948</v>
       </c>
       <c r="F260" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="G260">
-        <v>24.824182694243067</v>
+        <v>25.107809154669543</v>
       </c>
       <c r="H260">
-        <v>125.78405903139652</v>
+        <v>125.86192830995979</v>
       </c>
     </row>
     <row r="261" spans="2:8">
@@ -15829,19 +15832,19 @@
         <v>674</v>
       </c>
       <c r="C261">
-        <v>32.796393212671738</v>
+        <v>32.838284210587084</v>
       </c>
       <c r="D261">
-        <v>132.52258740471089</v>
+        <v>132.37699501710549</v>
       </c>
       <c r="F261" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="G261">
-        <v>28.634538418324308</v>
+        <v>28.644477570897426</v>
       </c>
       <c r="H261">
-        <v>127.63432198477828</v>
+        <v>127.5517033100982</v>
       </c>
     </row>
     <row r="262" spans="2:8">
@@ -15849,19 +15852,19 @@
         <v>675</v>
       </c>
       <c r="C262">
-        <v>33.965509685513645</v>
+        <v>33.605781540023827</v>
       </c>
       <c r="D262">
-        <v>135.25457300343123</v>
+        <v>135.06616020351947</v>
       </c>
       <c r="F262" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="G262">
-        <v>28.342112352341974</v>
+        <v>28.399703529450854</v>
       </c>
       <c r="H262">
-        <v>129.46919173555284</v>
+        <v>129.21792730748413</v>
       </c>
     </row>
     <row r="263" spans="2:8">
@@ -15869,19 +15872,19 @@
         <v>676</v>
       </c>
       <c r="C263">
-        <v>31.550192137224879</v>
+        <v>31.530147176247681</v>
       </c>
       <c r="D263">
-        <v>131.70164591938115</v>
+        <v>131.57888890071339</v>
       </c>
       <c r="F263" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="G263">
-        <v>25.511898266503003</v>
+        <v>25.613675369966039</v>
       </c>
       <c r="H263">
-        <v>131.76893620506388</v>
+        <v>131.33260837546436</v>
       </c>
     </row>
     <row r="264" spans="2:8">
@@ -15889,19 +15892,19 @@
         <v>677</v>
       </c>
       <c r="C264">
-        <v>33.006234630874133</v>
+        <v>32.99133796901824</v>
       </c>
       <c r="D264">
-        <v>134.62653033705877</v>
+        <v>133.90360308216228</v>
       </c>
       <c r="F264" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="G264">
-        <v>27.760199175814339</v>
+        <v>27.618525615289947</v>
       </c>
       <c r="H264">
-        <v>125.88103620782169</v>
+        <v>125.82791747356694</v>
       </c>
     </row>
     <row r="265" spans="2:8">
@@ -15909,19 +15912,19 @@
         <v>678</v>
       </c>
       <c r="C265">
-        <v>30.285214043194767</v>
+        <v>30.260469751385287</v>
       </c>
       <c r="D265">
-        <v>129.93915805207479</v>
+        <v>129.70586495498355</v>
       </c>
       <c r="F265" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="G265">
-        <v>26.606723057124174</v>
+        <v>26.727683627870377</v>
       </c>
       <c r="H265">
-        <v>127.32485168540629</v>
+        <v>127.64352445927948</v>
       </c>
     </row>
     <row r="266" spans="2:8">
@@ -15929,19 +15932,19 @@
         <v>679</v>
       </c>
       <c r="C266">
-        <v>31.935615150249681</v>
+        <v>31.880169043997025</v>
       </c>
       <c r="D266">
-        <v>129.11096992059461</v>
+        <v>129.02328718276993</v>
       </c>
       <c r="F266" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="G266">
-        <v>32.796393212671738</v>
+        <v>32.838284210587084</v>
       </c>
       <c r="H266">
-        <v>132.52258740471089</v>
+        <v>132.37699501710549</v>
       </c>
     </row>
     <row r="267" spans="2:8">
@@ -15949,19 +15952,19 @@
         <v>680</v>
       </c>
       <c r="C267">
-        <v>34.055441721886098</v>
+        <v>34.168001890807723</v>
       </c>
       <c r="D267">
-        <v>130.59135620561543</v>
+        <v>130.66843087193791</v>
       </c>
       <c r="F267" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="G267">
-        <v>33.965509685513645</v>
+        <v>33.605781540023827</v>
       </c>
       <c r="H267">
-        <v>135.25457300343123</v>
+        <v>135.06616020351947</v>
       </c>
     </row>
     <row r="268" spans="2:8">
@@ -15969,19 +15972,19 @@
         <v>681</v>
       </c>
       <c r="C268">
-        <v>33.409055210459087</v>
+        <v>33.449768320720089</v>
       </c>
       <c r="D268">
-        <v>128.79554670645661</v>
+        <v>128.72012778262751</v>
       </c>
       <c r="F268" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="G268">
-        <v>31.550192137224879</v>
+        <v>31.530147176247681</v>
       </c>
       <c r="H268">
-        <v>131.70164591938115</v>
+        <v>131.57888890071339</v>
       </c>
     </row>
     <row r="269" spans="2:8">
@@ -15989,19 +15992,19 @@
         <v>682</v>
       </c>
       <c r="C269">
-        <v>43.198532086418936</v>
+        <v>43.467569198107689</v>
       </c>
       <c r="D269">
-        <v>140.92789175632942</v>
+        <v>140.8451250235658</v>
       </c>
       <c r="F269" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="G269">
-        <v>33.006234630874133</v>
+        <v>32.99133796901824</v>
       </c>
       <c r="H269">
-        <v>134.62653033705877</v>
+        <v>133.90360308216228</v>
       </c>
     </row>
     <row r="270" spans="2:8">
@@ -16009,19 +16012,19 @@
         <v>683</v>
       </c>
       <c r="C270">
-        <v>41.449853601398999</v>
+        <v>41.503085916868486</v>
       </c>
       <c r="D270">
-        <v>142.07930331134563</v>
+        <v>141.91802299370221</v>
       </c>
       <c r="F270" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="G270">
-        <v>30.285214043194767</v>
+        <v>30.260469751385287</v>
       </c>
       <c r="H270">
-        <v>129.93915805207479</v>
+        <v>129.70586495498355</v>
       </c>
     </row>
     <row r="271" spans="2:8">
@@ -16029,19 +16032,19 @@
         <v>684</v>
       </c>
       <c r="C271">
-        <v>41.382257626347794</v>
+        <v>41.25000463168243</v>
       </c>
       <c r="D271">
-        <v>140.21980443639964</v>
+        <v>140.24751220109255</v>
       </c>
       <c r="F271" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="G271">
-        <v>31.935615150249681</v>
+        <v>31.880169043997025</v>
       </c>
       <c r="H271">
-        <v>129.11096992059461</v>
+        <v>129.02328718276993</v>
       </c>
     </row>
     <row r="272" spans="2:8">
@@ -16049,19 +16052,19 @@
         <v>685</v>
       </c>
       <c r="C272">
-        <v>42.767607745467593</v>
+        <v>42.494097202990481</v>
       </c>
       <c r="D272">
-        <v>144.72231619899657</v>
+        <v>144.36088659713727</v>
       </c>
       <c r="F272" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="G272">
-        <v>34.055441721886098</v>
+        <v>34.168001890807723</v>
       </c>
       <c r="H272">
-        <v>130.59135620561543</v>
+        <v>130.66843087193791</v>
       </c>
     </row>
     <row r="273" spans="2:8">
@@ -16072,16 +16075,16 @@
         <v>43.947965722856047</v>
       </c>
       <c r="D273">
-        <v>144.48680019910688</v>
+        <v>144.66187355698406</v>
       </c>
       <c r="F273" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="G273">
-        <v>33.409055210459087</v>
+        <v>33.449768320720089</v>
       </c>
       <c r="H273">
-        <v>128.79554670645661</v>
+        <v>128.72012778262751</v>
       </c>
     </row>
     <row r="274" spans="2:8">
@@ -16089,19 +16092,19 @@
         <v>687</v>
       </c>
       <c r="C274">
-        <v>44.697399359293172</v>
+        <v>44.814613560885753</v>
       </c>
       <c r="D274">
-        <v>144.6438108657</v>
+        <v>144.24463673704989</v>
       </c>
       <c r="F274" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="G274">
-        <v>43.198532086418936</v>
+        <v>43.467569198107689</v>
       </c>
       <c r="H274">
-        <v>140.92789175632942</v>
+        <v>140.8451250235658</v>
       </c>
     </row>
     <row r="275" spans="2:8">
@@ -16109,19 +16112,19 @@
         <v>688</v>
       </c>
       <c r="C275">
-        <v>44.62245599564946</v>
+        <v>44.772620433183782</v>
       </c>
       <c r="D275">
-        <v>140.22939558571642</v>
+        <v>140.47760045996375</v>
       </c>
       <c r="F275" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="G275">
-        <v>41.449853601398999</v>
+        <v>41.503085916868486</v>
       </c>
       <c r="H275">
-        <v>142.07930331134563</v>
+        <v>141.91802299370221</v>
       </c>
     </row>
     <row r="276" spans="2:8">
@@ -16129,19 +16132,19 @@
         <v>689</v>
       </c>
       <c r="C276">
-        <v>45.521776359374002</v>
+        <v>45.593282516097815</v>
       </c>
       <c r="D276">
-        <v>141.89612420032034</v>
+        <v>141.87681973346676</v>
       </c>
       <c r="F276" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="G276">
-        <v>41.382257626347794</v>
+        <v>41.25000463168243</v>
       </c>
       <c r="H276">
-        <v>140.21980443639964</v>
+        <v>140.24751220109255</v>
       </c>
     </row>
     <row r="277" spans="2:8">
@@ -16149,19 +16152,19 @@
         <v>690</v>
       </c>
       <c r="C277">
-        <v>44.959701132046163</v>
+        <v>45.136267941625377</v>
       </c>
       <c r="D277">
-        <v>143.19146219971361</v>
+        <v>143.28434044747988</v>
       </c>
       <c r="F277" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="G277">
-        <v>42.767607745467593</v>
+        <v>42.494097202990481</v>
       </c>
       <c r="H277">
-        <v>144.72231619899657</v>
+        <v>144.36088659713727</v>
       </c>
     </row>
     <row r="278" spans="2:8">
@@ -16169,19 +16172,19 @@
         <v>691</v>
       </c>
       <c r="C278">
-        <v>39.345561508501049</v>
+        <v>39.128778294769006</v>
       </c>
       <c r="D278">
-        <v>139.05607831929763</v>
+        <v>139.13705161724229</v>
       </c>
       <c r="F278" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="G278">
         <v>43.947965722856047</v>
       </c>
       <c r="H278">
-        <v>144.48680019910688</v>
+        <v>144.66187355698406</v>
       </c>
     </row>
     <row r="279" spans="2:8">
@@ -16189,19 +16192,19 @@
         <v>692</v>
       </c>
       <c r="C279">
-        <v>37.877553267715399</v>
+        <v>37.848165429839419</v>
       </c>
       <c r="D279">
-        <v>138.12786820208541</v>
+        <v>138.26086497295543</v>
       </c>
       <c r="F279" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="G279">
-        <v>44.697399359293172</v>
+        <v>44.814613560885753</v>
       </c>
       <c r="H279">
-        <v>144.6438108657</v>
+        <v>144.24463673704989</v>
       </c>
     </row>
     <row r="280" spans="2:8">
@@ -16209,19 +16212,19 @@
         <v>693</v>
       </c>
       <c r="C280">
-        <v>37.315478040387561</v>
+        <v>37.339743479830958</v>
       </c>
       <c r="D280">
-        <v>136.59701420280243</v>
+        <v>136.58703046975728</v>
       </c>
       <c r="F280" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="G280">
-        <v>44.62245599564946</v>
+        <v>44.772620433183782</v>
       </c>
       <c r="H280">
-        <v>140.22939558571642</v>
+        <v>140.47760045996375</v>
       </c>
     </row>
     <row r="281" spans="2:8">
@@ -16229,19 +16232,19 @@
         <v>694</v>
       </c>
       <c r="C281">
-        <v>38.597009558695028</v>
+        <v>38.235138003058616</v>
       </c>
       <c r="D281">
-        <v>136.66766900276934</v>
+        <v>136.94067076221</v>
       </c>
       <c r="F281" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="G281">
-        <v>45.521776359374002</v>
+        <v>45.593282516097815</v>
       </c>
       <c r="H281">
-        <v>141.89612420032034</v>
+        <v>141.87681973346676</v>
       </c>
     </row>
     <row r="282" spans="2:8">
@@ -16249,19 +16252,19 @@
         <v>695</v>
       </c>
       <c r="C282">
-        <v>34.920172840852004</v>
+        <v>34.877613599360245</v>
       </c>
       <c r="D282">
-        <v>130.06597435970772</v>
+        <v>130.13660409704076</v>
       </c>
       <c r="F282" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="G282">
-        <v>44.959701132046163</v>
+        <v>45.136267941625377</v>
       </c>
       <c r="H282">
-        <v>143.19146219971361</v>
+        <v>143.28434044747988</v>
       </c>
     </row>
     <row r="283" spans="2:8">
@@ -16269,19 +16272,19 @@
         <v>696</v>
       </c>
       <c r="C283">
-        <v>35.577368491266093</v>
+        <v>35.545155354656785</v>
       </c>
       <c r="D283">
-        <v>132.02256882032972</v>
+        <v>131.94831458682509</v>
       </c>
       <c r="F283" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="G283">
-        <v>39.345561508501049</v>
+        <v>39.128778294769006</v>
       </c>
       <c r="H283">
-        <v>139.05607831929763</v>
+        <v>139.13705161724229</v>
       </c>
     </row>
     <row r="284" spans="2:8">
@@ -16289,19 +16292,19 @@
         <v>697</v>
       </c>
       <c r="C284">
-        <v>37.592768485869293</v>
+        <v>37.252062064729245</v>
       </c>
       <c r="D284">
-        <v>133.24483647103926</v>
+        <v>133.123035207388</v>
       </c>
       <c r="F284" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="G284">
-        <v>37.877553267715399</v>
+        <v>37.848165429839419</v>
       </c>
       <c r="H284">
-        <v>138.12786820208541</v>
+        <v>138.26086497295543</v>
       </c>
     </row>
     <row r="285" spans="2:8">
@@ -16309,19 +16312,19 @@
         <v>698</v>
       </c>
       <c r="C285">
-        <v>36.303742631197451</v>
+        <v>36.303315274178594</v>
       </c>
       <c r="D285">
-        <v>135.77270820318856</v>
+        <v>135.75393144151963</v>
       </c>
       <c r="F285" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="G285">
-        <v>37.315478040387561</v>
+        <v>37.339743479830958</v>
       </c>
       <c r="H285">
-        <v>136.59701420280243</v>
+        <v>136.58703046975728</v>
       </c>
     </row>
     <row r="286" spans="2:8">
@@ -16329,19 +16332,19 @@
         <v>699</v>
       </c>
       <c r="C286">
-        <v>36.327408956558621</v>
+        <v>36.170460743581494</v>
       </c>
       <c r="D286">
-        <v>134.24805199337632</v>
+        <v>134.12233717644077</v>
       </c>
       <c r="F286" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="G286">
-        <v>38.597009558695028</v>
+        <v>38.235138003058616</v>
       </c>
       <c r="H286">
-        <v>136.66766900276934</v>
+        <v>136.94067076221</v>
       </c>
     </row>
     <row r="287" spans="2:8">
@@ -16349,19 +16352,19 @@
         <v>700</v>
       </c>
       <c r="C287">
-        <v>26.989353149764732</v>
+        <v>27.204888006162541</v>
       </c>
       <c r="D287">
-        <v>141.88490915270651</v>
+        <v>142.12237465999934</v>
       </c>
       <c r="F287" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="G287">
-        <v>34.920172840852004</v>
+        <v>34.877613599360245</v>
       </c>
       <c r="H287">
-        <v>130.06597435970772</v>
+        <v>130.13660409704076</v>
       </c>
     </row>
     <row r="288" spans="2:8">
@@ -16369,19 +16372,19 @@
         <v>701</v>
       </c>
       <c r="C288">
-        <v>23.983053648171296</v>
+        <v>23.439998949464769</v>
       </c>
       <c r="D288">
-        <v>153.43640819491492</v>
+        <v>153.12021637002653</v>
       </c>
       <c r="F288" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="G288">
-        <v>35.577368491266093</v>
+        <v>35.545155354656785</v>
       </c>
       <c r="H288">
-        <v>132.02256882032972</v>
+        <v>131.94831458682509</v>
       </c>
     </row>
     <row r="289" spans="2:8">
@@ -16389,19 +16392,19 @@
         <v>702</v>
       </c>
       <c r="C289">
-        <v>24.741052240453403</v>
+        <v>24.796014527638562</v>
       </c>
       <c r="D289">
-        <v>141.39144705769962</v>
+        <v>141.26023535130909</v>
       </c>
       <c r="F289" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="G289">
-        <v>37.592768485869293</v>
+        <v>37.252062064729245</v>
       </c>
       <c r="H289">
-        <v>133.24483647103926</v>
+        <v>133.123035207388</v>
       </c>
     </row>
     <row r="290" spans="2:8">
@@ -16409,19 +16412,19 @@
         <v>703</v>
       </c>
       <c r="C290">
-        <v>22.863899417758542</v>
+        <v>23.298235018493006</v>
       </c>
       <c r="D290">
-        <v>141.18957620065129</v>
+        <v>141.64045430982983</v>
       </c>
       <c r="F290" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="G290">
-        <v>36.303742631197451</v>
+        <v>36.303315274178594</v>
       </c>
       <c r="H290">
-        <v>135.77270820318856</v>
+        <v>135.75393144151963</v>
       </c>
     </row>
     <row r="291" spans="2:8">
@@ -16429,19 +16432,19 @@
         <v>704</v>
       </c>
       <c r="C291">
-        <v>31.113914698870417</v>
+        <v>31.434970526406527</v>
       </c>
       <c r="D291">
-        <v>139.50171153477521</v>
+        <v>139.74818097983936</v>
       </c>
       <c r="F291" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="G291">
-        <v>36.327408956558621</v>
+        <v>36.170460743581494</v>
       </c>
       <c r="H291">
-        <v>134.24805199337632</v>
+        <v>134.12233717644077</v>
       </c>
     </row>
     <row r="292" spans="2:8">
@@ -16449,19 +16452,19 @@
         <v>705</v>
       </c>
       <c r="C292">
-        <v>34.205328449173521</v>
+        <v>34.397127615176323</v>
       </c>
       <c r="D292">
-        <v>137.73534153560257</v>
+        <v>137.7222660013698</v>
       </c>
       <c r="F292" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="G292">
-        <v>26.989353149764732</v>
+        <v>27.204888006162541</v>
       </c>
       <c r="H292">
-        <v>141.88490915270651</v>
+        <v>142.12237465999934</v>
       </c>
     </row>
     <row r="293" spans="2:8">
@@ -16469,19 +16472,19 @@
         <v>706</v>
       </c>
       <c r="C293">
-        <v>33.580800418809254</v>
+        <v>33.549028912729732</v>
       </c>
       <c r="D293">
-        <v>139.54096420142346</v>
+        <v>139.63363489281076</v>
       </c>
       <c r="F293" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="G293">
-        <v>23.983053648171296</v>
+        <v>23.439998949464769</v>
       </c>
       <c r="H293">
-        <v>153.43640819491492</v>
+        <v>153.12021637002653</v>
       </c>
     </row>
     <row r="294" spans="2:8">
@@ -16489,19 +16492,19 @@
         <v>707</v>
       </c>
       <c r="C294">
-        <v>37.877553267715399</v>
+        <v>37.97171208671584</v>
       </c>
       <c r="D294">
-        <v>142.22584660016591</v>
+        <v>141.96863025997928</v>
       </c>
       <c r="F294" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="G294">
-        <v>24.741052240453403</v>
+        <v>24.796014527638562</v>
       </c>
       <c r="H294">
-        <v>141.39144705769962</v>
+        <v>141.26023535130909</v>
       </c>
     </row>
     <row r="295" spans="2:8">
@@ -16509,19 +16512,19 @@
         <v>708</v>
       </c>
       <c r="C295">
-        <v>39.001703722371083</v>
+        <v>39.208144574744267</v>
       </c>
       <c r="D295">
-        <v>141.99033060027622</v>
+        <v>142.06208299152522</v>
       </c>
       <c r="F295" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="G295">
-        <v>22.863899417758542</v>
+        <v>23.298235018493006</v>
       </c>
       <c r="H295">
-        <v>141.18957620065129</v>
+        <v>141.64045430982983</v>
       </c>
     </row>
     <row r="296" spans="2:8">
@@ -16529,19 +16532,19 @@
         <v>709</v>
       </c>
       <c r="C296">
-        <v>36.528572722128587</v>
+        <v>36.679210421320136</v>
       </c>
       <c r="D296">
-        <v>141.18957620065129</v>
+        <v>141.29428382626909</v>
       </c>
       <c r="F296" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="G296">
-        <v>31.113914698870417</v>
+        <v>31.434970526406527</v>
       </c>
       <c r="H296">
-        <v>139.50171153477521</v>
+        <v>139.74818097983936</v>
       </c>
     </row>
     <row r="297" spans="2:8">
@@ -16549,74 +16552,74 @@
         <v>710</v>
       </c>
       <c r="C297">
-        <v>35.254535540185486</v>
+        <v>35.147697605955742</v>
       </c>
       <c r="D297">
-        <v>140.24751220109255</v>
+        <v>140.36658879545362</v>
       </c>
       <c r="F297" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="G297">
-        <v>34.205328449173521</v>
+        <v>34.397127615176323</v>
       </c>
       <c r="H297">
-        <v>137.73534153560257</v>
+        <v>137.7222660013698</v>
       </c>
     </row>
     <row r="298" spans="2:8">
       <c r="F298" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="G298">
-        <v>33.580800418809254</v>
+        <v>33.549028912729732</v>
       </c>
       <c r="H298">
-        <v>139.54096420142346</v>
+        <v>139.63363489281076</v>
       </c>
     </row>
     <row r="299" spans="2:8">
       <c r="F299" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="G299">
-        <v>37.877553267715399</v>
+        <v>37.97171208671584</v>
       </c>
       <c r="H299">
-        <v>142.22584660016591</v>
+        <v>141.96863025997928</v>
       </c>
     </row>
     <row r="300" spans="2:8">
       <c r="F300" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="G300">
-        <v>39.001703722371083</v>
+        <v>39.208144574744267</v>
       </c>
       <c r="H300">
-        <v>141.99033060027622</v>
+        <v>142.06208299152522</v>
       </c>
     </row>
     <row r="301" spans="2:8">
       <c r="F301" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="G301">
-        <v>36.528572722128587</v>
+        <v>36.679210421320136</v>
       </c>
       <c r="H301">
-        <v>141.18957620065129</v>
+        <v>141.29428382626909</v>
       </c>
     </row>
     <row r="302" spans="2:8">
       <c r="F302" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="G302">
-        <v>35.254535540185486</v>
+        <v>35.147697605955742</v>
       </c>
       <c r="H302">
-        <v>140.24751220109255</v>
+        <v>140.36658879545362</v>
       </c>
     </row>
   </sheetData>
@@ -16625,7 +16628,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{859EFA80-2533-4AA0-AEA3-B5F9B46BFCDA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7AC2C85-9502-481B-B568-A0D69649E6CA}">
   <dimension ref="B9:L302"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -16689,13 +16692,13 @@
         <v>712</v>
       </c>
       <c r="J11" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K11" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="L11" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="12" spans="2:12">
@@ -16718,13 +16721,13 @@
         <v>713</v>
       </c>
       <c r="J12" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K12" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="L12" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="13" spans="2:12">
@@ -16747,13 +16750,13 @@
         <v>713</v>
       </c>
       <c r="J13" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K13" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="L13" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="14" spans="2:12">
@@ -16776,13 +16779,13 @@
         <v>714</v>
       </c>
       <c r="J14" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="L14" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="15" spans="2:12">
@@ -16805,13 +16808,13 @@
         <v>714</v>
       </c>
       <c r="J15" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K15" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="L15" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -16834,13 +16837,13 @@
         <v>715</v>
       </c>
       <c r="J16" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K16" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="L16" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="17" spans="2:12">
@@ -16863,13 +16866,13 @@
         <v>716</v>
       </c>
       <c r="J17" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K17" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="L17" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="18" spans="2:12">
@@ -16892,13 +16895,13 @@
         <v>717</v>
       </c>
       <c r="J18" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K18" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="L18" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="19" spans="2:12">
@@ -16921,13 +16924,13 @@
         <v>714</v>
       </c>
       <c r="J19" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="L19" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="20" spans="2:12">
@@ -16950,13 +16953,13 @@
         <v>718</v>
       </c>
       <c r="J20" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K20" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="L20" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="21" spans="2:12">
@@ -16979,13 +16982,13 @@
         <v>719</v>
       </c>
       <c r="J21" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K21" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="L21" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="22" spans="2:12">
@@ -17008,13 +17011,13 @@
         <v>720</v>
       </c>
       <c r="J22" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K22" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="L22" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="23" spans="2:12">
@@ -17037,13 +17040,13 @@
         <v>721</v>
       </c>
       <c r="J23" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K23" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="L23" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="24" spans="2:12">
@@ -17066,13 +17069,13 @@
         <v>722</v>
       </c>
       <c r="J24" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K24" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="L24" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="25" spans="2:12">
@@ -17095,13 +17098,13 @@
         <v>723</v>
       </c>
       <c r="J25" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K25" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="L25" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="26" spans="2:12">
@@ -17124,13 +17127,13 @@
         <v>722</v>
       </c>
       <c r="J26" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K26" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="L26" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="27" spans="2:12">
@@ -17153,13 +17156,13 @@
         <v>722</v>
       </c>
       <c r="J27" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K27" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="L27" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="28" spans="2:12">
@@ -17182,13 +17185,13 @@
         <v>721</v>
       </c>
       <c r="J28" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K28" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="L28" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="29" spans="2:12">
@@ -17211,13 +17214,13 @@
         <v>724</v>
       </c>
       <c r="J29" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K29" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="L29" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="30" spans="2:12">
@@ -17240,13 +17243,13 @@
         <v>725</v>
       </c>
       <c r="J30" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K30" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="L30" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="31" spans="2:12">
@@ -17269,13 +17272,13 @@
         <v>726</v>
       </c>
       <c r="J31" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K31" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="L31" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="32" spans="2:12">
@@ -17298,13 +17301,13 @@
         <v>727</v>
       </c>
       <c r="J32" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K32" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="L32" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="33" spans="2:12">
@@ -17327,13 +17330,13 @@
         <v>716</v>
       </c>
       <c r="J33" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K33" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="L33" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="34" spans="2:12">
@@ -17356,13 +17359,13 @@
         <v>714</v>
       </c>
       <c r="J34" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K34" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="L34" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="35" spans="2:12">
@@ -17385,13 +17388,13 @@
         <v>728</v>
       </c>
       <c r="J35" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K35" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="L35" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="36" spans="2:12">
@@ -17414,13 +17417,13 @@
         <v>729</v>
       </c>
       <c r="J36" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K36" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="L36" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="37" spans="2:12">
@@ -17443,13 +17446,13 @@
         <v>730</v>
       </c>
       <c r="J37" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K37" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="L37" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="38" spans="2:12">
@@ -17472,13 +17475,13 @@
         <v>716</v>
       </c>
       <c r="J38" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K38" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="L38" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="39" spans="2:12">
@@ -17501,13 +17504,13 @@
         <v>715</v>
       </c>
       <c r="J39" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K39" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="L39" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="40" spans="2:12">
@@ -17530,13 +17533,13 @@
         <v>715</v>
       </c>
       <c r="J40" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K40" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="L40" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="41" spans="2:12">
@@ -17559,13 +17562,13 @@
         <v>731</v>
       </c>
       <c r="J41" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K41" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="L41" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="42" spans="2:12">
@@ -17588,13 +17591,13 @@
         <v>728</v>
       </c>
       <c r="J42" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K42" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="L42" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="43" spans="2:12">
@@ -17617,13 +17620,13 @@
         <v>721</v>
       </c>
       <c r="J43" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K43" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="L43" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="44" spans="2:12">
@@ -17646,13 +17649,13 @@
         <v>732</v>
       </c>
       <c r="J44" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K44" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="L44" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="45" spans="2:12">
@@ -17675,13 +17678,13 @@
         <v>733</v>
       </c>
       <c r="J45" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K45" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="L45" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="46" spans="2:12">
@@ -17704,13 +17707,13 @@
         <v>728</v>
       </c>
       <c r="J46" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K46" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="L46" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="47" spans="2:12">
@@ -17733,13 +17736,13 @@
         <v>712</v>
       </c>
       <c r="J47" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K47" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="L47" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="48" spans="2:12">
@@ -17762,13 +17765,13 @@
         <v>721</v>
       </c>
       <c r="J48" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K48" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="L48" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="49" spans="2:12">
@@ -17791,13 +17794,13 @@
         <v>730</v>
       </c>
       <c r="J49" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K49" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="L49" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="50" spans="2:12">
@@ -17820,13 +17823,13 @@
         <v>734</v>
       </c>
       <c r="J50" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K50" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="L50" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="51" spans="2:12">
@@ -17849,13 +17852,13 @@
         <v>734</v>
       </c>
       <c r="J51" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K51" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="L51" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="52" spans="2:12">
@@ -17878,13 +17881,13 @@
         <v>729</v>
       </c>
       <c r="J52" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K52" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="L52" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="53" spans="2:12">
@@ -17907,13 +17910,13 @@
         <v>720</v>
       </c>
       <c r="J53" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K53" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="L53" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="54" spans="2:12">
@@ -17936,13 +17939,13 @@
         <v>721</v>
       </c>
       <c r="J54" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K54" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="L54" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="55" spans="2:12">
@@ -17965,13 +17968,13 @@
         <v>735</v>
       </c>
       <c r="J55" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K55" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="L55" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="56" spans="2:12">
@@ -17994,13 +17997,13 @@
         <v>736</v>
       </c>
       <c r="J56" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K56" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="L56" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="57" spans="2:12">
@@ -18023,13 +18026,13 @@
         <v>737</v>
       </c>
       <c r="J57" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K57" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="L57" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="58" spans="2:12">
@@ -18052,13 +18055,13 @@
         <v>737</v>
       </c>
       <c r="J58" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K58" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="L58" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="59" spans="2:12">
@@ -18081,13 +18084,13 @@
         <v>736</v>
       </c>
       <c r="J59" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K59" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="L59" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="60" spans="2:12">
@@ -18110,13 +18113,13 @@
         <v>738</v>
       </c>
       <c r="J60" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K60" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="L60" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="61" spans="2:12">
@@ -18139,13 +18142,13 @@
         <v>739</v>
       </c>
       <c r="J61" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K61" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="L61" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="62" spans="2:12">
@@ -18168,13 +18171,13 @@
         <v>740</v>
       </c>
       <c r="J62" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K62" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="L62" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="63" spans="2:12">
@@ -18197,13 +18200,13 @@
         <v>737</v>
       </c>
       <c r="J63" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K63" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="L63" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="64" spans="2:12">
@@ -18226,13 +18229,13 @@
         <v>730</v>
       </c>
       <c r="J64" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K64" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="L64" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="65" spans="2:12">
@@ -18255,13 +18258,13 @@
         <v>735</v>
       </c>
       <c r="J65" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K65" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="L65" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="66" spans="2:12">
@@ -18284,13 +18287,13 @@
         <v>722</v>
       </c>
       <c r="J66" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K66" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="L66" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="67" spans="2:12">
@@ -18313,13 +18316,13 @@
         <v>737</v>
       </c>
       <c r="J67" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K67" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="L67" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="68" spans="2:12">
@@ -18342,13 +18345,13 @@
         <v>741</v>
       </c>
       <c r="J68" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K68" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="L68" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="69" spans="2:12">
@@ -18371,13 +18374,13 @@
         <v>742</v>
       </c>
       <c r="J69" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K69" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="L69" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="70" spans="2:12">
@@ -18400,13 +18403,13 @@
         <v>742</v>
       </c>
       <c r="J70" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K70" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="L70" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="71" spans="2:12">
@@ -18429,13 +18432,13 @@
         <v>727</v>
       </c>
       <c r="J71" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K71" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="L71" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="72" spans="2:12">
@@ -18458,13 +18461,13 @@
         <v>740</v>
       </c>
       <c r="J72" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K72" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="L72" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="73" spans="2:12">
@@ -18487,13 +18490,13 @@
         <v>743</v>
       </c>
       <c r="J73" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K73" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="L73" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="74" spans="2:12">
@@ -18516,13 +18519,13 @@
         <v>744</v>
       </c>
       <c r="J74" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K74" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="L74" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="75" spans="2:12">
@@ -18545,13 +18548,13 @@
         <v>745</v>
       </c>
       <c r="J75" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K75" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="L75" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="76" spans="2:12">
@@ -18574,13 +18577,13 @@
         <v>746</v>
       </c>
       <c r="J76" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K76" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="L76" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="77" spans="2:12">
@@ -18603,13 +18606,13 @@
         <v>746</v>
       </c>
       <c r="J77" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K77" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="L77" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="78" spans="2:12">
@@ -18632,13 +18635,13 @@
         <v>720</v>
       </c>
       <c r="J78" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K78" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="L78" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="79" spans="2:12">
@@ -18661,13 +18664,13 @@
         <v>747</v>
       </c>
       <c r="J79" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K79" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="L79" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="80" spans="2:12">
@@ -18690,13 +18693,13 @@
         <v>720</v>
       </c>
       <c r="J80" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K80" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="L80" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="81" spans="2:12">
@@ -18719,13 +18722,13 @@
         <v>747</v>
       </c>
       <c r="J81" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K81" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="L81" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="82" spans="2:12">
@@ -18748,13 +18751,13 @@
         <v>748</v>
       </c>
       <c r="J82" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K82" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="L82" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="83" spans="2:12">
@@ -18777,13 +18780,13 @@
         <v>740</v>
       </c>
       <c r="J83" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K83" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="L83" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="84" spans="2:12">
@@ -18806,13 +18809,13 @@
         <v>741</v>
       </c>
       <c r="J84" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K84" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="L84" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="85" spans="2:12">
@@ -18835,13 +18838,13 @@
         <v>712</v>
       </c>
       <c r="J85" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K85" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="L85" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="86" spans="2:12">
@@ -18864,13 +18867,13 @@
         <v>714</v>
       </c>
       <c r="J86" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K86" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="L86" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="87" spans="2:12">
@@ -18893,13 +18896,13 @@
         <v>719</v>
       </c>
       <c r="J87" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K87" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="L87" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="88" spans="2:12">
@@ -18922,13 +18925,13 @@
         <v>749</v>
       </c>
       <c r="J88" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K88" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="L88" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="89" spans="2:12">
@@ -18951,13 +18954,13 @@
         <v>722</v>
       </c>
       <c r="J89" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K89" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="L89" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="90" spans="2:12">
@@ -18980,13 +18983,13 @@
         <v>716</v>
       </c>
       <c r="J90" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K90" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="L90" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="91" spans="2:12">
@@ -19009,13 +19012,13 @@
         <v>716</v>
       </c>
       <c r="J91" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K91" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="L91" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="92" spans="2:12">
@@ -19038,13 +19041,13 @@
         <v>750</v>
       </c>
       <c r="J92" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K92" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="L92" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="93" spans="2:12">
@@ -19067,13 +19070,13 @@
         <v>742</v>
       </c>
       <c r="J93" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K93" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="L93" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="94" spans="2:12">
@@ -19096,13 +19099,13 @@
         <v>751</v>
       </c>
       <c r="J94" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K94" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="L94" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="95" spans="2:12">
@@ -19125,13 +19128,13 @@
         <v>751</v>
       </c>
       <c r="J95" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K95" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="L95" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="96" spans="2:12">
@@ -19154,13 +19157,13 @@
         <v>731</v>
       </c>
       <c r="J96" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K96" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="L96" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="97" spans="2:12">
@@ -19183,13 +19186,13 @@
         <v>744</v>
       </c>
       <c r="J97" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K97" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="L97" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="98" spans="2:12">
@@ -19212,13 +19215,13 @@
         <v>731</v>
       </c>
       <c r="J98" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K98" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="L98" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="99" spans="2:12">
@@ -19241,13 +19244,13 @@
         <v>727</v>
       </c>
       <c r="J99" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K99" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="L99" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="100" spans="2:12">
@@ -19270,13 +19273,13 @@
         <v>712</v>
       </c>
       <c r="J100" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K100" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="L100" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="101" spans="2:12">
@@ -19299,13 +19302,13 @@
         <v>717</v>
       </c>
       <c r="J101" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K101" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="L101" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="102" spans="2:12">
@@ -19328,13 +19331,13 @@
         <v>752</v>
       </c>
       <c r="J102" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K102" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="L102" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="103" spans="2:12">
@@ -19357,13 +19360,13 @@
         <v>749</v>
       </c>
       <c r="J103" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K103" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="L103" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="104" spans="2:12">
@@ -19386,13 +19389,13 @@
         <v>717</v>
       </c>
       <c r="J104" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K104" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="L104" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="105" spans="2:12">
@@ -19415,13 +19418,13 @@
         <v>730</v>
       </c>
       <c r="J105" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K105" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="L105" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="106" spans="2:12">
@@ -19444,13 +19447,13 @@
         <v>714</v>
       </c>
       <c r="J106" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K106" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="L106" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="107" spans="2:12">
@@ -19473,13 +19476,13 @@
         <v>714</v>
       </c>
       <c r="J107" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K107" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="L107" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="108" spans="2:12">
@@ -19502,13 +19505,13 @@
         <v>750</v>
       </c>
       <c r="J108" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K108" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="L108" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="109" spans="2:12">
@@ -19531,13 +19534,13 @@
         <v>730</v>
       </c>
       <c r="J109" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K109" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="L109" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="110" spans="2:12">
@@ -19560,13 +19563,13 @@
         <v>752</v>
       </c>
       <c r="J110" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K110" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="L110" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="111" spans="2:12">
@@ -19589,13 +19592,13 @@
         <v>714</v>
       </c>
       <c r="J111" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K111" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="L111" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="112" spans="2:12">
@@ -19618,13 +19621,13 @@
         <v>736</v>
       </c>
       <c r="J112" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K112" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="L112" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="113" spans="2:12">
@@ -19647,13 +19650,13 @@
         <v>740</v>
       </c>
       <c r="J113" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K113" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="L113" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="114" spans="2:12">
@@ -19676,13 +19679,13 @@
         <v>728</v>
       </c>
       <c r="J114" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K114" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="L114" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="115" spans="2:12">
@@ -19705,13 +19708,13 @@
         <v>724</v>
       </c>
       <c r="J115" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K115" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="L115" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="116" spans="2:12">
@@ -19734,13 +19737,13 @@
         <v>750</v>
       </c>
       <c r="J116" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K116" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="L116" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="117" spans="2:12">
@@ -19763,13 +19766,13 @@
         <v>731</v>
       </c>
       <c r="J117" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K117" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="L117" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="118" spans="2:12">
@@ -19792,13 +19795,13 @@
         <v>716</v>
       </c>
       <c r="J118" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K118" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="L118" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="119" spans="2:12">
@@ -19821,13 +19824,13 @@
         <v>723</v>
       </c>
       <c r="J119" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K119" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="L119" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="120" spans="2:12">
@@ -19850,13 +19853,13 @@
         <v>733</v>
       </c>
       <c r="J120" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K120" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="L120" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="121" spans="2:12">
@@ -19879,13 +19882,13 @@
         <v>753</v>
       </c>
       <c r="J121" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K121" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="L121" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="122" spans="2:12">
@@ -19908,13 +19911,13 @@
         <v>753</v>
       </c>
       <c r="J122" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K122" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="L122" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="123" spans="2:12">
@@ -19937,13 +19940,13 @@
         <v>753</v>
       </c>
       <c r="J123" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K123" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="L123" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="124" spans="2:12">
@@ -19966,13 +19969,13 @@
         <v>715</v>
       </c>
       <c r="J124" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K124" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="L124" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="125" spans="2:12">
@@ -19995,13 +19998,13 @@
         <v>714</v>
       </c>
       <c r="J125" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K125" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="L125" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="126" spans="2:12">
@@ -20024,13 +20027,13 @@
         <v>726</v>
       </c>
       <c r="J126" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K126" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="L126" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="127" spans="2:12">
@@ -20053,13 +20056,13 @@
         <v>731</v>
       </c>
       <c r="J127" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K127" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="L127" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="128" spans="2:12">
@@ -20082,13 +20085,13 @@
         <v>750</v>
       </c>
       <c r="J128" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K128" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="L128" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="129" spans="2:12">
@@ -20111,13 +20114,13 @@
         <v>729</v>
       </c>
       <c r="J129" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K129" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="L129" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="130" spans="2:12">
@@ -20140,13 +20143,13 @@
         <v>734</v>
       </c>
       <c r="J130" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K130" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="L130" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="131" spans="2:12">
@@ -20169,13 +20172,13 @@
         <v>729</v>
       </c>
       <c r="J131" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K131" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="L131" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="132" spans="2:12">
@@ -20198,13 +20201,13 @@
         <v>720</v>
       </c>
       <c r="J132" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K132" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="L132" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="133" spans="2:12">
@@ -20227,13 +20230,13 @@
         <v>751</v>
       </c>
       <c r="J133" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K133" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="L133" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="134" spans="2:12">
@@ -20256,13 +20259,13 @@
         <v>716</v>
       </c>
       <c r="J134" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K134" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="L134" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="135" spans="2:12">
@@ -20285,13 +20288,13 @@
         <v>754</v>
       </c>
       <c r="J135" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K135" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="L135" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="136" spans="2:12">
@@ -20314,13 +20317,13 @@
         <v>717</v>
       </c>
       <c r="J136" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K136" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="L136" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="137" spans="2:12">
@@ -20343,13 +20346,13 @@
         <v>739</v>
       </c>
       <c r="J137" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K137" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="L137" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="138" spans="2:12">
@@ -20372,13 +20375,13 @@
         <v>730</v>
       </c>
       <c r="J138" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K138" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="L138" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="139" spans="2:12">
@@ -20401,13 +20404,13 @@
         <v>730</v>
       </c>
       <c r="J139" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K139" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="L139" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="140" spans="2:12">
@@ -20430,13 +20433,13 @@
         <v>730</v>
       </c>
       <c r="J140" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K140" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="L140" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="141" spans="2:12">
@@ -20459,13 +20462,13 @@
         <v>730</v>
       </c>
       <c r="J141" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K141" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="L141" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="142" spans="2:12">
@@ -20488,13 +20491,13 @@
         <v>752</v>
       </c>
       <c r="J142" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K142" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="L142" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="143" spans="2:12">
@@ -20517,13 +20520,13 @@
         <v>744</v>
       </c>
       <c r="J143" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K143" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="L143" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="144" spans="2:12">
@@ -20546,13 +20549,13 @@
         <v>744</v>
       </c>
       <c r="J144" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K144" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="L144" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="145" spans="2:12">
@@ -20575,13 +20578,13 @@
         <v>715</v>
       </c>
       <c r="J145" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K145" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="L145" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="146" spans="2:12">
@@ -20604,13 +20607,13 @@
         <v>715</v>
       </c>
       <c r="J146" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K146" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="L146" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="147" spans="2:12">
@@ -20633,13 +20636,13 @@
         <v>715</v>
       </c>
       <c r="J147" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K147" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="L147" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="148" spans="2:12">
@@ -20662,13 +20665,13 @@
         <v>747</v>
       </c>
       <c r="J148" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K148" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="L148" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="149" spans="2:12">
@@ -20691,13 +20694,13 @@
         <v>748</v>
       </c>
       <c r="J149" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K149" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="L149" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="150" spans="2:12">
@@ -20720,13 +20723,13 @@
         <v>752</v>
       </c>
       <c r="J150" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K150" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="L150" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="151" spans="2:12">
@@ -20749,13 +20752,13 @@
         <v>732</v>
       </c>
       <c r="J151" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K151" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="L151" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="152" spans="2:12">
@@ -20778,13 +20781,13 @@
         <v>715</v>
       </c>
       <c r="J152" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K152" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="L152" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="153" spans="2:12">
@@ -20807,13 +20810,13 @@
         <v>753</v>
       </c>
       <c r="J153" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K153" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="L153" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="154" spans="2:12">
@@ -20836,13 +20839,13 @@
         <v>750</v>
       </c>
       <c r="J154" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K154" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="L154" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="155" spans="2:12">
@@ -20865,13 +20868,13 @@
         <v>750</v>
       </c>
       <c r="J155" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K155" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="L155" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="156" spans="2:12">
@@ -20894,13 +20897,13 @@
         <v>731</v>
       </c>
       <c r="J156" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K156" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="L156" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="157" spans="2:12">
@@ -20923,13 +20926,13 @@
         <v>720</v>
       </c>
       <c r="J157" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K157" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="L157" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="158" spans="2:12">
@@ -20952,13 +20955,13 @@
         <v>750</v>
       </c>
       <c r="J158" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K158" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="L158" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="159" spans="2:12">
@@ -20981,13 +20984,13 @@
         <v>750</v>
       </c>
       <c r="J159" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K159" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="L159" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="160" spans="2:12">
@@ -21010,13 +21013,13 @@
         <v>749</v>
       </c>
       <c r="J160" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K160" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="L160" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="161" spans="2:12">
@@ -21039,13 +21042,13 @@
         <v>712</v>
       </c>
       <c r="J161" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K161" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="L161" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="162" spans="2:12">
@@ -21068,13 +21071,13 @@
         <v>720</v>
       </c>
       <c r="J162" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K162" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="L162" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="163" spans="2:12">
@@ -21097,13 +21100,13 @@
         <v>727</v>
       </c>
       <c r="J163" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K163" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="L163" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="164" spans="2:12">
@@ -21126,13 +21129,13 @@
         <v>746</v>
       </c>
       <c r="J164" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K164" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="L164" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="165" spans="2:12">
@@ -21155,13 +21158,13 @@
         <v>730</v>
       </c>
       <c r="J165" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K165" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="L165" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="166" spans="2:12">
@@ -21184,13 +21187,13 @@
         <v>720</v>
       </c>
       <c r="J166" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K166" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="L166" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="167" spans="2:12">
@@ -21213,13 +21216,13 @@
         <v>712</v>
       </c>
       <c r="J167" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K167" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="L167" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="168" spans="2:12">
@@ -21242,13 +21245,13 @@
         <v>712</v>
       </c>
       <c r="J168" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K168" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="L168" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="169" spans="2:12">
@@ -21271,13 +21274,13 @@
         <v>719</v>
       </c>
       <c r="J169" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K169" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="L169" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="170" spans="2:12">
@@ -21300,13 +21303,13 @@
         <v>720</v>
       </c>
       <c r="J170" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K170" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="L170" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="171" spans="2:12">
@@ -21329,13 +21332,13 @@
         <v>743</v>
       </c>
       <c r="J171" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K171" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="L171" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="172" spans="2:12">
@@ -21358,13 +21361,13 @@
         <v>733</v>
       </c>
       <c r="J172" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K172" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="L172" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="173" spans="2:12">
@@ -21387,13 +21390,13 @@
         <v>716</v>
       </c>
       <c r="J173" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K173" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="L173" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="174" spans="2:12">
@@ -21416,13 +21419,13 @@
         <v>716</v>
       </c>
       <c r="J174" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K174" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="L174" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="175" spans="2:12">
@@ -21445,13 +21448,13 @@
         <v>716</v>
       </c>
       <c r="J175" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K175" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="L175" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="176" spans="2:12">
@@ -21474,13 +21477,13 @@
         <v>716</v>
       </c>
       <c r="J176" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K176" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="L176" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="177" spans="2:12">
@@ -21503,13 +21506,13 @@
         <v>724</v>
       </c>
       <c r="J177" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K177" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="L177" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="178" spans="2:12">
@@ -21532,13 +21535,13 @@
         <v>724</v>
       </c>
       <c r="J178" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K178" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="L178" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="179" spans="2:12">
@@ -21561,13 +21564,13 @@
         <v>724</v>
       </c>
       <c r="J179" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K179" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="L179" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="180" spans="2:12">
@@ -21590,13 +21593,13 @@
         <v>724</v>
       </c>
       <c r="J180" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K180" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="L180" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="181" spans="2:12">
@@ -21619,13 +21622,13 @@
         <v>731</v>
       </c>
       <c r="J181" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K181" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="L181" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="182" spans="2:12">
@@ -21648,13 +21651,13 @@
         <v>712</v>
       </c>
       <c r="J182" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K182" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="L182" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="183" spans="2:12">
@@ -21677,13 +21680,13 @@
         <v>755</v>
       </c>
       <c r="J183" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K183" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="L183" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="184" spans="2:12">
@@ -21706,13 +21709,13 @@
         <v>755</v>
       </c>
       <c r="J184" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K184" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="L184" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="185" spans="2:12">
@@ -21735,13 +21738,13 @@
         <v>755</v>
       </c>
       <c r="J185" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K185" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="L185" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="186" spans="2:12">
@@ -21764,13 +21767,13 @@
         <v>755</v>
       </c>
       <c r="J186" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K186" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="L186" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="187" spans="2:12">
@@ -21793,13 +21796,13 @@
         <v>755</v>
       </c>
       <c r="J187" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K187" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="L187" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="188" spans="2:12">
@@ -21822,13 +21825,13 @@
         <v>755</v>
       </c>
       <c r="J188" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K188" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="L188" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="189" spans="2:12">
@@ -21851,13 +21854,13 @@
         <v>755</v>
       </c>
       <c r="J189" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K189" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="L189" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="190" spans="2:12">
@@ -21880,13 +21883,13 @@
         <v>755</v>
       </c>
       <c r="J190" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K190" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="L190" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="191" spans="2:12">
@@ -21909,13 +21912,13 @@
         <v>755</v>
       </c>
       <c r="J191" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K191" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="L191" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="192" spans="2:12">
@@ -21938,13 +21941,13 @@
         <v>755</v>
       </c>
       <c r="J192" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K192" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="L192" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="193" spans="2:12">
@@ -21967,13 +21970,13 @@
         <v>756</v>
       </c>
       <c r="J193" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K193" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="L193" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="194" spans="2:12">
@@ -21996,13 +21999,13 @@
         <v>740</v>
       </c>
       <c r="J194" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K194" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="L194" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="195" spans="2:12">
@@ -22022,16 +22025,16 @@
         <v>711</v>
       </c>
       <c r="H195" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="J195" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K195" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="L195" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="196" spans="2:12">
@@ -22051,16 +22054,16 @@
         <v>711</v>
       </c>
       <c r="H196" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="J196" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K196" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="L196" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="197" spans="2:12">
@@ -22083,13 +22086,13 @@
         <v>744</v>
       </c>
       <c r="J197" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K197" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="L197" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="198" spans="2:12">
@@ -22112,13 +22115,13 @@
         <v>721</v>
       </c>
       <c r="J198" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K198" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="L198" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="199" spans="2:12">
@@ -22138,16 +22141,16 @@
         <v>711</v>
       </c>
       <c r="H199" t="s">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="J199" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K199" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="L199" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="200" spans="2:12">
@@ -22167,16 +22170,16 @@
         <v>711</v>
       </c>
       <c r="H200" t="s">
-        <v>720</v>
+        <v>746</v>
       </c>
       <c r="J200" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K200" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="L200" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="201" spans="2:12">
@@ -22196,16 +22199,16 @@
         <v>711</v>
       </c>
       <c r="H201" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="J201" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K201" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="L201" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="202" spans="2:12">
@@ -22225,16 +22228,16 @@
         <v>711</v>
       </c>
       <c r="H202" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="J202" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K202" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="L202" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="203" spans="2:12">
@@ -22254,16 +22257,16 @@
         <v>711</v>
       </c>
       <c r="H203" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="J203" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K203" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="L203" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="204" spans="2:12">
@@ -22286,13 +22289,13 @@
         <v>755</v>
       </c>
       <c r="J204" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K204" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="L204" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="205" spans="2:12">
@@ -22315,13 +22318,13 @@
         <v>755</v>
       </c>
       <c r="J205" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K205" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="L205" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="206" spans="2:12">
@@ -22344,13 +22347,13 @@
         <v>755</v>
       </c>
       <c r="J206" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K206" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="L206" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="207" spans="2:12">
@@ -22370,16 +22373,16 @@
         <v>711</v>
       </c>
       <c r="H207" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
       <c r="J207" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K207" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="L207" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
     </row>
     <row r="208" spans="2:12">
@@ -22402,13 +22405,13 @@
         <v>755</v>
       </c>
       <c r="J208" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K208" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="L208" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="209" spans="2:12">
@@ -22431,13 +22434,13 @@
         <v>755</v>
       </c>
       <c r="J209" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K209" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="L209" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="210" spans="2:12">
@@ -22460,13 +22463,13 @@
         <v>755</v>
       </c>
       <c r="J210" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K210" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="L210" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="211" spans="2:12">
@@ -22489,13 +22492,13 @@
         <v>755</v>
       </c>
       <c r="J211" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K211" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="L211" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="212" spans="2:12">
@@ -22518,13 +22521,13 @@
         <v>755</v>
       </c>
       <c r="J212" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K212" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="L212" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="213" spans="2:12">
@@ -22544,16 +22547,16 @@
         <v>711</v>
       </c>
       <c r="H213" t="s">
-        <v>740</v>
+        <v>725</v>
       </c>
       <c r="J213" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K213" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="L213" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="214" spans="2:12">
@@ -22576,13 +22579,13 @@
         <v>723</v>
       </c>
       <c r="J214" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K214" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="L214" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="215" spans="2:12">
@@ -22602,16 +22605,16 @@
         <v>711</v>
       </c>
       <c r="H215" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="J215" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K215" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="L215" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="216" spans="2:12">
@@ -22631,16 +22634,16 @@
         <v>711</v>
       </c>
       <c r="H216" t="s">
-        <v>740</v>
+        <v>753</v>
       </c>
       <c r="J216" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K216" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="L216" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="217" spans="2:12">
@@ -22660,16 +22663,16 @@
         <v>711</v>
       </c>
       <c r="H217" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="J217" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K217" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="L217" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="218" spans="2:12">
@@ -22692,13 +22695,13 @@
         <v>732</v>
       </c>
       <c r="J218" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K218" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="L218" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="219" spans="2:12">
@@ -22718,16 +22721,16 @@
         <v>711</v>
       </c>
       <c r="H219" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="J219" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K219" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="L219" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="220" spans="2:12">
@@ -22750,13 +22753,13 @@
         <v>757</v>
       </c>
       <c r="J220" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K220" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="L220" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="221" spans="2:12">
@@ -22779,13 +22782,13 @@
         <v>738</v>
       </c>
       <c r="J221" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K221" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="L221" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="222" spans="2:12">
@@ -22808,13 +22811,13 @@
         <v>717</v>
       </c>
       <c r="J222" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K222" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="L222" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="223" spans="2:12">
@@ -22837,13 +22840,13 @@
         <v>740</v>
       </c>
       <c r="J223" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K223" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="L223" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="224" spans="2:12">
@@ -22863,16 +22866,16 @@
         <v>711</v>
       </c>
       <c r="H224" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="J224" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K224" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="L224" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="225" spans="2:12">
@@ -22895,13 +22898,13 @@
         <v>741</v>
       </c>
       <c r="J225" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K225" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="L225" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="226" spans="2:12">
@@ -22921,16 +22924,16 @@
         <v>711</v>
       </c>
       <c r="H226" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="J226" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K226" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="L226" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="227" spans="2:12">
@@ -22950,16 +22953,16 @@
         <v>711</v>
       </c>
       <c r="H227" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="J227" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K227" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="L227" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="228" spans="2:12">
@@ -22982,13 +22985,13 @@
         <v>744</v>
       </c>
       <c r="J228" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K228" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="L228" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="229" spans="2:12">
@@ -23011,13 +23014,13 @@
         <v>721</v>
       </c>
       <c r="J229" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K229" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="L229" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="230" spans="2:12">
@@ -23040,13 +23043,13 @@
         <v>734</v>
       </c>
       <c r="J230" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K230" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="L230" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="231" spans="2:12">
@@ -23069,13 +23072,13 @@
         <v>730</v>
       </c>
       <c r="J231" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K231" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="L231" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="232" spans="2:12">
@@ -23098,13 +23101,13 @@
         <v>749</v>
       </c>
       <c r="J232" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K232" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="L232" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="233" spans="2:12">
@@ -23124,16 +23127,16 @@
         <v>711</v>
       </c>
       <c r="H233" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="J233" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K233" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="L233" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="234" spans="2:12">
@@ -23153,16 +23156,16 @@
         <v>711</v>
       </c>
       <c r="H234" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="J234" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K234" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="L234" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="235" spans="2:12">
@@ -23185,13 +23188,13 @@
         <v>716</v>
       </c>
       <c r="J235" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K235" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="L235" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="236" spans="2:12">
@@ -23211,16 +23214,16 @@
         <v>711</v>
       </c>
       <c r="H236" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="J236" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K236" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="L236" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="237" spans="2:12">
@@ -23240,16 +23243,16 @@
         <v>711</v>
       </c>
       <c r="H237" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="J237" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K237" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="L237" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="238" spans="2:12">
@@ -23269,16 +23272,16 @@
         <v>711</v>
       </c>
       <c r="H238" t="s">
-        <v>740</v>
+        <v>751</v>
       </c>
       <c r="J238" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K238" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="L238" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="239" spans="2:12">
@@ -23298,16 +23301,16 @@
         <v>711</v>
       </c>
       <c r="H239" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="J239" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K239" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="L239" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="240" spans="2:12">
@@ -23327,16 +23330,16 @@
         <v>711</v>
       </c>
       <c r="H240" t="s">
-        <v>740</v>
+        <v>758</v>
       </c>
       <c r="J240" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K240" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="L240" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="241" spans="2:12">
@@ -23356,16 +23359,16 @@
         <v>711</v>
       </c>
       <c r="H241" t="s">
-        <v>754</v>
+        <v>739</v>
       </c>
       <c r="J241" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K241" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="L241" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="242" spans="2:12">
@@ -23385,16 +23388,16 @@
         <v>711</v>
       </c>
       <c r="H242" t="s">
-        <v>740</v>
+        <v>753</v>
       </c>
       <c r="J242" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K242" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="L242" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="243" spans="2:12">
@@ -23414,16 +23417,16 @@
         <v>711</v>
       </c>
       <c r="H243" t="s">
-        <v>740</v>
+        <v>714</v>
       </c>
       <c r="J243" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K243" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="L243" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="244" spans="2:12">
@@ -23446,13 +23449,13 @@
         <v>715</v>
       </c>
       <c r="J244" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K244" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="L244" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="245" spans="2:12">
@@ -23475,13 +23478,13 @@
         <v>714</v>
       </c>
       <c r="J245" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K245" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="L245" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="246" spans="2:12">
@@ -23504,13 +23507,13 @@
         <v>738</v>
       </c>
       <c r="J246" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K246" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="L246" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="247" spans="2:12">
@@ -23533,13 +23536,13 @@
         <v>755</v>
       </c>
       <c r="J247" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K247" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="L247" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="248" spans="2:12">
@@ -23559,16 +23562,16 @@
         <v>711</v>
       </c>
       <c r="H248" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
       <c r="J248" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K248" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="L248" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="249" spans="2:12">
@@ -23591,13 +23594,13 @@
         <v>738</v>
       </c>
       <c r="J249" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K249" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="L249" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="250" spans="2:12">
@@ -23620,13 +23623,13 @@
         <v>755</v>
       </c>
       <c r="J250" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K250" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="L250" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="251" spans="2:12">
@@ -23649,13 +23652,13 @@
         <v>755</v>
       </c>
       <c r="J251" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K251" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="L251" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="252" spans="2:12">
@@ -23678,13 +23681,13 @@
         <v>755</v>
       </c>
       <c r="J252" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K252" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="L252" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="253" spans="2:12">
@@ -23707,13 +23710,13 @@
         <v>755</v>
       </c>
       <c r="J253" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K253" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="L253" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="254" spans="2:12">
@@ -23736,13 +23739,13 @@
         <v>740</v>
       </c>
       <c r="J254" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K254" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="L254" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="255" spans="2:12">
@@ -23765,13 +23768,13 @@
         <v>740</v>
       </c>
       <c r="J255" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K255" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="L255" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="256" spans="2:12">
@@ -23794,13 +23797,13 @@
         <v>740</v>
       </c>
       <c r="J256" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K256" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="L256" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="257" spans="2:12">
@@ -23820,16 +23823,16 @@
         <v>711</v>
       </c>
       <c r="H257" t="s">
-        <v>756</v>
+        <v>740</v>
       </c>
       <c r="J257" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K257" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="L257" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="258" spans="2:12">
@@ -23852,13 +23855,13 @@
         <v>740</v>
       </c>
       <c r="J258" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K258" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="L258" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="259" spans="2:12">
@@ -23881,13 +23884,13 @@
         <v>740</v>
       </c>
       <c r="J259" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K259" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="L259" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="260" spans="2:12">
@@ -23910,13 +23913,13 @@
         <v>740</v>
       </c>
       <c r="J260" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K260" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="L260" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="261" spans="2:12">
@@ -23939,13 +23942,13 @@
         <v>740</v>
       </c>
       <c r="J261" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K261" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="L261" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="262" spans="2:12">
@@ -23965,16 +23968,16 @@
         <v>711</v>
       </c>
       <c r="H262" t="s">
-        <v>719</v>
+        <v>740</v>
       </c>
       <c r="J262" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K262" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="L262" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="263" spans="2:12">
@@ -23997,13 +24000,13 @@
         <v>740</v>
       </c>
       <c r="J263" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K263" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="L263" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="264" spans="2:12">
@@ -24026,13 +24029,13 @@
         <v>740</v>
       </c>
       <c r="J264" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K264" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="L264" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="265" spans="2:12">
@@ -24055,13 +24058,13 @@
         <v>740</v>
       </c>
       <c r="J265" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K265" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="L265" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="266" spans="2:12">
@@ -24084,13 +24087,13 @@
         <v>740</v>
       </c>
       <c r="J266" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K266" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="L266" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="267" spans="2:12">
@@ -24113,13 +24116,13 @@
         <v>740</v>
       </c>
       <c r="J267" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K267" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="L267" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="268" spans="2:12">
@@ -24142,13 +24145,13 @@
         <v>740</v>
       </c>
       <c r="J268" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K268" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="L268" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="269" spans="2:12">
@@ -24168,16 +24171,16 @@
         <v>711</v>
       </c>
       <c r="H269" t="s">
-        <v>755</v>
+        <v>740</v>
       </c>
       <c r="J269" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K269" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="L269" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="270" spans="2:12">
@@ -24200,13 +24203,13 @@
         <v>740</v>
       </c>
       <c r="J270" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K270" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="L270" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="271" spans="2:12">
@@ -24229,13 +24232,13 @@
         <v>740</v>
       </c>
       <c r="J271" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K271" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="L271" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="272" spans="2:12">
@@ -24258,13 +24261,13 @@
         <v>740</v>
       </c>
       <c r="J272" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K272" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="L272" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="273" spans="2:12">
@@ -24287,13 +24290,13 @@
         <v>740</v>
       </c>
       <c r="J273" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K273" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="L273" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="274" spans="2:12">
@@ -24316,13 +24319,13 @@
         <v>740</v>
       </c>
       <c r="J274" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K274" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="L274" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="275" spans="2:12">
@@ -24345,13 +24348,13 @@
         <v>740</v>
       </c>
       <c r="J275" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K275" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="L275" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="276" spans="2:12">
@@ -24374,13 +24377,13 @@
         <v>740</v>
       </c>
       <c r="J276" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K276" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="L276" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="277" spans="2:12">
@@ -24403,13 +24406,13 @@
         <v>740</v>
       </c>
       <c r="J277" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K277" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="L277" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="278" spans="2:12">
@@ -24432,13 +24435,13 @@
         <v>740</v>
       </c>
       <c r="J278" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K278" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="L278" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="279" spans="2:12">
@@ -24461,13 +24464,13 @@
         <v>740</v>
       </c>
       <c r="J279" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K279" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="L279" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="280" spans="2:12">
@@ -24490,13 +24493,13 @@
         <v>740</v>
       </c>
       <c r="J280" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K280" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="L280" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="281" spans="2:12">
@@ -24519,13 +24522,13 @@
         <v>740</v>
       </c>
       <c r="J281" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K281" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="L281" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="282" spans="2:12">
@@ -24548,13 +24551,13 @@
         <v>740</v>
       </c>
       <c r="J282" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K282" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="L282" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="283" spans="2:12">
@@ -24577,13 +24580,13 @@
         <v>740</v>
       </c>
       <c r="J283" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K283" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="L283" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="284" spans="2:12">
@@ -24606,13 +24609,13 @@
         <v>740</v>
       </c>
       <c r="J284" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K284" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="L284" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="285" spans="2:12">
@@ -24635,13 +24638,13 @@
         <v>740</v>
       </c>
       <c r="J285" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K285" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="L285" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="286" spans="2:12">
@@ -24664,13 +24667,13 @@
         <v>740</v>
       </c>
       <c r="J286" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K286" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="L286" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="287" spans="2:12">
@@ -24693,13 +24696,13 @@
         <v>740</v>
       </c>
       <c r="J287" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K287" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="L287" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="288" spans="2:12">
@@ -24722,13 +24725,13 @@
         <v>740</v>
       </c>
       <c r="J288" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K288" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="L288" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="289" spans="2:12">
@@ -24751,13 +24754,13 @@
         <v>740</v>
       </c>
       <c r="J289" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K289" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="L289" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="290" spans="2:12">
@@ -24780,13 +24783,13 @@
         <v>740</v>
       </c>
       <c r="J290" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K290" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="L290" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="291" spans="2:12">
@@ -24809,13 +24812,13 @@
         <v>740</v>
       </c>
       <c r="J291" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K291" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="L291" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="292" spans="2:12">
@@ -24838,13 +24841,13 @@
         <v>740</v>
       </c>
       <c r="J292" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K292" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="L292" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="293" spans="2:12">
@@ -24867,13 +24870,13 @@
         <v>740</v>
       </c>
       <c r="J293" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K293" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="L293" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="294" spans="2:12">
@@ -24896,13 +24899,13 @@
         <v>740</v>
       </c>
       <c r="J294" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K294" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="L294" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="295" spans="2:12">
@@ -24925,13 +24928,13 @@
         <v>740</v>
       </c>
       <c r="J295" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K295" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="L295" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="296" spans="2:12">
@@ -24954,13 +24957,13 @@
         <v>740</v>
       </c>
       <c r="J296" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K296" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="L296" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="297" spans="2:12">
@@ -24980,71 +24983,71 @@
         <v>711</v>
       </c>
       <c r="H297" t="s">
-        <v>716</v>
+        <v>740</v>
       </c>
       <c r="J297" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K297" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="L297" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="298" spans="2:12">
       <c r="J298" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K298" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="L298" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="299" spans="2:12">
       <c r="J299" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K299" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="L299" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="300" spans="2:12">
       <c r="J300" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K300" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="L300" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="301" spans="2:12">
       <c r="J301" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K301" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="L301" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="302" spans="2:12">
       <c r="J302" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="K302" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="L302" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
   </sheetData>
